--- a/output/c4ai_dados_completos_limpo.xlsx
+++ b/output/c4ai_dados_completos_limpo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E407"/>
+  <dimension ref="A1:E408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Embedding propagation over heterogeneous event networks for link prediction</t>
+          <t>Learning to sense from events via semantic variational autoencoder</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Paulo Ricardo Viviurka do Carmo; Ricardo Marcondes Marcacini</t>
+          <t xml:space="preserve">Marcos Paulo Silva Gôlo; Rafael Geraldeli Rossi; Ricardo Marcondes Marcacini </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1704,17 +1704,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Previsão do preço futuro de commodities agrícolas: um estudo para enriquecer séries temporais</t>
+          <t>Embedding propagation over heterogeneous event networks for link prediction</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ivan José Reis Filho; Ricardo Marcondes Marcacini; Solange Oliveira Rezende</t>
+          <t>Paulo Ricardo Viviurka do Carmo; Ricardo Marcondes Marcacini</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trabalho de Evento</t>
+          <t>Artigo</t>
         </is>
       </c>
     </row>
@@ -1729,17 +1729,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>What is it about humanity that we can’t give away to intelligent machines? A European perspective</t>
+          <t>Previsão do preço futuro de commodities agrícolas: um estudo para enriquecer séries temporais</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Crispin Coombs; Patrick Stacey; Peter Kawalek; Boyka Simeonova; Joerg Becker; Katrin Bergener; João Álvaro Carvalho; Marcelo Fantinato; Niels Garmann-Johnsen; Christian Grimme. Armin Stein; Heike Trautmann</t>
+          <t>Ivan José Reis Filho; Ricardo Marcondes Marcacini; Solange Oliveira Rezende</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Citação</t>
+          <t>Trabalho de Evento</t>
         </is>
       </c>
     </row>
@@ -1754,17 +1754,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Desdobramentos da Implementação da Rede GO FAIR Agro Brasil no Biênio 2021-2023</t>
+          <t>What is it about humanity that we can’t give away to intelligent machines? A European perspective</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Debora Pignatari Drucker; Sérgio Manuel Serra da Cruz; Milena Ambrosio Telles; Ana Paula Ludtke Ferreira; Fernando Elias Corrêa; Patrícia Rocha Bello Bertin; Leandro Marassi; Krisley Aquino; Gabriel Bezerra; Pedro Vieira Cruz; Filipi Miranda Soares</t>
+          <t>Crispin Coombs; Patrick Stacey; Peter Kawalek; Boyka Simeonova; Joerg Becker; Katrin Bergener; João Álvaro Carvalho; Marcelo Fantinato; Niels Garmann-Johnsen; Christian Grimme. Armin Stein; Heike Trautmann</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Trabalho de Evento</t>
+          <t>Citação</t>
         </is>
       </c>
     </row>
@@ -1775,16 +1775,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Forecasting future corn and soybean prices: an analysis of the use of textual information to enrich time-series</t>
+          <t>Desdobramentos da Implementação da Rede GO FAIR Agro Brasil no Biênio 2021-2023</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ivan José Reis Filho; Guilherme Corrêa; Guilherme Mendonça Freire; Solange Oliveira Rezende</t>
+          <t>Debora Pignatari Drucker; Sérgio Manuel Serra da Cruz; Milena Ambrosio Telles; Ana Paula Ludtke Ferreira; Fernando Elias Corrêa; Patrícia Rocha Bello Bertin; Leandro Marassi; Krisley Aquino; Gabriel Bezerra; Pedro Vieira Cruz; Filipi Miranda Soares</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1796,25 +1796,25 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI HEALTH</t>
+          <t>AGRIBIO</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Characterizing data patterns with core–periphery network modeling</t>
+          <t>Forecasting future corn and soybean prices: an analysis of the use of textual information to enrich time-series</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Jianglong Yan; Leandro Anghinoni; Yu-Tao Zhu; Weiguang Liu; Gen Li; Qiusheng Zheng; Liang Zhao</t>
+          <t>Ivan José Reis Filho; Guilherme Corrêa; Guilherme Mendonça Freire; Solange Oliveira Rezende</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Artigo Acadêmico Completo Publicado (revista)</t>
+          <t>Trabalho de Evento</t>
         </is>
       </c>
     </row>
@@ -1829,12 +1829,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Quantized pinning bipartite synchronization of fractional-order coupled reaction–diffusion neural networks with time-varying delays</t>
+          <t>Characterizing data patterns with core–periphery network modeling</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Kai Wu; Ming Tang; Han Ren; Liang Zhao</t>
+          <t>Jianglong Yan; Leandro Anghinoni; Yu-Tao Zhu; Weiguang Liu; Gen Li; Qiusheng Zheng; Liang Zhao</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Error-Correcting Mean-Teacher: Corrections instead of consistency-targets applied to semi-supervised medical image segmentation</t>
+          <t>Quantized pinning bipartite synchronization of fractional-order coupled reaction–diffusion neural networks with time-varying delays</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Robert Mendel; David Rauber; Luis de Souza; João Papa; Christoph Palm</t>
+          <t>Kai Wu; Ming Tang; Han Ren; Liang Zhao</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lightweight neural architectures to improve COVID-19 identification</t>
+          <t>Error-Correcting Mean-Teacher: Corrections instead of consistency-targets applied to semi-supervised medical image segmentation</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mohammad Mehedi Hassan; Salman AlQahtani; Abdulhameed Alelaiwi; João Papa</t>
+          <t>Robert Mendel; David Rauber; Luis de Souza; João Papa; Christoph Palm</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tabular data augmentation for video-based detection of hypomimia in Parkinson’s disease</t>
+          <t>Lightweight neural architectures to improve COVID-19 identification</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Guilherme Oliveira; Quoc Ngo; Leandro Passos; João Papa; Danilo Jodas; Dinesh Kumar</t>
+          <t>Mohammad Mehedi Hassan; Salman AlQahtani; Abdulhameed Alelaiwi; João Papa</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1929,12 +1929,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Artificial intelligence for oral cancer diagnosis: What are the possibilities?</t>
+          <t>Tabular data augmentation for video-based detection of hypomimia in Parkinson’s disease</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mattheus Tobias; Bruna Nogueira; Marcos Santana; Rafael Pires; João Papa; Paulo Santos</t>
+          <t>Guilherme Oliveira; Quoc Ngo; Leandro Passos; João Papa; Danilo Jodas; Dinesh Kumar</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Histopathological diagnosis of colon cancer using micro-FTIR hyperspectral imaging and deep learning</t>
+          <t>Artificial intelligence for oral cancer diagnosis: What are the possibilities?</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Frederico Barbosa Muniz; Matheus de Freitas Oliveira Baffa; Sergio Britto Garcia; Luciano Bachmann; Joaquim Cezar Felipe</t>
+          <t>Mattheus Tobias; Bruna Nogueira; Marcos Santana; Rafael Pires; João Papa; Paulo Santos</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Deep learning for automatic mandible segmentation on dental panoramic x-ray images</t>
+          <t>Histopathological diagnosis of colon cancer using micro-FTIR hyperspectral imaging and deep learning</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Leonardo Ferreira Machado; Plauto Christopher Aranha Watanabe; Giovani Aantonio Rodrigues; Luiz Otavio Murta Junior</t>
+          <t>Frederico Barbosa Muniz; Matheus de Freitas Oliveira Baffa; Sergio Britto Garcia; Luciano Bachmann; Joaquim Cezar Felipe</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2004,12 +2004,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wearable potentiometric biosensor for analysis of urea in sweat</t>
+          <t>Deep learning for automatic mandible segmentation on dental panoramic x-ray images</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Gisela Ibáñez-Redín; Giovana Rosso Cagnani; Nathalia Gomes; Paulo Raymundo-Pereira; Sergio Machado; Marco Antonio Gutierrez; Jose Eduardo Krieger; Osvaldo Oliveira</t>
+          <t>Leonardo Ferreira Machado; Plauto Christopher Aranha Watanabe; Giovani Aantonio Rodrigues; Luiz Otavio Murta Junior</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Siamese Convolutional Neural Network For Heartbeat Classification Using Limited 12-lead Ecg Datasets. Ieee Access, V. 2023, P. 1-1, 2023. Doi: 10.1109/access.2023.3236189.</t>
+          <t>Wearable potentiometric biosensor for analysis of urea in sweat</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Eduardo Vasconcellos; Bruno Georgevich Ferreira; Jorge Leandro; Baldoino Neto; Filipe Rolim Cordeiro; Idágene Cestari</t>
+          <t>Gisela Ibáñez-Redín; Giovana Rosso Cagnani; Nathalia Gomes; Paulo Raymundo-Pereira; Sergio Machado; Marco Antonio Gutierrez; Jose Eduardo Krieger; Osvaldo Oliveira</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Blood Pressure Estimation From Photoplethysmography by Considering Intra-and Inter-Subject Variabilities: Guidelines for a Fair Assessment</t>
+          <t>Siamese Convolutional Neural Network For Heartbeat Classification Using Limited 12-lead Ecg Datasets. Ieee Access, V. 2023, P. 1-1, 2023. Doi: 10.1109/access.2023.3236189.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Thiago Bulhões Da Silva Costa; Felipe Meneguitti Dias; Diego Armando Cardona Cardenas; Marcelo Arruda Fiuza De Toledo; Daniel Mário De Lima; Jose Eduardo Krieger</t>
+          <t>Eduardo Vasconcellos; Bruno Georgevich Ferreira; Jorge Leandro; Baldoino Neto; Filipe Rolim Cordeiro; Idágene Cestari</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Siamese pyramidal deep learning network for strain estimation in 3D cardiac cine-MR</t>
+          <t>Blood Pressure Estimation From Photoplethysmography by Considering Intra-and Inter-Subject Variabilities: Guidelines for a Fair Assessment</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Catharine Graves; Marina Rebelo; Ramon Moreno; Roberto Dantas-Jr; Antonildes Assunção-Jr; Cesar Nomura; Marco Gutierrez</t>
+          <t>Thiago Bulhões Da Silva Costa; Felipe Meneguitti Dias; Diego Armando Cardona Cardenas; Marcelo Arruda Fiuza De Toledo; Daniel Mário De Lima; Jose Eduardo Krieger</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Feature extraction and selection from electroencephalogram signals for epileptic seizure diagnosis</t>
+          <t>Siamese pyramidal deep learning network for strain estimation in 3D cardiac cine-MR</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dionathan Luan de Vargas; Jefferson Tales Oliva; Marcelo Teixeira; Dalcimar Casanova; João Luís Garcia Rosa </t>
+          <t>Catharine Graves; Marina Rebelo; Ramon Moreno; Roberto Dantas-Jr; Antonildes Assunção-Jr; Cesar Nomura; Marco Gutierrez</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Text characterization based on recurrence networks</t>
+          <t>Feature extraction and selection from electroencephalogram signals for epileptic seizure diagnosis</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Bárbara e Souza; Filipi Silva; Henrique de Arruda; Giovana da Silva; Luciano Costa; Diego Amancio</t>
+          <t xml:space="preserve">Dionathan Luan de Vargas; Jefferson Tales Oliva; Marcelo Teixeira; Dalcimar Casanova; João Luís Garcia Rosa </t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Network Analysis and Natural Language Processing to Obtain a Landscape of the Scientific Literature on Materials Applications</t>
+          <t>Text characterization based on recurrence networks</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ana Caroline Brito; Maria Cristina Oliveira; Osvaldo Oliveira; Filipi Silva; Diego Amancio</t>
+          <t>Bárbara e Souza; Filipi Silva; Henrique de Arruda; Giovana da Silva; Luciano Costa; Diego Amancio</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>A Stochastic Grammar Approach to Mass Classification in Mammograms</t>
+          <t>Network Analysis and Natural Language Processing to Obtain a Landscape of the Scientific Literature on Materials Applications</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ricardo Wandré Dias Pedro; Ana Luiza Silveira Ferreira; Rodolph Vinicius Siqueira Pessoa; Almir Galvão Vieira Bitencourt; Ariane Machado-Lima; Fátima Nunes</t>
+          <t>Ana Caroline Brito; Maria Cristina Oliveira; Osvaldo Oliveira; Filipi Silva; Diego Amancio</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Left ventricle segmentation combining deep learning and deformable models with anatomical constraints</t>
+          <t>A Stochastic Grammar Approach to Mass Classification in Mammograms</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Matheus Ribeiro; Fátima Nunes</t>
+          <t>Ricardo Wandré Dias Pedro; Ana Luiza Silveira Ferreira; Rodolph Vinicius Siqueira Pessoa; Almir Galvão Vieira Bitencourt; Ariane Machado-Lima; Fátima Nunes</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Neuroplasticity changes in knee osteoarthritis (KOA) indexed by event-related desynchronization/synchronization during a motor inhibition task</t>
+          <t>Left ventricle segmentation combining deep learning and deformable models with anatomical constraints</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Lucas Marques; Ana Castellani; Sara Barbosa; Marta Imamura; Linamara Battistella; Marcel Simis; Felipe Fregni</t>
+          <t>Matheus Ribeiro; Fátima Nunes</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2254,12 +2254,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Robotic-Assisted Gait Training (RAGT) in Stroke Rehabilitation: A Pilot Study</t>
+          <t>Neuroplasticity changes in knee osteoarthritis (KOA) indexed by event-related desynchronization/synchronization during a motor inhibition task</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mariana Vita Milazzotto Neves; Leonardo Furlan; Felipe Fregni; Linamara Rizzo Battistella; Marcel Simis</t>
+          <t>Lucas Marques; Ana Castellani; Sara Barbosa; Marta Imamura; Linamara Battistella; Marcel Simis; Felipe Fregni</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Association of Mu opioid receptor (A118G) and BDNF (G196A) polymorphisms with rehabilitation-induced cortical inhibition and analgesic response in chronic osteoarthritis pain</t>
+          <t>Robotic-Assisted Gait Training (RAGT) in Stroke Rehabilitation: A Pilot Study</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Fernanda de Toledo Gonçalves; Kevin Pacheco-Barrios; Ingrid Rebello-Sanchez; Luis Castelo-Branco; Paulo de Melo; Joao Parente; Alejandra Cardenas-Rojas; Isabela Firigato; Anne Victorio Pessotto; Marta Imamura ; Marcel Simis; Linamara Battistella; Felipe Fregni</t>
+          <t>Mariana Vita Milazzotto Neves; Leonardo Furlan; Felipe Fregni; Linamara Rizzo Battistella; Marcel Simis</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2304,12 +2304,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TransGNN: A Transductive Graph Neural Network with Graph Dynamic Embedding</t>
+          <t>Association of Mu opioid receptor (A118G) and BDNF (G196A) polymorphisms with rehabilitation-induced cortical inhibition and analgesic response in chronic osteoarthritis pain</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Leandro Anghinoni; Yu-tao Zhu; Donghong Ji; Liang Zhao</t>
+          <t>Fernanda de Toledo Gonçalves; Kevin Pacheco-Barrios; Ingrid Rebello-Sanchez; Luis Castelo-Branco; Paulo de Melo; Joao Parente; Alejandra Cardenas-Rojas; Isabela Firigato; Anne Victorio Pessotto; Marta Imamura ; Marcel Simis; Linamara Battistella; Felipe Fregni</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2329,12 +2329,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Classification of coma etiology using convolutional neural networks and long-short term memory networks</t>
+          <t>TransGNN: A Transductive Graph Neural Network with Graph Dynamic Embedding</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Sérgio Baldo Júnior; Murillo Carneiro; João-Batista Destro-Filho; Liang Zhao; Renato Tinós</t>
+          <t>Leandro Anghinoni; Yu-tao Zhu; Donghong Ji; Liang Zhao</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Data classification via centrality measures of complex networks</t>
+          <t>Classification of coma etiology using convolutional neural networks and long-short term memory networks</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Janayna Fernandes; Guilherme Suzuki; Liang Zhao; Murillo Carneiro</t>
+          <t>Sérgio Baldo Júnior; Murillo Carneiro; João-Batista Destro-Filho; Liang Zhao; Renato Tinós</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Complex Network-Based Data Classification Using Minimum Spanning Tree Metric and Optimization</t>
+          <t>Data classification via centrality measures of complex networks</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Josimar Chire Saire; Liang Zhao</t>
+          <t>Janayna Fernandes; Guilherme Suzuki; Liang Zhao; Murillo Carneiro</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>High-Level Classification for EEG Analysis</t>
+          <t>Complex Network-Based Data Classification Using Minimum Spanning Tree Metric and Optimization</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Murillo Carneiro; Camila Ramos; João-Batista Destro-Filho; Yu-tao Zhu; Donghong Ji; Liang Zhao</t>
+          <t>Josimar Chire Saire; Liang Zhao</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Maximizing portfolio profitability during a cryptocurrency downtrend: A Bitcoin Blockchain transaction-based approach</t>
+          <t>High-Level Classification for EEG Analysis</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Esteban Wilfredo Vilca Zuniga; Caetano Mazzoni Ranieri; Liang Zhao; Jó Ueyama; Yu-tao Zhu; Donghong Ji</t>
+          <t>Murillo Carneiro; Camila Ramos; João-Batista Destro-Filho; Yu-tao Zhu; Donghong Ji; Liang Zhao</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Genetic Algorithm with Linkage Learning</t>
+          <t>Maximizing portfolio profitability during a cryptocurrency downtrend: A Bitcoin Blockchain transaction-based approach</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Renato Tinós; Michal Przewozniczek; Darrell Whitley; Francisco Chicano</t>
+          <t>Esteban Wilfredo Vilca Zuniga; Caetano Mazzoni Ranieri; Liang Zhao; Jó Ueyama; Yu-tao Zhu; Donghong Ji</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>First Improvement Hill Climber with Linkage Learning -- on Introducing Dark Gray-Box Optimization into Statistical Linkage Learning Genetic Algorithms</t>
+          <t>Genetic Algorithm with Linkage Learning</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Michal Witold Przewozniczek; Renato Tinós; Marcin Michal Komarnicki</t>
+          <t>Renato Tinós; Michal Przewozniczek; Darrell Whitley; Francisco Chicano</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Harmony Search-Based Approaches for Fine-Tuning Deep Belief Networks</t>
+          <t>First Improvement Hill Climber with Linkage Learning -- on Introducing Dark Gray-Box Optimization into Statistical Linkage Learning Genetic Algorithms</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Douglas Rodrigues; Mateus Roder; Leandro Aparecido Passos; Gustavo Henrique de Rosa; João Paulo Papa; Zong Woo Geem </t>
+          <t>Michal Witold Przewozniczek; Renato Tinós; Marcin Michal Komarnicki</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fine-Tuning Restricted Boltzmann Machines Using No-Boundary Jellyfish</t>
+          <t>Harmony Search-Based Approaches for Fine-Tuning Deep Belief Networks</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Douglas Rodrigues; Gustavo Henrique de Rosa; Kelton Augusto Pontara da Costa; Danilo Samuel Jodas; João Paulo Papa</t>
+          <t xml:space="preserve">Douglas Rodrigues; Mateus Roder; Leandro Aparecido Passos; Gustavo Henrique de Rosa; João Paulo Papa; Zong Woo Geem </t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>A Multi-Class Probabilistic Optimum-Path Forest</t>
+          <t>Fine-Tuning Restricted Boltzmann Machines Using No-Boundary Jellyfish</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Silas Nachif Fernandes; ,Leandro Passos; André Souza; Danilo Jodas; Marco Akio; André Souza; João Paulo Papa</t>
+          <t xml:space="preserve"> Douglas Rodrigues; Gustavo Henrique de Rosa; Kelton Augusto Pontara da Costa; Danilo Samuel Jodas; João Paulo Papa</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Deep Learning Semantic Segmentation Models for Detecting the Tree Crown Foliage</t>
+          <t>A Multi-Class Probabilistic Optimum-Path Forest</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Danilo Samuel Jodas; Giulian Del Nero Velasco; Reinaldo Araujo de Lima; Aline Ribeiro Machado; João Paulo Papa</t>
+          <t xml:space="preserve"> Silas Nachif Fernandes; ,Leandro Passos; André Souza; Danilo Jodas; Marco Akio; André Souza; João Paulo Papa</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Extractive Text Summarization Using Generalized Additive Models with Interactions for Sentence Selection</t>
+          <t>Deep Learning Semantic Segmentation Models for Detecting the Tree Crown Foliage</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Vinícius Camargo da Silva; João Paulo Papa; Kelton Augusto Pontara da Costa</t>
+          <t>Danilo Samuel Jodas; Giulian Del Nero Velasco; Reinaldo Araujo de Lima; Aline Ribeiro Machado; João Paulo Papa</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FakeRecogna Anomaly: Fake News Detection in a New Brazilian Corpus</t>
+          <t>Extractive Text Summarization Using Generalized Additive Models with Interactions for Sentence Selection</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Gabriel Lino Garcia; Luis Afonso; Leandro Passos; Kelton da Costa; João Paulo Papa; Danilo Jodas</t>
+          <t>Vinícius Camargo da Silva; João Paulo Papa; Kelton Augusto Pontara da Costa</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -2654,12 +2654,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Binary Flying Squirrel Optimizer for Feature Selection</t>
+          <t>FakeRecogna Anomaly: Fake News Detection in a New Brazilian Corpus</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Luiz Fernando Merli de Oliveira Sementille; Douglas Rodrigues; André Nunes de Souuza; João Paulo Papa</t>
+          <t>Gabriel Lino Garcia; Luis Afonso; Leandro Passos; Kelton da Costa; João Paulo Papa; Danilo Jodas</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Feature Selection and Hyperparameter Fine-Tuning in Artificial Neural Networks for Wood Quality Classification</t>
+          <t>Binary Flying Squirrel Optimizer for Feature Selection</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mateus Roder; Leandro Aparecido Passos; João Paulo Papa; André Luis Debiaso Rossi </t>
+          <t>Luiz Fernando Merli de Oliveira Sementille; Douglas Rodrigues; André Nunes de Souuza; João Paulo Papa</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Advancing Thyroid Pathologies Detection with Recurrent Neural Networks and Micro-FTIR Hyperspectral Imaging</t>
+          <t>Feature Selection and Hyperparameter Fine-Tuning in Artificial Neural Networks for Wood Quality Classification</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Matheus De Freitas Oliveira Baffa; Luciano Bachmann; Denise Maria Zezell; Thiago Martini Pereira; Thomas Martin Deserno; Joaquim Cezar Felipe</t>
+          <t xml:space="preserve">Mateus Roder; Leandro Aparecido Passos; João Paulo Papa; André Luis Debiaso Rossi </t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -2725,44 +2725,44 @@
         </is>
       </c>
       <c r="B93" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Advancing Thyroid Pathologies Detection with Recurrent Neural Networks and Micro-FTIR Hyperspectral Imaging</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Matheus De Freitas Oliveira Baffa; Luciano Bachmann; Denise Maria Zezell; Thiago Martini Pereira; Thomas Martin Deserno; Joaquim Cezar Felipe</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Artigo Acadêmico Completo Publicado (revista)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AI HEALTH</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
         <v>2022</v>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Amplified signal response by cluster synchronization competition in rings with short-distance couplings</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t xml:space="preserve">Xiaoming Liang; Lei Hua; Xiyun Zhang; Liang Zhao
 </t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Artigo Acadêmico Completo Publicado (revista)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>AI HEALTH</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>TOE: A Grid-Tagging Discontinuous NER Model Enhanced by Embedding Tag/Word Relations and More Fine-Grained Tags</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Jiang Liu; Donghong Ji; Jingye Li; Dongdong Xie; Chong Teng; Liang Zhao; Fei Li</t>
-        </is>
-      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>Artigo Acadêmico Completo Publicado (revista)</t>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Heart rate variability as a biomarker in patients with Chronic Chagas Cardiomyopathy with or without concomitant digestive involvement and its relationship with the Rassi score</t>
+          <t>TOE: A Grid-Tagging Discontinuous NER Model Enhanced by Embedding Tag/Word Relations and More Fine-Grained Tags</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Luiz Eduardo Virgilio Silva; Henrique Turin Moreira; Marina Madureira de Oliveira; Lorena Sayore Suzumura Cintra; Helio Cesar Salgado; Rubens Fazan Jr; Renato Tinós; Anis Rassi Jr; André Schmidt; Antônio Marin-Neto</t>
+          <t>Jiang Liu; Donghong Ji; Jingye Li; Dongdong Xie; Chong Teng; Liang Zhao; Fei Li</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Clinical and demographic predictors of symptoms of depression and anxiety in patients with spinal cord injury</t>
+          <t>Heart rate variability as a biomarker in patients with Chronic Chagas Cardiomyopathy with or without concomitant digestive involvement and its relationship with the Rassi score</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Ana Clara Portela Hara; Nicole Aching ; Lucas Marques; Felipe Fregni; Linamara Battisttella; Marcel Simis</t>
+          <t>Luiz Eduardo Virgilio Silva; Henrique Turin Moreira; Marina Madureira de Oliveira; Lorena Sayore Suzumura Cintra; Helio Cesar Salgado; Rubens Fazan Jr; Renato Tinós; Anis Rassi Jr; André Schmidt; Antônio Marin-Neto</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>OneEE: A One-Stage Framework for Fast Overlapping and Nested Event Extraction</t>
+          <t>Clinical and demographic predictors of symptoms of depression and anxiety in patients with spinal cord injury</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Hu Cao; Jingye Li; Fangfang Su; Fei Li; Hao Fei; Shengqiong Wu; Bobo Li; Liang Zhao; Donghong Ji</t>
+          <t>Ana Clara Portela Hara; Nicole Aching ; Lucas Marques; Felipe Fregni; Linamara Battisttella; Marcel Simis</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Analysis of Radiographic Images of Patients with COVID-19 Using Fractal Dimension and Complex Network-Based High-Level Classification</t>
+          <t>OneEE: A One-Stage Framework for Fast Overlapping and Nested Event Extraction</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weiguang Liu; Jianglong Yan; Yu-tao Zhu; Everson José de Freitas Pereira; Gen Li; Qiusheng Zheng; Liang Zhao </t>
+          <t>Hu Cao; Jingye Li; Fangfang Su; Fei Li; Hao Fei; Shengqiong Wu; Bobo Li; Liang Zhao; Donghong Ji</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Classification of Dispersed Patterns of Radiographic Images with COVID-19 by Core-Periphery Network Modeling</t>
+          <t>Analysis of Radiographic Images of Patients with COVID-19 Using Fractal Dimension and Complex Network-Based High-Level Classification</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jianglong Yan; Weiguang Liu; Yu-tao Zhu; Gen Li; Qiusheng Zheng; Liang Zhao </t>
+          <t xml:space="preserve">Weiguang Liu; Jianglong Yan; Yu-tao Zhu; Everson José de Freitas Pereira; Gen Li; Qiusheng Zheng; Liang Zhao </t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Feature Ranking from Random Forest Through Complex Network’s Centrality Measures</t>
+          <t>Classification of Dispersed Patterns of Radiographic Images with COVID-19 by Core-Periphery Network Modeling</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adriano Henrique Cantão; Alessandra Alaniz Macedo; Liang Zhao; José Augusto Baranauskas </t>
+          <t xml:space="preserve">Jianglong Yan; Weiguang Liu; Yu-tao Zhu; Gen Li; Qiusheng Zheng; Liang Zhao </t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Histopathological Analysis of Fine-Needle Aspiration Biopsies of Thyroid Nodules Using Explainable Convolutional Neural Networks</t>
+          <t>Feature Ranking from Random Forest Through Complex Network’s Centrality Measures</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matheus de Freitas Oliveira Baffa; Luciano Bachmann; Thiago Martini Pereira; Denise Maria Zezell; Edson Garcia Soares; Joel Del Bel Pádua; Joaquim Cezar Felipe </t>
+          <t xml:space="preserve">Adriano Henrique Cantão; Alessandra Alaniz Macedo; Liang Zhao; José Augusto Baranauskas </t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>COVID-19 and Viral Pneumonia Classification Using Radiomic Features and Deep Learning</t>
+          <t>Histopathological Analysis of Fine-Needle Aspiration Biopsies of Thyroid Nodules Using Explainable Convolutional Neural Networks</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Matheus de Freitas Oliveira Baffa; Fernando Lucas Lima Martins; Alessandra Martins Coelho; Joaquim Cezar Felipe</t>
+          <t xml:space="preserve">Matheus de Freitas Oliveira Baffa; Luciano Bachmann; Thiago Martini Pereira; Denise Maria Zezell; Edson Garcia Soares; Joel Del Bel Pádua; Joaquim Cezar Felipe </t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -2980,17 +2980,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Multilevel Coarsening for Interactive Visualization of Large Bipartite Networks</t>
+          <t>COVID-19 and Viral Pneumonia Classification Using Radiomic Features and Deep Learning</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Alan Demétrius Baria Valejo; Renato Fabbri; Alneu de Andrade Lopes; Liang Zhao; Maria Cristina Ferreira de Oliveira</t>
+          <t>Matheus de Freitas Oliveira Baffa; Fernando Lucas Lima Martins; Alessandra Martins Coelho; Joaquim Cezar Felipe</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Publicação</t>
+          <t>Artigo Acadêmico Completo Publicado (revista)</t>
         </is>
       </c>
     </row>
@@ -3001,16 +3001,16 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>A New Particle Competition Model for Community Detection with Application in Functional Brain Networks</t>
+          <t>Multilevel Coarsening for Interactive Visualization of Large Bipartite Networks</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Paulo Henrique Lima de Paula; Liang Zhao</t>
+          <t>Alan Demétrius Baria Valejo; Renato Fabbri; Alneu de Andrade Lopes; Liang Zhao; Maria Cristina Ferreira de Oliveira</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Anomaly Detection in Brazilian Federal Government Purchase Cards Through Unsupervised Learning Techniques</t>
+          <t>A New Particle Competition Model for Community Detection with Application in Functional Brain Networks</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breno Nunes; Tiago Colliri; Marcelo Lauretto; Weiguang Liu; Liang Zhao </t>
+          <t>Paulo Henrique Lima de Paula; Liang Zhao</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Coarsening Algorithm via Semi-synchronous Label Propagation for Bipartite Networks</t>
+          <t>Anomaly Detection in Brazilian Federal Government Purchase Cards Through Unsupervised Learning Techniques</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alan Demétrius Baria Valejo; Paulo Eduardo Althoff; Thiago de Paulo Faleiros; Maria Lígia Chuerubim; Jianglong Yan; Weiguang Liu; Liang Zhao </t>
+          <t xml:space="preserve">Breno Nunes; Tiago Colliri; Marcelo Lauretto; Weiguang Liu; Liang Zhao </t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Detecting Early Signs of Insufficiency in COVID-19 Patients from CBC Tests Through a Supervised Learning Approach</t>
+          <t>Coarsening Algorithm via Semi-synchronous Label Propagation for Bipartite Networks</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiago Colliri; Marcia Minakawa; Liang Zhao </t>
+          <t xml:space="preserve">Alan Demétrius Baria Valejo; Paulo Eduardo Althoff; Thiago de Paulo Faleiros; Maria Lígia Chuerubim; Jianglong Yan; Weiguang Liu; Liang Zhao </t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3101,16 +3101,16 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Clustered and deep echo state networks for signal noise reduction</t>
+          <t>Detecting Early Signs of Insufficiency in COVID-19 Patients from CBC Tests Through a Supervised Learning Approach</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laercio de Oliveira Junior; Florian Stelzer; Liang Zhao </t>
+          <t xml:space="preserve">Tiago Colliri; Marcia Minakawa; Liang Zhao </t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3122,25 +3122,25 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>HUMANITIES</t>
+          <t>AI HEALTH</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Direito e Inteligência Artificial: Fundamentos Volume 5</t>
+          <t>Clustered and deep echo state networks for signal noise reduction</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Paola Cantarini; Willis Guerra FIlho; Cristina Godoy</t>
+          <t xml:space="preserve">Laercio de Oliveira Junior; Florian Stelzer; Liang Zhao </t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Livro Editores</t>
+          <t>Publicação</t>
         </is>
       </c>
     </row>
@@ -3155,17 +3155,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Latin America's Contested Norms</t>
+          <t>Direito e Inteligência Artificial: Fundamentos Volume 5</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>João Paulo Veiga; Scott Martin</t>
+          <t>Paola Cantarini; Willis Guerra FIlho; Cristina Godoy</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Capítulo de Livro</t>
+          <t>Livro Editores</t>
         </is>
       </c>
     </row>
@@ -3180,17 +3180,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Direito e Inteligência Artificial: Fundamentos Volume 1</t>
+          <t>Artificial Intelligence Latin America's Contested Norms</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Willis Guerra Filho; Lucia Santaella; Dora Kaufman; Paola Cantarini (Editores)</t>
+          <t>João Paulo Veiga; Scott Martin</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Livro Editores</t>
+          <t>Capítulo de Livro</t>
         </is>
       </c>
     </row>
@@ -3201,21 +3201,21 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Mineração de Processos como Ferramenta para Promoção da Transparência: Oportunidades e Desafios</t>
+          <t>Direito e Inteligência Artificial: Fundamentos Volume 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Renata Mendes de Araujo; Sarajane Marques Peres; Marcelo Fantinato; Adriana Jacoto Unger; Thais Rodrigues Neubauer</t>
+          <t>Willis Guerra Filho; Lucia Santaella; Dora Kaufman; Paola Cantarini (Editores)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Artigo Acadêmico</t>
+          <t>Livro Editores</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>X-Processes: Process model discovery with the best balance among fitness, precision, simplicity, and generalization through a genetic algorithm</t>
+          <t>Mineração de Processos como Ferramenta para Promoção da Transparência: Oportunidades e Desafios</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Marcelo Fantinato ; Sarajane Marques Peres; Hajo Reijers</t>
+          <t>Renata Mendes de Araujo; Sarajane Marques Peres; Marcelo Fantinato; Adriana Jacoto Unger; Thais Rodrigues Neubauer</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Regulação da Inteligência Artificial: Qual Modelo Adotar?</t>
+          <t>X-Processes: Process model discovery with the best balance among fitness, precision, simplicity, and generalization through a genetic algorithm</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Cristina Godoy Bernardo de Oliveira; João Paulo Cândia Veiga; Fabio Cozman</t>
+          <t>Marcelo Fantinato ; Sarajane Marques Peres; Hajo Reijers</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Parental perception of children's privacy in smart toys in countries of different economic levels</t>
+          <t>Regulação da Inteligência Artificial: Qual Modelo Adotar?</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Fernanda Maria Pinheiro Amâncio; Ana Paula Souza; Marcelo Fantinato; Sarajane Marques Peres; Patrick Hung; Luis Gustavo Coutinho do Rêgo; Jorge Roa</t>
+          <t>Cristina Godoy Bernardo de Oliveira; João Paulo Cândia Veiga; Fabio Cozman</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3305,17 +3305,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Reconhecimento Facial e Direitos Fundamentais. In: Direito e Inteligência Artificial: Fundamentos Volume 5</t>
+          <t>Parental perception of children's privacy in smart toys in countries of different economic levels</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paola Cantarini </t>
+          <t>Fernanda Maria Pinheiro Amâncio; Ana Paula Souza; Marcelo Fantinato; Sarajane Marques Peres; Patrick Hung; Luis Gustavo Coutinho do Rêgo; Jorge Roa</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Capítulo de Livro</t>
+          <t>Artigo Acadêmico</t>
         </is>
       </c>
     </row>
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Verbete - Dicionário dos Anti (2) – Anticolonialismo de Dados, Forthcoming.</t>
+          <t>Reconhecimento Facial e Direitos Fundamentais. In: Direito e Inteligência Artificial: Fundamentos Volume 5</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Paola Cantarini</t>
+          <t xml:space="preserve">Paola Cantarini </t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Filosofia da inteligência artificial com base nos valores construcionistas do “homo poieticus”</t>
+          <t>Verbete - Dicionário dos Anti (2) – Anticolonialismo de Dados, Forthcoming.</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Livro</t>
+          <t>Capítulo de Livro</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>A nova dimensão dos neurodireitos cibernéticos: imunização pactuada contra a ciberescravidão?</t>
+          <t>Filosofia da inteligência artificial com base nos valores construcionistas do “homo poieticus”</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Artigo</t>
+          <t>Livro</t>
         </is>
       </c>
     </row>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>GOBERNANZA ALGORÍTMICA, EXPLICACIÓN POR DISEÑO Y JUSTICIA POR DISEÑO</t>
+          <t>A nova dimensão dos neurodireitos cibernéticos: imunização pactuada contra a ciberescravidão?</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://jornal.usp.br/artigos/por-umaia-democratica-inclusiva-e-decolonial-frameworks-de-protecao-a-todos-os-direitos-fundamentais/, May, 13th</t>
+          <t>GOBERNANZA ALGORÍTMICA, EXPLICACIÓN POR DISEÑO Y JUSTICIA POR DISEÑO</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Capítulo de Livro</t>
+          <t>Artigo</t>
         </is>
       </c>
     </row>
@@ -3455,17 +3455,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>This hot AI summer will impact Brazil’s democracy</t>
+          <t>https://jornal.usp.br/artigos/por-umaia-democratica-inclusiva-e-decolonial-frameworks-de-protecao-a-todos-os-direitos-fundamentais/, May, 13th</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Cristina Godoy de Oliveira; Fabio Cozman; João Paulo Veiga</t>
+          <t>Paola Cantarini</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Artigo</t>
+          <t>Capítulo de Livro</t>
         </is>
       </c>
     </row>
@@ -3480,17 +3480,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Regulando a inteligência artificial: limites e possibilidades dos modelos jurídicos</t>
+          <t>This hot AI summer will impact Brazil’s democracy</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Cristina Godoy Bernardo de Oliveira; Pedro Sberni Rodrigues; Tiago Augustini de Lima</t>
+          <t>Cristina Godoy de Oliveira; Fabio Cozman; João Paulo Veiga</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Artigo Completo</t>
+          <t>Artigo</t>
         </is>
       </c>
     </row>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Profiling à brasileira: entre riscos reais e imediatas expectativas</t>
+          <t>Regulando a inteligência artificial: limites e possibilidades dos modelos jurídicos</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Cristina Godoy Bernardo de Oliveira; Rafael Meira Silva</t>
+          <t>Cristina Godoy Bernardo de Oliveira; Pedro Sberni Rodrigues; Tiago Augustini de Lima</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>A Inteligência Artificial na divisão leste-oeste</t>
+          <t>Profiling à brasileira: entre riscos reais e imediatas expectativas</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Isadora Maria Roseiro Ruiz; Cristina Godoy Bernardo de Oliveira</t>
+          <t>Cristina Godoy Bernardo de Oliveira; Rafael Meira Silva</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>The Alleged (Un)regulation of AI Use in Brazil: The Impact Assessment as a Solution</t>
+          <t>A Inteligência Artificial na divisão leste-oeste</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Cristina Godoy de Oliveira; Marco Papp</t>
+          <t>Isadora Maria Roseiro Ruiz; Cristina Godoy Bernardo de Oliveira</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -3580,12 +3580,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Regulation and Ethics of Facial Recognition Systems: An Analysis of Cases in the Court of Appeal in the State of São Paulo</t>
+          <t>The Alleged (Un)regulation of AI Use in Brazil: The Impact Assessment as a Solution</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cristina Godoy de Oliveira; Otávio de Paula Albuquerque; Emily Liene Belotti; Isabella Ferreira Lopes; Rodrigo Brandão Silva; Glauco Arbix </t>
+          <t>Cristina Godoy de Oliveira; Marco Papp</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>A Decentralized Super App</t>
+          <t>Regulation and Ethics of Facial Recognition Systems: An Analysis of Cases in the Court of Appeal in the State of São Paulo</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Fernando Kaway Carvalho Ota; Cristina Godoy de Oliveira; Rafael Meira Silva; Radu State</t>
+          <t xml:space="preserve">Cristina Godoy de Oliveira; Otávio de Paula Albuquerque; Emily Liene Belotti; Isabella Ferreira Lopes; Rodrigo Brandão Silva; Glauco Arbix </t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SOCIEDADE, DEMOCRACIA E CONFIANÇA: LEITURAS SOBRE A LEGITIMIDADE DO PODER POLÍTICO. In:  SOCIOLOGIA, ANTROPOLOGIA E CULTURA  JURÍDICAS. XXX CONGRESSO NACIONAL DO CONPEDI FORTALEZA - CE</t>
+          <t>A Decentralized Super App</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Cristina Godoy Bernardo De Oliveira; Lucas Paulo Fernandes; Felipe Slikta Padilha</t>
+          <t>Fernando Kaway Carvalho Ota; Cristina Godoy de Oliveira; Rafael Meira Silva; Radu State</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Governança de dados na agricultura digital: relato da experiência do C4AI</t>
+          <t>SOCIEDADE, DEMOCRACIA E CONFIANÇA: LEITURAS SOBRE A LEGITIMIDADE DO PODER POLÍTICO. In:  SOCIOLOGIA, ANTROPOLOGIA E CULTURA  JURÍDICAS. XXX CONGRESSO NACIONAL DO CONPEDI FORTALEZA - CE</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Cássia Mendes; Fernando Correa; Debora Drucker; Filipi Soares; Antônio Saraiva; Alexandre Delbem; Fernando Osório; Cristina Godoy de Oliveira; Juliano Maranhão</t>
+          <t>Cristina Godoy Bernardo De Oliveira; Lucas Paulo Fernandes; Felipe Slikta Padilha</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -3680,17 +3680,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ChatGPT e Fake News: inteligencia artificial e a promoção da desinformação. In: Edith Maria Barbosa Ramos. Direito, Novas Tecnologias e Desenvolvimento.</t>
+          <t>Governança de dados na agricultura digital: relato da experiência do C4AI</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Godoy de Oliveira, Cristina; Lima, T. A.; Bec¸ak,</t>
+          <t>Cássia Mendes; Fernando Correa; Debora Drucker; Filipi Soares; Antônio Saraiva; Alexandre Delbem; Fernando Osório; Cristina Godoy de Oliveira; Juliano Maranhão</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Capítulo de Livro</t>
+          <t>Artigo Completo</t>
         </is>
       </c>
     </row>
@@ -3701,21 +3701,21 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sources of Understanding in Supervised Machine Learning Models</t>
+          <t>ChatGPT e Fake News: inteligencia artificial e a promoção da desinformação. In: Edith Maria Barbosa Ramos. Direito, Novas Tecnologias e Desenvolvimento.</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Paulo Pirozelli</t>
+          <t>Godoy de Oliveira, Cristina; Lima, T. A.; Bec¸ak,</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Artigo</t>
+          <t>Capítulo de Livro</t>
         </is>
       </c>
     </row>
@@ -3730,12 +3730,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NATURAL LANGUAGE AT A CROSSROADS: FORMAL AND PROBABILISTIC APPROACHES IN PHILOSOPHY AND COMPUTER SCIENCE</t>
+          <t>Sources of Understanding in Supervised Machine Learning Models</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Paulo Pirozelli; Igor Câmara</t>
+          <t>Paulo Pirozelli</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Recommendations for a smart toy parental control tool</t>
+          <t>NATURAL LANGUAGE AT A CROSSROADS: FORMAL AND PROBABILISTIC APPROACHES IN PHILOSOPHY AND COMPUTER SCIENCE</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Otavio de Paula Albuquerque; Marcelo Fantinat; Patrick Hung; Sarajane Marques Peres; Farkhund Iqbal; Umair Rehman; Muhammad Umair Shah </t>
+          <t>Paulo Pirozelli; Igor Câmara</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -3780,17 +3780,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Recommendations For A Smart Toy Parental Control Tool. Journal Of Supercomputing, V. 1, P. 1-39, 2022.</t>
+          <t>Recommendations for a smart toy parental control tool</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Albuquerque, O. P.; Fantinato, M.; Hung, P.; Peres, S. M.; Iqbal, F.; Rehman, U.; Shah, M. U.</t>
+          <t xml:space="preserve">Otavio de Paula Albuquerque; Marcelo Fantinat; Patrick Hung; Sarajane Marques Peres; Farkhund Iqbal; Umair Rehman; Muhammad Umair Shah </t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Artigo Acadêmico</t>
+          <t>Artigo</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>An Exploratory Research About Ethical Issues On A Smart Toy: The Hello Barbie Case Study. In: Anais do Iii Workshop Sobre As Implicac¸ ˜oes da Computac¸ ˜ao Na Sociedade (wics 2022), 2022. P. 67-76.</t>
+          <t>Recommendations For A Smart Toy Parental Control Tool. Journal Of Supercomputing, V. 1, P. 1-39, 2022.</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Albuquerque, O. P.; Fantinato, M.; Peres, S. M.; Hung, P. C. K.</t>
+          <t>Albuquerque, O. P.; Fantinato, M.; Hung, P.; Peres, S. M.; Iqbal, F.; Rehman, U.; Shah, M. U.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Exploratory Research About Ethical Issues On A Smart Toy: The Hello Barbie Case Study. In: Workshop Sobre As Implicações da Computação Na Sociedade, 2022, Brasil. Anais do Iii Workshop Sobre As Implicações da Computação Na Sociedade (wics 2022), 2022. P. 67-76.</t>
+          <t>An Exploratory Research About Ethical Issues On A Smart Toy: The Hello Barbie Case Study. In: Anais do Iii Workshop Sobre As Implicac¸ ˜oes da Computac¸ ˜ao Na Sociedade (wics 2022), 2022. P. 67-76.</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Albuquerque, Ota´vio De Paula; Fantinato, Marcelo; Peres, Sarajane Marques; Hung, Patrick C. K. .</t>
+          <t>Albuquerque, O. P.; Fantinato, M.; Peres, S. M.; Hung, P. C. K.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Context-aware Completion Time Prediction For Business Process Monitoring. In: Proceedings Of The 10th World Conference On Information Systems And Technologies (worldcist’22), 2022. P. 1-12. 128</t>
+          <t>Exploratory Research About Ethical Issues On A Smart Toy: The Hello Barbie Case Study. In: Workshop Sobre As Implicações da Computação Na Sociedade, 2022, Brasil. Anais do Iii Workshop Sobre As Implicações da Computação Na Sociedade (wics 2022), 2022. P. 67-76.</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Alves, R. M.; Barbieri, L.; Stroeh, K.; Madeira, E. R. M.; Peres, S. M.</t>
+          <t>Albuquerque, Ota´vio De Paula; Fantinato, Marcelo; Peres, Sarajane Marques; Hung, Patrick C. K. .</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Getting To Know And Interacting With The Social Robot Zenbo (tm): An Exploratory Study With Brazilian Older Adults. In: Ieee Ctsoc International Conference On Games, Entertainment &amp; Media (gem), 2022, Bridgetown. Proceedings Of The Ieee Ctsoc International Conference On Games, Entertainment &amp; Media (gem 2022), 2022. P. 1-6.</t>
+          <t>Context-aware Completion Time Prediction For Business Process Monitoring. In: Proceedings Of The 10th World Conference On Information Systems And Technologies (worldcist’22), 2022. P. 1-12. 128</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Araujo, B. S. ; Araujo, J. V. F. ; Fantinato, M.; Cachioni, M. ; Albuquerque, O. P.; Giorgi, P. A. S.; Melo, R. C. ; Batistoni, S. S. T. ;peres, S. M.; Hung, Patrick C. K. .</t>
+          <t>Alves, R. M.; Barbieri, L.; Stroeh, K.; Madeira, E. R. M.; Peres, S. M.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Artificial Intelligence, Human Oversight, And Public Policies: Facial Recognition Systems In Brazilian Cities. In: Proceedings Of The 35th Canadian Conference On Artificial Intelligence, 2022.</t>
+          <t>Getting To Know And Interacting With The Social Robot Zenbo (tm): An Exploratory Study With Brazilian Older Adults. In: Ieee Ctsoc International Conference On Games, Entertainment &amp; Media (gem), 2022, Bridgetown. Proceedings Of The Ieee Ctsoc International Conference On Games, Entertainment &amp; Media (gem 2022), 2022. P. 1-6.</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Brandão, R.</t>
+          <t>Araujo, B. S. ; Araujo, J. V. F. ; Fantinato, M.; Cachioni, M. ; Albuquerque, O. P.; Giorgi, P. A. S.; Melo, R. C. ; Batistoni, S. S. T. ;peres, S. M.; Hung, Patrick C. K. .</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Emerging Technologies And The Future Of Work In The World’s Largest Economies: A Public Policy Comparison From 11 Countries. In: 79th Annual Midwest Political Science Association Hybrid Conference, 2022.</t>
+          <t>Artificial Intelligence, Human Oversight, And Public Policies: Facial Recognition Systems In Brazilian Cities. In: Proceedings Of The 35th Canadian Conference On Artificial Intelligence, 2022.</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Regulating Artificial Intelligence (ai) In Brazil: A Non-existent Agenda? In: 79th Annual Midwest Political Science Association Hybrid Conference, 2022.</t>
+          <t>Emerging Technologies And The Future Of Work In The World’s Largest Economies: A Public Policy Comparison From 11 Countries. In: 79th Annual Midwest Political Science Association Hybrid Conference, 2022.</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Interactive Trace Clustering To Enhance Incident Completion Time Prediction In Process Mining. In: Ceur Workshop Proceedings: Ci4pm-22 - 1st International Workshop On Computational Intelligence For Process Mining, 2022. P. 1-12.</t>
+          <t>Regulating Artificial Intelligence (ai) In Brazil: A Non-existent Agenda? In: 79th Annual Midwest Political Science Association Hybrid Conference, 2022.</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Neubauer, T. R.; Fernandes, A. G. L.; Fantinato, M.; Peres, S. M.</t>
+          <t>Brandão, R.</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -4005,12 +4005,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Transparency Promoted By Process Mining: An Exploratory Study In A Public Health Product Management Process. In: Workshop de Computação Aplicada Em Governo Eletrônico, 2022, Brasil. Anais do X Workshop de Computação Aplicada Em Governo Eletrônico (wcge 2022), 2022. P. 37-49.</t>
+          <t>Interactive Trace Clustering To Enhance Incident Completion Time Prediction In Process Mining. In: Ceur Workshop Proceedings: Ci4pm-22 - 1st International Workshop On Computational Intelligence For Process Mining, 2022. P. 1-12.</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Neubauer, Thais Rodrigues; Araujo, Renata Mendes De; Fantinato, Marcelo; Peres, Sarajane Marques; Peres, S. M.</t>
+          <t>Neubauer, T. R.; Fernandes, A. G. L.; Fantinato, M.; Peres, S. M.</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Resource Allocation Optimization In Business Processes Supported By Reinforcement Learning And Process Mining. In: 11th Brazilian Conference On Intelligent Systems (bracis 2022), 2022, Campinas. Proceedings Of 11th Brazilian Conference On Intelligent Systems, 2022. V. I. P. 580-595.</t>
+          <t>Transparency Promoted By Process Mining: An Exploratory Study In A Public Health Product Management Process. In: Workshop de Computação Aplicada Em Governo Eletrônico, 2022, Brasil. Anais do X Workshop de Computação Aplicada Em Governo Eletrônico (wcge 2022), 2022. P. 37-49.</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Neubauer, T. R. ; Silva, V. F. ; Fantinato, M.; Peres, S. M..</t>
+          <t>Neubauer, Thais Rodrigues; Araujo, Renata Mendes De; Fantinato, Marcelo; Peres, Sarajane Marques; Peres, S. M.</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Revista Jurídica- Unicuritiba, V.1, P.148-166 - 166, 2022.</t>
+          <t>Resource Allocation Optimization In Business Processes Supported By Reinforcement Learning And Process Mining. In: 11th Brazilian Conference On Intelligent Systems (bracis 2022), 2022, Campinas. Proceedings Of 11th Brazilian Conference On Intelligent Systems, 2022. V. I. P. 580-595.</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Oliveira, C. G. B.; Mendes, G. A. S. Green Technologies, And Intellectual Property Rights.</t>
+          <t>Neubauer, T. R. ; Silva, V. F. ; Fantinato, M.; Peres, S. M..</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Desafios da Regulação do Digital e da Inteligência Artificial No Brasil. In Bicentenário da Independência: Ciência e Tecnologia, Revista Usp, N. 135, 2022. Doi: https://doi.org/10.11606/issn.2316-9036.i135p137-162</t>
+          <t>Revista Jurídica- Unicuritiba, V.1, P.148-166 - 166, 2022.</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Oliveira, Cristina Godoy Bernardo De.</t>
+          <t>Oliveira, C. G. B.; Mendes, G. A. S. Green Technologies, And Intellectual Property Rights.</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -4105,17 +4105,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Desmistificando A Inteligência Artificial. Belo Horizonte: Editora Autêntica, 2022. Isbn 978-65-5928-158-9. 331 Páginas.</t>
+          <t>Desafios da Regulação do Digital e da Inteligência Artificial No Brasil. In Bicentenário da Independência: Ciência e Tecnologia, Revista Usp, N. 135, 2022. Doi: https://doi.org/10.11606/issn.2316-9036.i135p137-162</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Kaufman, D.</t>
+          <t>Oliveira, Cristina Godoy Bernardo De.</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Livro</t>
+          <t>Artigo Acadêmico</t>
         </is>
       </c>
     </row>
@@ -4130,12 +4130,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>M. Fake News e Inteligência Artificial - O Poder dos Algoritmos Na Guerra da Desinformação. Editora Almedina, 424 Páginas, 2022.</t>
+          <t>Desmistificando A Inteligência Artificial. Belo Horizonte: Editora Autêntica, 2022. Isbn 978-65-5928-158-9. 331 Páginas.</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Prado,</t>
+          <t>Kaufman, D.</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -4155,17 +4155,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>We Are Us, Come On. In: Ferrari, P. (ed.). We: Techno Consequences On The Human. Porto Alegre: Editora Fi, 269 P., Pp. 15-19, 2022. Isbn: 978-65-5917-471-3.</t>
+          <t>M. Fake News e Inteligência Artificial - O Poder dos Algoritmos Na Guerra da Desinformação. Editora Almedina, 424 Páginas, 2022.</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Bucci, E.</t>
+          <t>Prado,</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Capítulo de Livro</t>
+          <t>Livro</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Marco Legal da Ia (pl 21/20) - An´ Alise Comparativa `a Luz da Regulamentação Europeia (ai Act). In: Faleiros Junio, J. L. M. Tutela Coletiva do Corpo Eletrônico: Novos Desafios Ao Direito Digital. Editora Foco, 2022.</t>
+          <t>We Are Us, Come On. In: Ferrari, P. (ed.). We: Techno Consequences On The Human. Porto Alegre: Editora Fi, 269 P., Pp. 15-19, 2022. Isbn: 978-65-5917-471-3.</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Cantarini, P.</t>
+          <t>Bucci, E.</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Mercados de Trabalho Heterogêneos e Plataformas. In: Direito Internacional do Trabalho e A Organização Internacional do Trabalho: Proteção Social, Econômica, Política e Jurídica das Relações de Trabalho Em Tempos de Crise; Organization: Mannrich, N.; Cavalcante, J. Q. P. M.; Villatore, A. C.; Gunther, L. E. Instituto Memoria Editora, Curitiba, 2022.</t>
+          <t>Marco Legal da Ia (pl 21/20) - An´ Alise Comparativa `a Luz da Regulamentação Europeia (ai Act). In: Faleiros Junio, J. L. M. Tutela Coletiva do Corpo Eletrônico: Novos Desafios Ao Direito Digital. Editora Foco, 2022.</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Comin, A. A.; Cavalcante, J. Q. P.</t>
+          <t>Cantarini, P.</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>O Direito do Futuro e O Futuro do Direito. 1 Ed. São Paulo: Thomson Reuters, 2022, V.1, P. 265-287.isbn: 9786559913138.</t>
+          <t>Mercados de Trabalho Heterogêneos e Plataformas. In: Direito Internacional do Trabalho e A Organização Internacional do Trabalho: Proteção Social, Econômica, Política e Jurídica das Relações de Trabalho Em Tempos de Crise; Organization: Mannrich, N.; Cavalcante, J. Q. P. M.; Villatore, A. C.; Gunther, L. E. Instituto Memoria Editora, Curitiba, 2022.</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Lima, C., Maranhão, J. e Almada, M. Data Protection By Design, Data Protection By Default. In: Legal Innovation -</t>
+          <t>Comin, A. A.; Cavalcante, J. Q. P.</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Artificial Intelligence, Algorithmic Transparency And Public Policies: The Case Of Facial Recognition Technologies In The Public Transportation System Of Large Brazilian Municipalities. In Brazilian Conference On Intelligent Systems. Bracis 2022. Lectures Notes In Computer Science, Vol. 13653, Springer, 2022. Doi:https://doi.org/10.1007/978-3-031-21686-2 39</t>
+          <t>O Direito do Futuro e O Futuro do Direito. 1 Ed. São Paulo: Thomson Reuters, 2022, V.1, P. 265-287.isbn: 9786559913138.</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Brandão, Rodrigo; Oliveira, Cristina Godoy; Peres, Sarajane; Silva Ju´ Nior, Leôncio Da; Papp, Marco; Veiga, João Paulo Cândia; Bec¸ Ak, Rubens; Camargo, Laura.</t>
+          <t>Lima, C., Maranhão, J. e Almada, M. Data Protection By Design, Data Protection By Default. In: Legal Innovation -</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4276,21 +4276,21 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>"a Dynamic Model For Balancing Values." In Proceedings Of The Eighteenth International Conference On Artificial Intelligence And Law, Pp. 89-98.</t>
+          <t>Artificial Intelligence, Algorithmic Transparency And Public Policies: The Case Of Facial Recognition Technologies In The Public Transportation System Of Large Brazilian Municipalities. In Brazilian Conference On Intelligent Systems. Bracis 2022. Lectures Notes In Computer Science, Vol. 13653, Springer, 2022. Doi:https://doi.org/10.1007/978-3-031-21686-2 39</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Maranhão, Juliano, Edelcio G. de Souza, And Giovanni Sartor</t>
+          <t>Brandão, Rodrigo; Oliveira, Cristina Godoy; Peres, Sarajane; Silva Ju´ Nior, Leôncio Da; Papp, Marco; Veiga, João Paulo Cândia; Bec¸ Ak, Rubens; Camargo, Laura.</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Publicação</t>
+          <t>Capítulo de Livro</t>
         </is>
       </c>
     </row>
@@ -4305,17 +4305,17 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>"voice-based Diagnosis Of Covid-19: Ethical And Legal Challenges." International Data Privacy Law 11, No. 1 (2021): 63-75.[1 Citation]</t>
+          <t>"a Dynamic Model For Balancing Values." In Proceedings Of The Eighteenth International Conference On Artificial Intelligence And Law, Pp. 89-98.</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Almada, Marco, And Juliano Maranhão</t>
+          <t>Maranhão, Juliano, Edelcio G. de Souza, And Giovanni Sartor</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Citação</t>
+          <t>Publicação</t>
         </is>
       </c>
     </row>
@@ -4330,17 +4330,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>"sociologia e Abordagem Sociológica Em A Estrutura das Revoluções Científicas." Sofia 10, No. 2 (2021): 131-148.</t>
+          <t>"voice-based Diagnosis Of Covid-19: Ethical And Legal Challenges." International Data Privacy Law 11, No. 1 (2021): 63-75.[1 Citation]</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Pirozelli, Paulo</t>
+          <t>Almada, Marco, And Juliano Maranhão</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Publicação</t>
+          <t>Citação</t>
         </is>
       </c>
     </row>
@@ -4355,42 +4355,42 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Zero Um: A Indústria Brasileira de Videogames. In: Vii Seminário Discente do Programa de Pós-graduação Em Sociologia da Universidade de São Paulo, November-11th, 2021 - Organization: Moises, P. [et. Al.]. S˜ao Paulo: Fflch/usp, 2022.</t>
+          <t>"sociologia e Abordagem Sociológica Em A Estrutura das Revoluções Científicas." Sofia 10, No. 2 (2021): 131-148.</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Repa, M.</t>
+          <t>Pirozelli, Paulo</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Artigo Acadêmico</t>
+          <t>Publicação</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>KEML</t>
+          <t>HUMANITIES</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Legal Document-Based, Domain-Driven Q&amp;A System: LLMs in Perspective. In the International Joint Conference on Neural Networks IJCNN 2024, Yokohama – Japao, 2024. p.1-9. ISBN: 978-8-3503-5931-2.</t>
+          <t>Zero Um: A Indústria Brasileira de Videogames. In: Vii Seminário Discente do Programa de Pós-graduação Em Sociologia da Universidade de São Paulo, November-11th, 2021 - Organization: Moises, P. [et. Al.]. S˜ao Paulo: Fflch/usp, 2022.</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Esp´ırito Santo, F. O., Peres, S. M.; Gramacho G. S., Brandao A. A. F., Cozman, F. G.</t>
+          <t>Repa, M.</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Publicação</t>
+          <t>Artigo Acadêmico</t>
         </is>
       </c>
     </row>
@@ -4405,12 +4405,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Benchmarks for Pira 2.0, a Reading Comprehension Dataset about the Ocean, the Brazilian Coast, and Climate Change. In the Data Intelligence MIT Press Direct 2024, 2024. v.6. p.29-63. https://doi.org/10. 1162/dint_a_00245</t>
+          <t>Legal Document-Based, Domain-Driven Q&amp;A System: LLMs in Perspective. In the International Joint Conference on Neural Networks IJCNN 2024, Yokohama – Japao, 2024. p.1-9. ISBN: 978-8-3503-5931-2.</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Pirozelli, P.; Jose, M. M.; Silveira, I. C.; Nakasato, F.; Peres, S. M.; Brand ao, A. A. F.; Costa, A. H. R.; Cozman, F. G.</t>
+          <t>Esp´ırito Santo, F. O., Peres, S. M.; Gramacho G. S., Brandao A. A. F., Cozman, F. G.</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>In Proceedings IEEE 17th International Conference on Semantic Computing ICSC 2023, Laguna Hills, CA, USA, 2023. p. 107-113. https://doi. org/10.1109/ICSC56153.2023.00024</t>
+          <t>Benchmarks for Pira 2.0, a Reading Comprehension Dataset about the Ocean, the Brazilian Coast, and Climate Change. In the Data Intelligence MIT Press Direct 2024, 2024. v.6. p.29-63. https://doi.org/10. 1162/dint_a_00245</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Pellicer, L. F. A.; Costa, A. H. R. Improving Zero-Shot Inference with Unsupervised keySentences Extration.</t>
+          <t>Pirozelli, P.; Jose, M. M.; Silveira, I. C.; Nakasato, F.; Peres, S. M.; Brand ao, A. A. F.; Costa, A. H. R.; Cozman, F. G.</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Credal marginal MAP. Annual Conference on Neural Information Processing Systems NeurIPS, 2024.</t>
+          <t>In Proceedings IEEE 17th International Conference on Semantic Computing ICSC 2023, Laguna Hills, CA, USA, 2023. p. 107-113. https://doi. org/10.1109/ICSC56153.2023.00024</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Marinescu, R., Bhattacharjya, D., Lee, J., Cozman, F., Gray, A..</t>
+          <t>Pellicer, L. F. A.; Costa, A. H. R. Improving Zero-Shot Inference with Unsupervised keySentences Extration.</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Detection of potentially non-compliant clauses in online ToS in Portuguese. In: 23rd. Portuguese Conference on Artificial Intelligence EPIA 24, 2024.</t>
+          <t>Credal marginal MAP. Annual Conference on Neural Information Processing Systems NeurIPS, 2024.</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Tocchini, M., Rocha, I. M., Barros, R. M., Silva, J. O. E., Garcia, A. F., Maranhao, J. S. A., Sichman, J.</t>
+          <t>Marinescu, R., Bhattacharjya, D., Lee, J., Cozman, F., Gray, A..</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Trilha do 8º Workshop de Teses e Dissertações em Ontologias WTDO 2024.</t>
+          <t>Detection of potentially non-compliant clauses in online ToS in Portuguese. In: 23rd. Portuguese Conference on Artificial Intelligence EPIA 24, 2024.</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Soares, V. M. A.; Wassermann, R. Ontology Extraction and Evaluation for the Blue Amazon. 17º Seminario de Pesquisa em Ontologias ONTOBRAS 2024</t>
+          <t>Tocchini, M., Rocha, I. M., Barros, R. M., Silva, J. O. E., Garcia, A. F., Maranhao, J. S. A., Sichman, J.</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -4526,16 +4526,16 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>A Physics-informed Neural Operator For The Simulation Of Surface Waves”. In: 42nd International Conference On Ocean, Offshore &amp; Arctic Engineering.</t>
+          <t>Trilha do 8º Workshop de Teses e Dissertações em Ontologias WTDO 2024.</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Mathias, M.s.;netto, C.f.d.; Moreno, F.m.; Coelho, J.f.; Freitas, L.p.; Barros, M.r.; Mello, P.c.; Dottori, M.; Reali Costa, A.h.; Nogueira Junior, A.c.; Gomi, E.s.; Cozman, F.g.; Tannuri, E.a.. ”</t>
+          <t>Soares, V. M. A.; Wassermann, R. Ontology Extraction and Evaluation for the Blue Amazon. 17º Seminario de Pesquisa em Ontologias ONTOBRAS 2024</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Echo State Networks For Surface Current Forecasting In A Port Access Channel”. In: 42nd International Conference On Ocean, Offshore &amp; Arctic Engineering.</t>
+          <t>A Physics-informed Neural Operator For The Simulation Of Surface Waves”. In: 42nd International Conference On Ocean, Offshore &amp; Arctic Engineering.</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Moreno, F.m.; Barros, M.r.; Netto, C.f.d.; Coelho, J.f.; Freitas, L.p.; Mathias, M.s.; Dottori, M.; Reali Costa, A.h.; Gomi, E.s.; Cozman, F.g.; Tannuri, E.a.. ”</t>
+          <t>Mathias, M.s.;netto, C.f.d.; Moreno, F.m.; Coelho, J.f.; Freitas, L.p.; Barros, M.r.; Mello, P.c.; Dottori, M.; Reali Costa, A.h.; Nogueira Junior, A.c.; Gomi, E.s.; Cozman, F.g.; Tannuri, E.a.. ”</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Modeling Oceanic Variables With Graph-guided Networks For Irregularly Sampled Multivariate Time Series”. In: 42nd International Conference On Ocean, Offshore &amp; Arctic Engineering.</t>
+          <t>Echo State Networks For Surface Current Forecasting In A Port Access Channel”. In: 42nd International Conference On Ocean, Offshore &amp; Arctic Engineering.</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Coelho, J.f.; Barros, M.r.; Netto, C.f.d.; Moreno, F.m.; Freitas, L.p.; Mathias, M.s.; Cozman, F.g.; Dottori, M.; Gomi, E.s.; Tannuri, E.a.; Reali Costa, A.h.. ”</t>
+          <t>Moreno, F.m.; Barros, M.r.; Netto, C.f.d.; Coelho, J.f.; Freitas, L.p.; Mathias, M.s.; Dottori, M.; Reali Costa, A.h.; Gomi, E.s.; Cozman, F.g.; Tannuri, E.a.. ”</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>A Reading Comprehension Dataset About The Ocean, The Brazilian Coast, And Climate Change. Data Intelligence, 2023. (accepted)</t>
+          <t>Modeling Oceanic Variables With Graph-guided Networks For Irregularly Sampled Multivariate Time Series”. In: 42nd International Conference On Ocean, Offshore &amp; Arctic Engineering.</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Pirozelli, P., José M. M., Cacão, F. N., Silveira, I. C., Costa, A. H. R., Brandão, A. A. F., Cozman, F. G. And Peres, S. M. Benchmarks For Pir ´a 2.0, “</t>
+          <t>Coelho, J.f.; Barros, M.r.; Netto, C.f.d.; Moreno, F.m.; Freitas, L.p.; Mathias, M.s.; Cozman, F.g.; Dottori, M.; Gomi, E.s.; Tannuri, E.a.; Reali Costa, A.h.. ”</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Applying A Context-based Method To Build A Knowledge Graph For The Blue Amazon. Data Intelligence, 2023. (accepted)</t>
+          <t>A Reading Comprehension Dataset About The Ocean, The Brazilian Coast, And Climate Change. Data Intelligence, 2023. (accepted)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Ligabue, P. M., Brandão, A. A. F., Peres, S. M., Cozman, F. G. And Pirozelli, P. “</t>
+          <t>Pirozelli, P., José M. M., Cacão, F. N., Silveira, I. C., Costa, A. H. R., Brandão, A. A. F., Cozman, F. G. And Peres, S. M. Benchmarks For Pir ´a 2.0, “</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Data Augmentation Techniques In Natural Language Processing. Applied Soft Computing, V. 132, P. 109803, 2023.</t>
+          <t>Applying A Context-based Method To Build A Knowledge Graph For The Blue Amazon. Data Intelligence, 2023. (accepted)</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Pellicer, L. F. A. O., Ferreira, T. M., Costa, A. H. R. “</t>
+          <t>Ligabue, P. M., Brandão, A. A. F., Peres, S. M., Cozman, F. G. And Pirozelli, P. “</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Improving Zero-shot Inference With Unsuper Vised Key-sentences Extraction. In Ieee 17th International Conference On Semantic Computing (icsc), 2023. P. 107-113.</t>
+          <t>Data Augmentation Techniques In Natural Language Processing. Applied Soft Computing, V. 132, P. 109803, 2023.</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Pellicer, L. F. A. O., Costa, A. H. R. “</t>
+          <t>Pellicer, L. F. A. O., Ferreira, T. M., Costa, A. H. R. “</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>A Method To Build Datasets Of Corporate Emails In Portuguese. Data, V. 8, P. 127, 2023.</t>
+          <t>Improving Zero-shot Inference With Unsuper Vised Key-sentences Extraction. In Ieee 17th International Conference On Semantic Computing (icsc), 2023. P. 107-113.</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Uematsu, A. A. M. G. And Brandão, A. A. F. Emailme: “</t>
+          <t>Pellicer, L. F. A. O., Costa, A. H. R. “</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Gubs Criterion: Arbitrary Trade-offs Between Cost And Probability-to-goal In Stochastic Planning Based On Expected Utility Theory. Artificial Intelligence, V. 316, P. 103848, 2023.</t>
+          <t>A Method To Build Datasets Of Corporate Emails In Portuguese. Data, V. 8, P. 127, 2023.</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Crispino, G. N., Freire, V. And Delgado, K. V. “</t>
+          <t>Uematsu, A. A. M. G. And Brandão, A. A. F. Emailme: “</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Coordination Within Conversational Agents With Multiple Sources. 20th Encontro Nacional de Inteligência Artificial e Computacional (eniac 2023). (accepted)</t>
+          <t>Gubs Criterion: Arbitrary Trade-offs Between Cost And Probability-to-goal In Stochastic Planning Based On Expected Utility Theory. Artificial Intelligence, V. 316, P. 103848, 2023.</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Matos, V. B., Grava, R., Tavares, R., José, M. M., Pirozelli, P., Brandão, A. A. F., Peres, S. M. And Cozman, F. G. “</t>
+          <t>Crispino, G. N., Freire, V. And Delgado, K. V. “</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -4780,12 +4780,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Allocating Dynamic And Finite Resources To A Set Of Known Tasks. 12th Brazilian Conference On Intelligent Systems (bracis 2023). (accepted)</t>
+          <t>Coordination Within Conversational Agents With Multiple Sources. 20th Encontro Nacional de Inteligência Artificial e Computacional (eniac 2023). (accepted)</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>da Silva, J. V.. Peres, S. M., Cordeiro, D. And Freire. V. “</t>
+          <t>Matos, V. B., Grava, R., Tavares, R., José, M. M., Pirozelli, P., Brandão, A. A. F., Peres, S. M. And Cozman, F. G. “</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -4805,12 +4805,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>D. D. Assessing Good, Bad And Ugly Arguments Generated By Chatgpt: A New Dataset, Its Methodology And Associated Tasks. Pia2023: 22nd Epia Conference On Artificial Intelligence. (accepted)</t>
+          <t>Allocating Dynamic And Finite Resources To A Set Of Known Tasks. 12th Brazilian Conference On Intelligent Systems (bracis 2023). (accepted)</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Rocha, V. H., Pirozelli, P., Silveira, I. C., Cozman, F. And Mau´ A, “</t>
+          <t>da Silva, J. V.. Peres, S. M., Cordeiro, D. And Freire. V. “</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -4830,12 +4830,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Alpha-mcmp: Trade-offs Between Probability And Cost In Ssps With The Mcmp Criterion. 12th Brazilian Conference On Intelligent Systems (bracis 2023). (accepted)</t>
+          <t>D. D. Assessing Good, Bad And Ugly Arguments Generated By Chatgpt: A New Dataset, Its Methodology And Associated Tasks. Pia2023: 22nd Epia Conference On Artificial Intelligence. (accepted)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Crispino, G., Freire, V., Delgado, K. V. “</t>
+          <t>Rocha, V. H., Pirozelli, P., Silveira, I. C., Cozman, F. And Mau´ A, “</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>A New Benchmark for Automatic Essay Scoring in Portuguese. In Proceedings of the 16th International Conference on Computational Processing of Portuguese, 2024.</t>
+          <t>Alpha-mcmp: Trade-offs Between Probability And Cost In Ssps With The Mcmp Criterion. 12th Brazilian Conference On Intelligent Systems (bracis 2023). (accepted)</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Silveira, I.C., Barbosa, B., Maua, D. D.</t>
+          <t>Crispino, G., Freire, V., Delgado, K. V. “</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -4880,12 +4880,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Applying a Context-based Method to Build a Knowledge Graph for the Blue Amazon. In the Data Intelligence MIT Press Direct 2024, 2024. v.6. p.64-103. https://doi.org/10. 1162/dint_a_00223</t>
+          <t>A New Benchmark for Automatic Essay Scoring in Portuguese. In Proceedings of the 16th International Conference on Computational Processing of Portuguese, 2024.</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Ligabue, P. M.; Brandao, A. A. F.; Peres, S. M.; Cozman, F. G.; Pirozelli, P.</t>
+          <t>Silveira, I.C., Barbosa, B., Maua, D. D.</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>A strategy for interpreting and visualizing the results of matrixtrifactorization-based coclustering algorithms. In Proceedings of the 20th Nacional Meeting on Artificial and Computational Intelligence, ENIAC 2023, Belo Horizonte, 2023.p. 839-853. ISSN 2763-9061. https://doi.org/10.5753/eniac</t>
+          <t>Applying a Context-based Method to Build a Knowledge Graph for the Blue Amazon. In the Data Intelligence MIT Press Direct 2024, 2024. v.6. p.64-103. https://doi.org/10. 1162/dint_a_00223</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Castro, A. B. R.; Peres, S. M.; Freitas Junior, W. L.; Pirozelli, P.; Cozman, F. G.; Brandao, A. A. F.</t>
+          <t>Ligabue, P. M.; Brandao, A. A. F.; Peres, S. M.; Cozman, F. G.; Pirozelli, P.</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -4930,12 +4930,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Trade-Offs Between Probability and Cost in SSPs with the MCMP Criterion. In Proceedings of the 12th Brazilian Conference on Intelligent Systems BRACIS 2023, Belo Horizonte, 2023. Part I. v.14195. p. 112–127. https://doi.org/10.1007/978-3-031-45368-7_8 79</t>
+          <t>A strategy for interpreting and visualizing the results of matrixtrifactorization-based coclustering algorithms. In Proceedings of the 20th Nacional Meeting on Artificial and Computational Intelligence, ENIAC 2023, Belo Horizonte, 2023.p. 839-853. ISSN 2763-9061. https://doi.org/10.5753/eniac</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Crispino, G. N.; Freire, V.; Delgado, K. V. Alpha-MCMP:</t>
+          <t>Castro, A. B. R.; Peres, S. M.; Freitas Junior, W. L.; Pirozelli, P.; Cozman, F. G.; Brandao, A. A. F.</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Coordination within Conversational Agents with Multiple Sources. In Proceedings of the 20th Nacional Meeting on Artificial and Computational Intelligence, ENIAC 2023, Belo Horizonte, 2023. p. 939-953. ISSN 2763-9061. https://doi.org/10.5753/eniac.2023.234533</t>
+          <t>Trade-Offs Between Probability and Cost in SSPs with the MCMP Criterion. In Proceedings of the 12th Brazilian Conference on Intelligent Systems BRACIS 2023, Belo Horizonte, 2023. Part I. v.14195. p. 112–127. https://doi.org/10.1007/978-3-031-45368-7_8 79</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Matos, V. B.; Grava, R.; Tavares, R.; Jose, M. M.; Pirozelli, P.; Brand ao, A. A. F.; Peres, S. M.; Cozman, F. G.</t>
+          <t>Crispino, G. N.; Freire, V.; Delgado, K. V. Alpha-MCMP:</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -4980,12 +4980,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Assessing Logical Reasoning Capabilities of Encoder-Only Transformer Models. arXiv preprint arXiv:2312.11720, 2023. https://doi.org/10.48550/arXiv.2312.11720</t>
+          <t>Coordination within Conversational Agents with Multiple Sources. In Proceedings of the 20th Nacional Meeting on Artificial and Computational Intelligence, ENIAC 2023, Belo Horizonte, 2023. p. 939-953. ISSN 2763-9061. https://doi.org/10.5753/eniac.2023.234533</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Pirozelli, P.; Jose, M. M.; Parenti Filho, T. P.; Brand ao, A. A. F.; Cozman, F. G.</t>
+          <t>Matos, V. B.; Grava, R.; Tavares, R.; Jose, M. M.; Pirozelli, P.; Brand ao, A. A. F.; Peres, S. M.; Cozman, F. G.</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Assessing Good, Bad and Ugly Arguments Generated by ChatGPT: a New Dataset, its Methodology and Associated Tasks. In Proceedings of the 22nd EPIA Conference on Artificial Intelligence – Progress in Artificial Intelligence EPIA 2023, Faial Island, Azores, 2023. v. 14115. p. 428–440. https://doi.</t>
+          <t>Assessing Logical Reasoning Capabilities of Encoder-Only Transformer Models. arXiv preprint arXiv:2312.11720, 2023. https://doi.org/10.48550/arXiv.2312.11720</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Rocha, V. H. N., Silveira, I. C., Pirozelli, P., Maua, D. D., Cozman, F. G.</t>
+          <t>Pirozelli, P.; Jose, M. M.; Parenti Filho, T. P.; Brand ao, A. A. F.; Cozman, F. G.</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -5030,12 +5030,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Allocating Dynamic and Finite Resources to a Set of Known Tasks. In Proceedings of 12th Brazilian Conference on Intelligent Systems BRACIS 2023, Belo Horizonte, 2023. v.14195 p. 193–208. https://doi.org/10.1007/978-3-031-45368-7_13</t>
+          <t>Assessing Good, Bad and Ugly Arguments Generated by ChatGPT: a New Dataset, its Methodology and Associated Tasks. In Proceedings of the 22nd EPIA Conference on Artificial Intelligence – Progress in Artificial Intelligence EPIA 2023, Faial Island, Azores, 2023. v. 14115. p. 428–440. https://doi.</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Silva, J. V.; Peres, S. M.; Cordeiro, D. A.; Freire, V.</t>
+          <t>Rocha, V. H. N., Silveira, I. C., Pirozelli, P., Maua, D. D., Cozman, F. G.</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>A Method to Build Datasets of Corporate Emails in Portuguese. Data MDPI, 2023. V.8 P.127. doi: 10.3390/data8080127</t>
+          <t>Allocating Dynamic and Finite Resources to a Set of Known Tasks. In Proceedings of 12th Brazilian Conference on Intelligent Systems BRACIS 2023, Belo Horizonte, 2023. v.14195 p. 193–208. https://doi.org/10.1007/978-3-031-45368-7_13</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Uematsu, A. A. M. G.; Brandao, A. A. F. eMailMe:</t>
+          <t>Silva, J. V.; Peres, S. M.; Cordeiro, D. A.; Freire, V.</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>The high-speed evolution of NLP, and where it hits a wall. Revista da UFMG, v. 30, p. 1, 2023. https://doi.org/10.35699/ 2965-6931.2023.47510</t>
+          <t>A Method to Build Datasets of Corporate Emails in Portuguese. Data MDPI, 2023. V.8 P.127. doi: 10.3390/data8080127</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Cozman, F. G., Neri, H. Pay Attention:</t>
+          <t>Uematsu, A. A. M. G.; Brandao, A. A. F. eMailMe:</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Markov conditions and factorization in logical credal networks. In: Symposium on Imprecise Probability: Theories and Applications, 2023. v. 215. p. 130-140. https://proceedings.mlr.press/v215/cozman23a.html</t>
+          <t>The high-speed evolution of NLP, and where it hits a wall. Revista da UFMG, v. 30, p. 1, 2023. https://doi.org/10.35699/ 2965-6931.2023.47510</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Cozman, F. G..</t>
+          <t>Cozman, F. G., Neri, H. Pay Attention:</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Who Killed the Winograd Schema Challenge?. In: 12th Brazilian Conference on Intelligent Systems BRACIS, 2023. v. 3. p. 211-225. https://doi.org/10.1007/978-3-031-45392-2_14</t>
+          <t>Markov conditions and factorization in logical credal networks. In: Symposium on Imprecise Probability: Theories and Applications, 2023. v. 215. p. 130-140. https://proceedings.mlr.press/v215/cozman23a.html</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Neri, H., Cozman, F. G.</t>
+          <t>Cozman, F. G..</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>A Comprehensive Differentiable Probabilistic Answer Set Programming Environment For Neurosymbolic Learning and Reasoning. In: Workshop on Knowledge and Logical Reasoning in the Era of Data-driven Learning Workshop at ICML2023, 2023. p. 1-11. https://doi.org/10.48550/arXiv.2308.02944</t>
+          <t>Who Killed the Winograd Schema Challenge?. In: 12th Brazilian Conference on Intelligent Systems BRACIS, 2023. v. 3. p. 211-225. https://doi.org/10.1007/978-3-031-45392-2_14</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Geh, R. L., Gonçalves, J. L., Silveira, I. C., Maua, D. D., Cozman, F. G. dPASP:</t>
+          <t>Neri, H., Cozman, F. G.</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Analise de Senti- mentos de Textos em Portugues do Mercado Financeiro. In: Brazilian Workshop on Artificial Intelligence in Finance, BWAIF 2023, v. 1., 2023, p. 144-155.</t>
+          <t>A Comprehensive Differentiable Probabilistic Answer Set Programming Environment For Neurosymbolic Learning and Reasoning. In: Workshop on Knowledge and Logical Reasoning in the Era of Data-driven Learning Workshop at ICML2023, 2023. p. 1-11. https://doi.org/10.48550/arXiv.2308.02944</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Santos, L. L., Bianchi, R. A. C., Costa, A. H. R. FinBERT-PT-BR:</t>
+          <t>Geh, R. L., Gonçalves, J. L., Silveira, I. C., Maua, D. D., Cozman, F. G. dPASP:</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -5201,16 +5201,16 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Enhancing The Forecast Of Ocean Physical Variables Through Physics Informed Machine Learning In The Santos Estuary, Brazil." In Oceans 2022-chennai, Pp. 1-7. Ieee</t>
+          <t>Analise de Senti- mentos de Textos em Portugues do Mercado Financeiro. In: Brazilian Workshop on Artificial Intelligence in Finance, BWAIF 2023, v. 1., 2023, p. 144-155.</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Moreno, Felipe M., Luiz A. Schiaveto Neto, Fabio G. Cozman, Marcelo Dottori, And Eduardo A. Tannuri</t>
+          <t>Santos, L. L., Bianchi, R. A. C., Costa, A. H. R. FinBERT-PT-BR:</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Tracking Environmental Policy Changes In The Brazilian Federal Official Gazette. In: Computational Processing Of The Portuguese Language. Propor 2022. Lecture Notes In Computer Science(), Vol 13208, Pp. 256-266. Springer, Cham https://doi.org/10.1007/978-3-030-98305-5_24</t>
+          <t>Enhancing The Forecast Of Ocean Physical Variables Through Physics Informed Machine Learning In The Santos Estuary, Brazil." In Oceans 2022-chennai, Pp. 1-7. Ieee</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Cação, F.n., Costa, A.h.r., Unterstell, N., Yonaha, L., Stec, T., Ishisaki, F.</t>
+          <t>Moreno, Felipe M., Luiz A. Schiaveto Neto, Fabio G. Cozman, Marcelo Dottori, And Eduardo A. Tannuri</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>“automatic Lustering Of Metocean Conditions In The Brazilian Coast.” In 41st Ocean, Offshore And Arctic Engineering Conference (omae), Omae2022-78608, Pp. 1-10,</t>
+          <t>Tracking Environmental Policy Changes In The Brazilian Federal Official Gazette. In: Computational Processing Of The Portuguese Language. Propor 2022. Lecture Notes In Computer Science(), Vol 13208, Pp. 256-266. Springer, Cham https://doi.org/10.1007/978-3-030-98305-5_24</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Moreno, Felipe Marino Moreno, Cozman, Fabio Gagliardi Cozman, Tannuri, Eduardo Aoun</t>
+          <t>Cação, F.n., Costa, A.h.r., Unterstell, N., Yonaha, L., Stec, T., Ishisaki, F.</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Leveraging Zero-shot Text Classification By Topic Modeling. In: Computational Processing Of The Portuguese Language. Propor 2022. Lecture Notes In Computer Science, Vol 13208, Pp. 125-136. Springer, Cham. 2022 https://doi.org/10.1007/978-3-030-98305-5_12</t>
+          <t>“automatic Lustering Of Metocean Conditions In The Brazilian Coast.” In 41st Ocean, Offshore And Arctic Engineering Conference (omae), Omae2022-78608, Pp. 1-10,</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Alcoforado, A. Et Al. Zeroberto</t>
+          <t>Moreno, Felipe Marino Moreno, Cozman, Fabio Gagliardi Cozman, Tannuri, Eduardo Aoun</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Integrating Question Answering And Text-to-sql In Portuguese. In: Computational Processing Of The Portuguese Language. Propor 2022. Lecture Notes In Computer Science, Vol 13208, Pp. 278-287, Springer, Cham, 2022 https://doi.org/10.1007/978-3-030- 98305-5_26</t>
+          <t>Leveraging Zero-shot Text Classification By Topic Modeling. In: Computational Processing Of The Portuguese Language. Propor 2022. Lecture Notes In Computer Science, Vol 13208, Pp. 125-136. Springer, Cham. 2022 https://doi.org/10.1007/978-3-030-98305-5_12</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>José, M.m., José, M.a., Mauá, D.d., Cozman, F.g.</t>
+          <t>Alcoforado, A. Et Al. Zeroberto</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>"ptt5-paraphraser: Diversity And Meaning Fidelity In Automatic Portuguese Paraphrasing."in International Conference On Computational Processing Of The Portuguese Language, Pp. 299-309. Springer, Cham, 2022.</t>
+          <t>Integrating Question Answering And Text-to-sql In Portuguese. In: Computational Processing Of The Portuguese Language. Propor 2022. Lecture Notes In Computer Science, Vol 13208, Pp. 278-287, Springer, Cham, 2022 https://doi.org/10.1007/978-3-030- 98305-5_26</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Pellicer, Lucas Francisco Amaral Orosco, Paulo Pirozelli, Anna Helena Reali Costa, And Alexandre Inoue</t>
+          <t>José, M.m., José, M.a., Mauá, D.d., Cozman, F.g.</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>"hyperintensional Partial Meet Contractions." In Proceedings Of The 19th International Conference On Principles Of Knowledge Representation And Reasoning (kr’22).</t>
+          <t>"ptt5-paraphraser: Diversity And Meaning Fidelity In Automatic Portuguese Paraphrasing."in International Conference On Computational Processing Of The Portuguese Language, Pp. 299-309. Springer, Cham, 2022.</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Souza, Marlo, And Wassermann, Renata</t>
+          <t>Pellicer, Lucas Francisco Amaral Orosco, Paulo Pirozelli, Anna Helena Reali Costa, And Alexandre Inoue</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>“repairing Ontologies Via Kernel Pseudo-contraction.” In Proceedings Of The 19th International Conference On Principles Of Knowledge Representation And Reasoning (kr’22).</t>
+          <t>"hyperintensional Partial Meet Contractions." In Proceedings Of The 19th International Conference On Principles Of Knowledge Representation And Reasoning (kr’22).</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>"a Physics-informed Neural Network To Model Port Channels" In Ai: Modeling Oceans And Climate Change,</t>
+          <t>“repairing Ontologies Via Kernel Pseudo-contraction.” In Proceedings Of The 19th International Conference On Principles Of Knowledge Representation And Reasoning (kr’22).</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Mathias, Marlon S., Marcel R. de Barros, Jefferson F. Coelho, Lucas P. de Freitas, Felipe M. Moreno, Caio</t>
+          <t>Souza, Marlo, And Wassermann, Renata</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Modeling Oceanic Variables With Dynamic Graph Neural Networks" In Ai: Modeling Oceans And Climate Change, 2022</t>
+          <t>"a Physics-informed Neural Network To Model Port Channels" In Ai: Modeling Oceans And Climate Change,</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Neeto, Caio F. D., Marcel R. de Barros, Jefferson F. Coelho, Lucas P. de Freitas, Felipe M. Moreno, Marlon S. Mathias, Marcelo Dottori, Fabio G. Cozman, Anna H. R. Costa, Edson S. Gomi, Eduardo A. Tannuri.</t>
+          <t>Mathias, Marlon S., Marcel R. de Barros, Jefferson F. Coelho, Lucas P. de Freitas, Felipe M. Moreno, Caio</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>"enhancing Oceanic Variables Forecast In The Santos Channel By Estimating Model Error With Random Forests" In Ai: Modeling Oceans And Climate Change, 2022</t>
+          <t>Modeling Oceanic Variables With Dynamic Graph Neural Networks" In Ai: Modeling Oceans And Climate Change, 2022</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Moreno, Felipe M., Caio F. D. Netto, Marcel R. de Barros, Jefferson F. Coelho, Lucas P. de Freitas, Marlon S. Mathias, Luiz A. Schiaveto Neto, Marcelo Dottori, Fabio G. Cozman, Anna H. R. Costa, Edson S. Gomi, Eduardo A. Tannuri</t>
+          <t>Neeto, Caio F. D., Marcel R. de Barros, Jefferson F. Coelho, Lucas P. de Freitas, Felipe M. Moreno, Marlon S. Mathias, Marcelo Dottori, Fabio G. Cozman, Anna H. R. Costa, Edson S. Gomi, Eduardo A. Tannuri.</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Augmenting A Physics-informed Neural Network For The 2d Burgers Equation By Addition Of Solution Data Points”. In: Brazilian Conference On Intelligent Systems, Bracis 2022, Pp.388–401. Doi:10.1007/978-3-031-21689-3 28, Campinas, Brasil, 2022.</t>
+          <t>"enhancing Oceanic Variables Forecast In The Santos Channel By Estimating Model Error With Random Forests" In Ai: Modeling Oceans And Climate Change, 2022</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Mathias, M.s.; De Almeida, W.p.; Barros, M.r.; Coelho, J.f.; De Freitas, L.p.; Moreno, F.m.; Netto, C.f.d.; Cozman, F.g.; Reali Costa, A.h.; Tannuri, E.a.; Gomi, E.s.; Dottori, M.. ”</t>
+          <t>Moreno, Felipe M., Caio F. D. Netto, Marcel R. de Barros, Jefferson F. Coelho, Lucas P. de Freitas, Marlon S. Mathias, Luiz A. Schiaveto Neto, Marcelo Dottori, Fabio G. Cozman, Anna H. R. Costa, Edson S. Gomi, Eduardo A. Tannuri</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>A Knowledge Graph For The Blue Amazon. In Proceedings Of 13th Ieee International Conference On Knowledge Graph - Ickg 2022, 2022, Online, P. 1-8.</t>
+          <t>Augmenting A Physics-informed Neural Network For The 2d Burgers Equation By Addition Of Solution Data Points”. In: Brazilian Conference On Intelligent Systems, Bracis 2022, Pp.388–401. Doi:10.1007/978-3-031-21689-3 28, Campinas, Brasil, 2022.</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Ligabue, P. M., Brand˜ao, A. A. F., Peres, S. M., Cozman, F. G. And Pirozelli, P. Blabkg: “</t>
+          <t>Mathias, M.s.; De Almeida, W.p.; Barros, M.r.; Coelho, J.f.; De Freitas, L.p.; Moreno, F.m.; Netto, C.f.d.; Cozman, F.g.; Reali Costa, A.h.; Tannuri, E.a.; Gomi, E.s.; Dottori, M.. ”</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>To Answer Or Not To Answer? Filtering Questions For Qa Systems. In Proceedings Of 11th Brazilian Conference On Intelligent Systems (bracis 2022), 2022, Campinas, V. Ii. P. 464-478.</t>
+          <t>A Knowledge Graph For The Blue Amazon. In Proceedings Of 13th Ieee International Conference On Knowledge Graph - Ickg 2022, 2022, Online, P. 1-8.</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Pirozelli, P., Brandão, A. A. F., Peres, S. M. And Cozman, F. G. “</t>
+          <t>Ligabue, P. M., Brand˜ao, A. A. F., Peres, S. M., Cozman, F. G. And Pirozelli, P. Blabkg: “</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Natural Language At A Crossroads: Formal And Probabilistic Approaches In Philosophy And Computer Sicence. Manuscrito, V. 45, P. 50-81, 2022.</t>
+          <t>To Answer Or Not To Answer? Filtering Questions For Qa Systems. In Proceedings Of 11th Brazilian Conference On Intelligent Systems (bracis 2022), 2022, Campinas, V. Ii. P. 464-478.</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Camara, I. C. E. S., Pirozelli, P. “</t>
+          <t>Pirozelli, P., Brandão, A. A. F., Peres, S. M. And Cozman, F. G. “</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -5576,16 +5576,16 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Epistemic Argumentation With Conditional Probabilities And Labeling Constraints." In International Symposium On Imprecise Probability: Theories And Applications, Pp. 100-109. Pmlr</t>
+          <t>Natural Language At A Crossroads: Formal And Probabilistic Approaches In Philosophy And Computer Sicence. Manuscrito, V. 45, P. 50-81, 2022.</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>De Bona, Glauber, Victor Hugo Nascimento Rocha, And Fabio Cozman</t>
+          <t>Camara, I. C. E. S., Pirozelli, P. “</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -5605,17 +5605,17 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Intelligent Trading Systems: A Sentiment-aware Reinforcement Learning Approach." In Proceedings Of The Second Acm International Conference On Ai In Finance, Pp. 1-9. [1 Citation]</t>
+          <t>Epistemic Argumentation With Conditional Probabilities And Labeling Constraints." In International Symposium On Imprecise Probability: Theories And Applications, Pp. 100-109. Pmlr</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Paiva, Francisco Caio Lima, Leonardo Kanashiro Felizardo, Reinaldo Augusto da Costa Bianchi, And Anna Helena Reali Costa</t>
+          <t>De Bona, Glauber, Victor Hugo Nascimento Rocha, And Fabio Cozman</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Citação</t>
+          <t>Publicação</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Answering Questions In Portuguese About The Brazilian Environment. In: Britto, A., Valdivia Delgado, K. (eds) Intelligent Systems. Bracis 2021. Lecture Notes In Computer Science, Vol 13074. Springer, Cham, 2021.[2 Citação] https://doi.org/10.1007/978-3-030-91699-2_29</t>
+          <t>Intelligent Trading Systems: A Sentiment-aware Reinforcement Learning Approach." In Proceedings Of The Second Acm International Conference On Ai In Finance, Pp. 1-9. [1 Citation]</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Cação, F.n., José, M.m., Oliveira, A.s., Spindola, S., Costa, A.h.r., Cozman, F.g. Deepagé</t>
+          <t>Paiva, Francisco Caio Lima, Leonardo Kanashiro Felizardo, Reinaldo Augusto da Costa Bianchi, And Anna Helena Reali Costa</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -5655,17 +5655,17 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Sea State Estimation With Neural Networks Based On The Motion Of A Moored Fpso Subjected To Campos Basin Metocean Conditions." In Brazilian Conference On Intelligent Systems, Pp. 294-308. Springer, Cham,</t>
+          <t>Answering Questions In Portuguese About The Brazilian Environment. In: Britto, A., Valdivia Delgado, K. (eds) Intelligent Systems. Bracis 2021. Lecture Notes In Computer Science, Vol 13074. Springer, Cham, 2021.[2 Citação] https://doi.org/10.1007/978-3-030-91699-2_29</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Bisinotto, Gustavo A., Lucas P. Cotrim, Fabio Gagliardi Cozman, And Eduardo A. Tannuri</t>
+          <t>Cação, F.n., José, M.m., Oliveira, A.s., Spindola, S., Costa, A.h.r., Cozman, F.g. Deepagé</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Publicação</t>
+          <t>Citação</t>
         </is>
       </c>
     </row>
@@ -5680,12 +5680,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>"interpretability Of Attention Mechanisms In A Portuguese-based Question Answering System About The Blue Amazon." In Anais do Xviii Encontro Nacional de Inteligência Artificial e Computacional, 775-786. Sbc, 2021</t>
+          <t>Sea State Estimation With Neural Networks Based On The Motion Of A Moored Fpso Subjected To Campos Basin Metocean Conditions." In Brazilian Conference On Intelligent Systems, Pp. 294-308. Springer, Cham,</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Spindola, Stefano, Marcos Menon José, André Seidel Oliveira, Flávio Nakasato Cação, And Fábio Gagliardi Cozman</t>
+          <t>Bisinotto, Gustavo A., Lucas P. Cotrim, Fabio Gagliardi Cozman, And Eduardo A. Tannuri</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -5705,17 +5705,17 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>"mrat-sql+ Gap: A Portuguese Text-to-sql Transformer." In Brazilian Conference On Intelligent Systems, Pp. 511-525. Springer, Cham, 2021. [1 Citation]</t>
+          <t>"interpretability Of Attention Mechanisms In A Portuguese-based Question Answering System About The Blue Amazon." In Anais do Xviii Encontro Nacional de Inteligência Artificial e Computacional, 775-786. Sbc, 2021</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>José, Marcelo Archanjo, And Fabio Gagliardi Cozman</t>
+          <t>Spindola, Stefano, Marcos Menon José, André Seidel Oliveira, Flávio Nakasato Cação, And Fábio Gagliardi Cozman</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Citação</t>
+          <t>Publicação</t>
         </is>
       </c>
     </row>
@@ -5730,17 +5730,17 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>"inteligência Artificial"</t>
+          <t>"mrat-sql+ Gap: A Portuguese Text-to-sql Transformer." In Brazilian Conference On Intelligent Systems, Pp. 511-525. Springer, Cham, 2021. [1 Citation]</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Cozman, Fabio G., Guilherme Ary Plonski, And Hugo Neri</t>
+          <t>José, Marcelo Archanjo, And Fabio Gagliardi Cozman</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Publicação</t>
+          <t>Citação</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Pirá A Bilingual Portuguese-english Dataset For Question-answering About The Ocean. In: Cikm '21: Proceedings Of The 30th Acm International Conference On Information &amp; Knowledge Management, Pp. 4544–4553, 2021 https://doi.org/10.1145/3459637.3482012012</t>
+          <t>"inteligência Artificial"</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Paschoal, André F. A.; Pirozelli, Paulo; Freire, Valdinei; Delgado, Karina V.; Peres, Sarajane M.; José, Marcos M.; Nakasato, Flávio; Oliveira, André S.; Brandão, Anarosa A. F.; Costa, Anna H. R.; Cozman, Fabio G.</t>
+          <t>Cozman, Fabio G., Guilherme Ary Plonski, And Hugo Neri</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -5772,25 +5772,25 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>MClimate</t>
+          <t>KEML</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Agriculture and Livestock Metadata Elements Set Almes Core [Data set]. Zenodo.</t>
+          <t>Pirá A Bilingual Portuguese-english Dataset For Question-answering About The Ocean. In: Cikm '21: Proceedings Of The 30th Acm International Conference On Information &amp; Knowledge Management, Pp. 4544–4553, 2021 https://doi.org/10.1145/3459637.3482012012</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Filipi Miranda Soares, Fernando Elias Corrêa;, Moreira, D. de A., Pignatari Drucker, D., Braghetto, K. R., Botazzo Alexandre Cláudio Botazzo Delbem C., Ferreira Pires, L., Bonino da Silva Santos, L. O., &amp; Antonio Mauro Saraiva; 2024</t>
+          <t>Paschoal, André F. A.; Pirozelli, Paulo; Freire, Valdinei; Delgado, Karina V.; Peres, Sarajane M.; José, Marcos M.; Nakasato, Flávio; Oliveira, André S.; Brandão, Anarosa A. F.; Costa, Anna H. R.; Cozman, Fabio G.</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Outros (relatórios Técnicos, Capítulos de Livros Etc.)</t>
+          <t>Publicação</t>
         </is>
       </c>
     </row>
@@ -5805,12 +5805,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Agriculture Product Types Ontology APTO [Data set]. Zenodo. https://doi.org/10.5281/zenodo.13271285</t>
+          <t>Agriculture and Livestock Metadata Elements Set Almes Core [Data set]. Zenodo.</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Filipi Miranda Soares, Ferreira Pires, L., Olavo Bonino da Silva Santos, L., Fernando Elias Corrêa;, de Abreu Moreira, D., Pignatari Drucker, D., Braghetto, K. R., Botazzo Alexandre Cláudio Botazzo Delbem C., &amp; Mauro Saraiva, A. 2024</t>
+          <t>Filipi Miranda Soares, Fernando Elias Corrêa;, Moreira, D. de A., Pignatari Drucker, D., Braghetto, K. R., Botazzo Alexandre Cláudio Botazzo Delbem C., Ferreira Pires, L., Bonino da Silva Santos, L. O., &amp; Antonio Mauro Saraiva; 2024</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>A LLM-Based Solution for Managing Species Names in Ontologies. Submitted to Scientific Data currently under review</t>
+          <t>Agriculture Product Types Ontology APTO [Data set]. Zenodo. https://doi.org/10.5281/zenodo.13271285</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Ontology Evaluation through User Experience UX Metrics: the application of the Tree Testing Protocol to evaluate an ontology of types. Under review by the authors.</t>
+          <t>A LLM-Based Solution for Managing Species Names in Ontologies. Submitted to Scientific Data currently under review</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Agricultural Biodiversity Standards, Best Practices and Guidelines Recommendations.</t>
+          <t>Ontology Evaluation through User Experience UX Metrics: the application of the Tree Testing Protocol to evaluate an ontology of types. Under review by the authors.</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Drucker, D., Salim, J. A., Poelen, J., Filipi Miranda Soares, Gonzalez-Vaquero, R. A., Ollerton, J., Devoto, M., Runzel, M., Robinson, D., Kasina, M., Taliga, C., Parr, C., Cox-Foster, ¨ 110 D., Hill, E., Maues, M. M., Antonio Mauro Saraiva Kayna Agostini;, Carvalheiro, L. G., Bergamo, P., ... Trekels, M. 2024 WorldFAIR D10.2</t>
+          <t>Filipi Miranda Soares, Ferreira Pires, L., Olavo Bonino da Silva Santos, L., Fernando Elias Corrêa;, de Abreu Moreira, D., Pignatari Drucker, D., Braghetto, K. R., Botazzo Alexandre Cláudio Botazzo Delbem C., &amp; Mauro Saraiva, A. 2024</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Agricultural biodiversity FAIR data assessment rubrics.</t>
+          <t>Agricultural Biodiversity Standards, Best Practices and Guidelines Recommendations.</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Pignatari Drucker, D., Salim, J. A., Poelen, J., Filipi Miranda Soares, Gonzalez-Vaquero, R. A., Devoto, M., Ollerton, J., Kasina, M., Carvalheiro, L. G., Bergamo, P. J., Alves, D. A., Varassin, I., Tinoco, C. F., Runzel, M., Robinson, D., Cardona-Duque, J., Id ¨ arraga, M., Agudelo-Zapata, M. C., Herrera, E. M., ... Saraiva, A. 2024 WorldFAIR D10.3</t>
+          <t>Drucker, D., Salim, J. A., Poelen, J., Filipi Miranda Soares, Gonzalez-Vaquero, R. A., Ollerton, J., Devoto, M., Runzel, M., Robinson, D., Kasina, M., Taliga, C., Parr, C., Cox-Foster, ¨ 110 D., Hill, E., Maues, M. M., Antonio Mauro Saraiva Kayna Agostini;, Carvalheiro, L. G., Bergamo, P., ... Trekels, M. 2024 WorldFAIR D10.2</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Resilience assessment of critical infrastructures using dynamic Bayesian networks and evidence propagation. Reliability Engineering &amp; System Safety, v. 241, p. 109691, 2024</t>
+          <t>Agricultural biodiversity FAIR data assessment rubrics.</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>CAETANO, Henrique de Oliveira; DESUO, Luiz; FOGLIATTO, Matheus SS; MACIEL, Carlos D.</t>
+          <t>Pignatari Drucker, D., Salim, J. A., Poelen, J., Filipi Miranda Soares, Gonzalez-Vaquero, R. A., Devoto, M., Ollerton, J., Kasina, M., Carvalheiro, L. G., Bergamo, P. J., Alves, D. A., Varassin, I., Tinoco, C. F., Runzel, M., Robinson, D., Cardona-Duque, J., Id ¨ arraga, M., Agudelo-Zapata, M. C., Herrera, E. M., ... Saraiva, A. 2024 WorldFAIR D10.3</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Intelligent Resource Allocation in Power Grids: Leveraging Variable Neighborhood Search for Optimal Switch Allocation. In: 2024 IEEE International Conference on Evolving and Adaptive Intelligent Systems EAIS IEEE, 2024. p. 1-8.</t>
+          <t>Resilience assessment of critical infrastructures using dynamic Bayesian networks and evidence propagation. Reliability Engineering &amp; System Safety, v. 241, p. 109691, 2024</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>CAETANO, Henrique de Oliveira; FOGLIATTO, Matheus de Souza Sant’Anna; DESUO´ NETO, Luiz; MACIEL, Carlos Dias; AIELLO, Marco et al.</t>
+          <t>CAETANO, Henrique de Oliveira; DESUO, Luiz; FOGLIATTO, Matheus SS; MACIEL, Carlos D.</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Model to create synthetic Power Distribution Systems. Electric Power Systems Research, v. 235, p. 110706, 2024.</t>
+          <t>Intelligent Resource Allocation in Power Grids: Leveraging Variable Neighborhood Search for Optimal Switch Allocation. In: 2024 IEEE International Conference on Evolving and Adaptive Intelligent Systems EAIS IEEE, 2024. p. 1-8.</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>CAETANO, Henrique de Oliveira; DESUO, Luiz; FOGLIATTO, Matheus de Souza Sant’Anna; RIBEIRO, Vitor P; BALESTIERI, Jose Ant onio P; MACIEL, Carlos D. A Bayesian Hierar- chical</t>
+          <t>CAETANO, Henrique de Oliveira; FOGLIATTO, Matheus de Souza Sant’Anna; DESUO´ NETO, Luiz; MACIEL, Carlos Dias; AIELLO, Marco et al.</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -6001,16 +6001,16 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Unveiling Knowledge Organization Systems’ Artifacts for Digital Agriculture with Lexical Network Analysis. In T. P. Sales, G. Guizzardi, J. Araujo, &amp; J. Borbinha Eds., Advances in Conceptual Modeling: ER 2023 Workshops, CMLS, CMOMM4FAIR, EmpER, JUSMOD, OntoCom, QUAMES, and SmartFood, Lisbon, Por</t>
+          <t>Model to create synthetic Power Distribution Systems. Electric Power Systems Research, v. 235, p. 110706, 2024.</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Soares, F. M, Bergier, I., Coradini, M. C., Ludtke Ferreira, A. P., Ambrosio Telles, ¨ M., Moreira dos Santos Maculan, B. C., Alencar, M. D. C. F., Marques Simao, V. P., Teixeira de Almeida, B., Pignatari Drucker, D., dos Santos Machado Vieira, M., &amp; Serra da Cruz , S. M. 2023</t>
+          <t>CAETANO, Henrique de Oliveira; DESUO, Luiz; FOGLIATTO, Matheus de Souza Sant’Anna; RIBEIRO, Vitor P; BALESTIERI, Jose Ant onio P; MACIEL, Carlos D. A Bayesian Hierar- chical</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Desdobramentos da Implementação da Rede GO FAIR Agro Brasil no Biénio 2021-2023. In: Congresso Brasileiro de Agroinformatica, 2023, Brasil. In: XIV Congresso Brasileiro de Agroin- formatica SBIAGRO, 2023, Natal/RN. Anais. Sociedade Brasileira de Computac¸ ao, 2023. p. 286-293. ISSN 217</t>
+          <t>Unveiling Knowledge Organization Systems’ Artifacts for Digital Agriculture with Lexical Network Analysis. In T. P. Sales, G. Guizzardi, J. Araujo, &amp; J. Borbinha Eds., Advances in Conceptual Modeling: ER 2023 Workshops, CMLS, CMOMM4FAIR, EmpER, JUSMOD, OntoCom, QUAMES, and SmartFood, Lisbon, Por</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Drucker, D.P.; Cruz, S.M.S; Telles, M.A.; Ferreira, A.P.L.; Correa, F.E.; Bertin, P.R.B; Marassi, L.; Aquino, K.; Bezerra, G.; Cruz, P.V.; Soares, F.M..</t>
+          <t>Soares, F. M, Bergier, I., Coradini, M. C., Ludtke Ferreira, A. P., Ambrosio Telles, ¨ M., Moreira dos Santos Maculan, B. C., Alencar, M. D. C. F., Marques Simao, V. P., Teixeira de Almeida, B., Pignatari Drucker, D., dos Santos Machado Vieira, M., &amp; Serra da Cruz , S. M. 2023</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Agriculture-related pollinator data standards use cases report. WorldFAIR Project. https://doi.org/10.5281/zenodo.8176978</t>
+          <t>Desdobramentos da Implementação da Rede GO FAIR Agro Brasil no Biénio 2021-2023. In: Congresso Brasileiro de Agroinformatica, 2023, Brasil. In: XIV Congresso Brasileiro de Agroin- formatica SBIAGRO, 2023, Natal/RN. Anais. Sociedade Brasileira de Computac¸ ao, 2023. p. 286-293. ISSN 217</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Trekels, M., Pignatari Drucker, D., Salim, J. A., Ollerton, J., Poelen, J., Miranda Soares, F., Runzel, M., Kasina, M., Groom, Q. J., &amp; Devoto, M. 2023 WorldFAIR ¨ Project D10.1</t>
+          <t>Drucker, D.P.; Cruz, S.M.S; Telles, M.A.; Ferreira, A.P.L.; Correa, F.E.; Bertin, P.R.B; Marassi, L.; Aquino, K.; Bezerra, G.; Cruz, P.V.; Soares, F.M..</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>A Multilayer System and Optimization Framework for Team Dispatch Towards Service Recovery. IEEE Transactions on Reliability, 2023.</t>
+          <t>Agriculture-related pollinator data standards use cases report. WorldFAIR Project. https://doi.org/10.5281/zenodo.8176978</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>DESUO, Luiz; FOGLIATTO, Matheus SS; CAETANO, Henrique O; MACIEL, Carlos D et al.</t>
+          <t>Trekels, M., Pignatari Drucker, D., Salim, J. A., Ollerton, J., Poelen, J., Miranda Soares, F., Runzel, M., Kasina, M., Groom, Q. J., &amp; Devoto, M. 2023 WorldFAIR ¨ Project D10.1</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Distribution Maintenance Operations and Carbon-Neutral Operation. In: 12th International Workshop on Advances in Cleaner Production IWACP, 2023.</t>
+          <t>A Multilayer System and Optimization Framework for Team Dispatch Towards Service Recovery. IEEE Transactions on Reliability, 2023.</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>DESUO, Luiz; CAETANO, Henrique O.; FOGLIATTO, Matheus S. S.; MACIEL, Carlos D. Power</t>
+          <t>DESUO, Luiz; FOGLIATTO, Matheus SS; CAETANO, Henrique O; MACIEL, Carlos D et al.</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>A stochastic Bayesian artificial intelli- gence framework to assess climatological water balance under missing variables for evapotranspiration estimates. Agronomy, v. 13, n. 12, p. 2970, 2023.</t>
+          <t>Distribution Maintenance Operations and Carbon-Neutral Operation. In: 12th International Workshop on Advances in Cleaner Production IWACP, 2023.</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>RIBEIRO, Vitor P; DESUO NETO, Luiz; MARQUES, Patricia AA; ACHCAR, Jorge A; JUNQUEIRA, Adriano M; CHINATTO Jr, Adilson W; JUNQUEIRA, Cynthia CM; MACIEL, Carlos D; BALESTIERI, Jose Antonio P.</t>
+          <t>DESUO, Luiz; CAETANO, Henrique O.; FOGLIATTO, Matheus S. S.; MACIEL, Carlos D. Power</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -6147,25 +6147,25 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>NLP2</t>
+          <t>MClimate</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>O Corpus DANTEStocks: Uma analise da distribuição de etiquetas morfossintáticas de acordo com o modelo Universal Dependencies. Revista da ABRALIN. To appear</t>
+          <t>A stochastic Bayesian artificial intelli- gence framework to assess climatological water balance under missing variables for evapotranspiration estimates. Agronomy, v. 13, n. 12, p. 2970, 2023.</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Di Felippo, A.; Roman, N.T.; Pardo, T.A.S.; Moura, L.P. 2024</t>
+          <t>RIBEIRO, Vitor P; DESUO NETO, Luiz; MARQUES, Patricia AA; ACHCAR, Jorge A; JUNQUEIRA, Adriano M; CHINATTO Jr, Adilson W; JUNQUEIRA, Cynthia CM; MACIEL, Carlos D; BALESTIERI, Jose Antonio P.</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Revista Nacional</t>
+          <t>Outros (relatórios Técnicos, Capítulos de Livros Etc.)</t>
         </is>
       </c>
     </row>
@@ -6180,12 +6180,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Construções comparativas em portugues e sua anotações ao usando a sintaxe de dependências. Revista da ABRALIN. To appear.</t>
+          <t>O Corpus DANTEStocks: Uma analise da distribuição de etiquetas morfossintáticas de acordo com o modelo Universal Dependencies. Revista da ABRALIN. To appear</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Duran, M.S.; Lopes, L.; Nunes, M.G.V.; Pardo, T.A.S. 2024</t>
+          <t>Di Felippo, A.; Roman, N.T.; Pardo, T.A.S.; Moura, L.P. 2024</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Termos do mercado financeiro: um estudo do corpus DANTEStocks. Tradterm, Vol. 46, pp. 6-30.</t>
+          <t>Construções comparativas em portugues e sua anotações ao usando a sintaxe de dependências. Revista da ABRALIN. To appear.</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Rodrigues, R.; Di Felippo, A.; Roman, N.T.; Semcovici, P.; Souza, J.W.C.; Pardo, T.A.S. 2024</t>
+          <t>Duran, M.S.; Lopes, L.; Nunes, M.G.V.; Pardo, T.A.S. 2024</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>TTS applied to the generation of datasets for automatic speech recognition In Proceedings of the 16th International Conference on Computational Processing of Portuguese Propor 2024, pages 633- 638, Santiago de Compostela, Galicia-Spain.</t>
+          <t>Termos do mercado financeiro: um estudo do corpus DANTEStocks. Tradterm, Vol. 46, pp. 6-30.</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Conferência Internacional</t>
+          <t>Revista Nacional</t>
         </is>
       </c>
     </row>
@@ -6255,12 +6255,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Simple and Fast Automatic Prosodic Segmentation of Brazilian Portuguese Spontaneous Speech In Proceedings of the 16th International Conference on Computational Processing of Portuguese PROPOR 2024, pages 32-44, Santiago de Compostela, Galicia. Association for Computational Linguistics.</t>
+          <t>TTS applied to the generation of datasets for automatic speech recognition In Proceedings of the 16th International Conference on Computational Processing of Portuguese Propor 2024, pages 633- 638, Santiago de Compostela, Galicia-Spain.</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Giovana Meloni Craveiro, Vinicius Gonçalves Santos, Gabriel Jose Pellisser Dalalana, Flaviane R. Fernandes Svartman, and Sandra Maria Aluísio. 2024.</t>
+          <t>Rodrigues, R.; Di Felippo, A.; Roman, N.T.; Semcovici, P.; Souza, J.W.C.; Pardo, T.A.S. 2024</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Portal NURC-SP: Design, Development, and Speech Processing Corpora Resources to Support the Public Dissemination of Portuguese Spoken Language In Proceedings of the 16th International Conference on Computational Processing of Portuguese PROPOR 2024, pages 187</t>
+          <t>Simple and Fast Automatic Prosodic Segmentation of Brazilian Portuguese Spontaneous Speech In Proceedings of the 16th International Conference on Computational Processing of Portuguese PROPOR 2024, pages 32-44, Santiago de Compostela, Galicia. Association for Computational Linguistics.</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Ana Carolina Rodrigues, Alessandra A. Macedo, Arnaldo Candido Jr, Flaviane R. F. Svartman, Giovana M. Craveiro, Marli Quadros Leite, Sandra M. Aluísio, Vinícius G. Santos, and Vinícius M. Garcia. 2024.</t>
+          <t>Giovana Meloni Craveiro, Vinicius Gonçalves Santos, Gabriel Jose Pellisser Dalalana, Flaviane R. Fernandes Svartman, and Sandra Maria Aluísio. 2024.</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Accent Classification is Challenging but Pre-training Helps: a case study with novel Brazilian Portuguese datasets In Proceedings of the 16th International Conference on Computational Processing of Portuguese Propor 2024, pages 364-373, Santiago de Compostela, Galicia/Spain. Association for Computational Linguistics</t>
+          <t>Portal NURC-SP: Design, Development, and Speech Processing Corpora Resources to Support the Public Dissemination of Portuguese Spoken Language In Proceedings of the 16th International Conference on Computational Processing of Portuguese PROPOR 2024, pages 187</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Ariadne Matos, Gustavo Araujo, Arnaldo Candido Junior, and Moacir Ponti. 2024.</t>
+          <t>Ana Carolina Rodrigues, Alessandra A. Macedo, Arnaldo Candido Jr, Flaviane R. F. Svartman, Giovana M. Craveiro, Marli Quadros Leite, Sandra M. Aluísio, Vinícius G. Santos, and Vinícius M. Garcia. 2024.</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Exploring Computational Discernibility of Discourse Domains in Brazilian Portuguese within the Carolina Corpus. In Proceedings of the 16th International Conference on Computational Processing of Portuguese - Vol. 1, Santiago de Compostela, Galicia Spain, pp 255 265, ACL 2024</t>
+          <t>Accent Classification is Challenging but Pre-training Helps: a case study with novel Brazilian Portuguese datasets In Proceedings of the 16th International Conference on Computational Processing of Portuguese Propor 2024, pages 364-373, Santiago de Compostela, Galicia/Spain. Association for Computational Linguistics</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Serras, Felipe Ribas; Sturzeneker, Mariana; de Mello Carpi, Miguel; Palma, Mayara Feliciano; Crespo, Maria Clara Ramos Morales; Costa, Aline Silva; Monte, Vanessa Martins; Namiuti, Cristiane; de Souza, Maria Clara Paixao; and Finger, Marcelo</t>
+          <t>Ariadne Matos, Gustavo Araujo, Arnaldo Candido Junior, and Moacir Ponti. 2024.</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Analysing and Validating Language Complexity Metrics Across South American Indigenous Languages. In Proceedings of the Workshop on Cognitive Modeling and Computational Linguistics, pp 152, 165, 2024</t>
+          <t>Exploring Computational Discernibility of Discourse Domains in Brazilian Portuguese within the Carolina Corpus. In Proceedings of the 16th International Conference on Computational Processing of Portuguese - Vol. 1, Santiago de Compostela, Galicia Spain, pp 255 265, ACL 2024</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Serras, Felipe; de Mello Carpi, Miguel; Catello Branco, Matheus; and Finger, Marcelo.</t>
+          <t>Serras, Felipe Ribas; Sturzeneker, Mariana; de Mello Carpi, Miguel; Palma, Mayara Feliciano; Crespo, Maria Clara Ramos Morales; Costa, Aline Silva; Monte, Vanessa Martins; Namiuti, Cristiane; de Souza, Maria Clara Paixao; and Finger, Marcelo</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Training Large Language Encoders with the Curated Carolina Corpus. In 5th OpenCor: Latin American and Iberian Languages Open Corpora Forum, Santiago de Compostela, 2024</t>
+          <t>Analysing and Validating Language Complexity Metrics Across South American Indigenous Languages. In Proceedings of the Workshop on Cognitive Modeling and Computational Linguistics, pp 152, 165, 2024</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Guilherme Lamartine Mello, Paulo Cavalin, Felipe Ribas Serras, Marcelo Finger, Pedro Domingues, Miguel de Mello Carpi and Marcos Jose Menegon.</t>
+          <t>Serras, Felipe; de Mello Carpi, Miguel; Catello Branco, Matheus; and Finger, Marcelo.</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -6405,12 +6405,12 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>A dual purpose corpus of contemporary Portuguese under continuous development. In 5th OpenCor: Latin American and Iberian Languages Open Corpora Forum Santiago de Compostela, 2024</t>
+          <t>Training Large Language Encoders with the Curated Carolina Corpus. In 5th OpenCor: Latin American and Iberian Languages Open Corpora Forum, Santiago de Compostela, 2024</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Felipe Ribas Serras, Mariana Sturzeneker, Maria Clara Crespo, Mayara Feliciano Palma, Miguel de Mello Carpi, Aline Silva Costa, Guilherme Lamartine de Mello, Vanessa Monte, Cristiane Namiuti, Maria Clara Paixao De Sousa and Marcelo 45 Finger. Carolina:</t>
+          <t>Guilherme Lamartine Mello, Paulo Cavalin, Felipe Ribas Serras, Marcelo Finger, Pedro Domingues, Miguel de Mello Carpi and Marcos Jose Menegon.</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Grammar Induction for Brazilian Indigenous Languages. In the Proceedings of 1st Workshop on NLP for Indigenous Languages of Lusophone Countries ILLC-NLP, pp. 64-72. May, 12</t>
+          <t>A dual purpose corpus of contemporary Portuguese under continuous development. In 5th OpenCor: Latin American and Iberian Languages Open Corpora Forum Santiago de Compostela, 2024</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Silva, D.P.G.; Pardo, T.A.S. 2024</t>
+          <t>Felipe Ribas Serras, Mariana Sturzeneker, Maria Clara Crespo, Mayara Feliciano Palma, Miguel de Mello Carpi, Aline Silva Costa, Guilherme Lamartine de Mello, Vanessa Monte, Cristiane Namiuti, Maria Clara Paixao De Sousa and Marcelo 45 Finger. Carolina:</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Bringing Pragmatics to Porttinari - Adding Speech Acts to News Texts. In the Proceedings of the 16th International Conference on Computational Processing of Portuguese PROPOR, pp. 137-145. May, 13-15</t>
+          <t>Grammar Induction for Brazilian Indigenous Languages. In the Proceedings of 1st Workshop on NLP for Indigenous Languages of Lusophone Countries ILLC-NLP, pp. 64-72. May, 12</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Silva, N. L. P.; Roman, N.T.; Di Felippo, A. 2024</t>
+          <t>Silva, D.P.G.; Pardo, T.A.S. 2024</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -6480,12 +6480,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>A Corpus of Stock Market Tweets Annotated with Named Entities. In the Proceedings of the 16th International Conference on Computational Processing of Portuguese PROPOR, pp. 276-284. May, 13-15</t>
+          <t>Bringing Pragmatics to Porttinari - Adding Speech Acts to News Texts. In the Proceedings of the 16th International Conference on Computational Processing of Portuguese PROPOR, pp. 137-145. May, 13-15</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Zerbinati, M.M.; Roman, N.T.; Di Felippo, A. 2024</t>
+          <t>Silva, N. L. P.; Roman, N.T.; Di Felippo, A. 2024</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Evaluating large language models for the tasks of PoS tagging within the Universal Dependency framework. In the Proceedings of the 16th International Conference on Computational Processing of Portuguese PROPOR, pp. 454-460. May, 13-15</t>
+          <t>A Corpus of Stock Market Tweets Annotated with Named Entities. In the Proceedings of the 16th International Conference on Computational Processing of Portuguese PROPOR, pp. 276-284. May, 13-15</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Machado, M.; Ruiz, E. 2024</t>
+          <t>Zerbinati, M.M.; Roman, N.T.; Di Felippo, A. 2024</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -6530,12 +6530,12 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Using Large Language Models for Identifying Satirical News in Brazilian Portuguese. In the Proceedings of the 16th International Conference on Computational Processing of Portuguese PROPOR, pp. 156-167. May, 13-15</t>
+          <t>Evaluating large language models for the tasks of PoS tagging within the Universal Dependency framework. In the Proceedings of the 16th International Conference on Computational Processing of Portuguese PROPOR, pp. 454-460. May, 13-15</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Wick-Pedro, G.; Silva, C.F.; Inacio, M.L.; Vale, O.A.; Caseli, H.M. 2024</t>
+          <t>Machado, M.; Ruiz, E. 2024</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Towards a Syntactic Lexicon of Brazilian Portuguese Adjectives. In the Proceedings of the 16th International Conference on Computational Processing of Portuguese PROPOR, pp. 532-538. May, 13-15</t>
+          <t>Using Large Language Models for Identifying Satirical News in Brazilian Portuguese. In the Proceedings of the 16th International Conference on Computational Processing of Portuguese PROPOR, pp. 156-167. May, 13-15</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Martinez, R.; Baptista, J.; Vale, O. 2024</t>
+          <t>Wick-Pedro, G.; Silva, C.F.; Inacio, M.L.; Vale, O.A.; Caseli, H.M. 2024</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -6580,12 +6580,12 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Towards Portparser - a highly accurate parsing system for Brazilian Portuguese following the Universal Dependencies framework. In the Proceedings of the 16th International Conference on Computational Processing of Portuguese PROPOR, pp. 401-410. May, 13-15</t>
+          <t>Towards a Syntactic Lexicon of Brazilian Portuguese Adjectives. In the Proceedings of the 16th International Conference on Computational Processing of Portuguese PROPOR, pp. 532-538. May, 13-15</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Lopes, L.; Pardo, T.A.S. 2024</t>
+          <t>Martinez, R.; Baptista, J.; Vale, O. 2024</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -6605,17 +6605,17 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>The relevance of diversity in data for speech processing Accepted for publication at The 34th Brazilian Conference on Intelligent Systems BRACIS 2024</t>
+          <t>Towards Portparser - a highly accurate parsing system for Brazilian Portuguese following the Universal Dependencies framework. In the Proceedings of the 16th International Conference on Computational Processing of Portuguese PROPOR, pp. 401-410. May, 13-15</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Giovana Meloni Craveiro and Julio Cesar Galdino.</t>
+          <t>Lopes, L.; Pardo, T.A.S. 2024</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Conferência Nacional</t>
+          <t>Conferência Internacional</t>
         </is>
       </c>
     </row>
@@ -6630,12 +6630,12 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>A Large Dataset of Spontaneous Speech with the Accent Spoken in Sao Paulo for Automatic Speech Recognition Evaluation Accepted for publication at The 34th Brazilian Conference on Intelligent Systems BRACIS 2024</t>
+          <t>The relevance of diversity in data for speech processing Accepted for publication at The 34th Brazilian Conference on Intelligent Systems BRACIS 2024</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Rodrigo Lima, Sidney Leal, Arnaldo Candido Jr. and Sandra Maria Aluisio.</t>
+          <t>Giovana Meloni Craveiro and Julio Cesar Galdino.</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Anotação de corpus, um lugar privilegiado de observação lingu ´ıstica: o estudo das aposições do português brasileiro segundo o modelo Universal Dependencies. In Anais do XVI Encontro de Lingu´ıstica de Corpus ELC To appear.</t>
+          <t>A Large Dataset of Spontaneous Speech with the Accent Spoken in Sao Paulo for Automatic Speech Recognition Evaluation Accepted for publication at The 34th Brazilian Conference on Intelligent Systems BRACIS 2024</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Duran, M.S.; Pardo, T.A.S. 2024</t>
+          <t>Rodrigo Lima, Sidney Leal, Arnaldo Candido Jr. and Sandra Maria Aluisio.</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Prompt-based mental health screening from social media text. In the Proceedings of the XIII Brazilian Workshop on Social Network Analysis and Mining BraSNAM, pp. 186-192 July, 21-25.</t>
+          <t>Anotação de corpus, um lugar privilegiado de observação lingu ´ıstica: o estudo das aposições do português brasileiro segundo o modelo Universal Dependencies. In Anais do XVI Encontro de Lingu´ıstica de Corpus ELC To appear.</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Santos, W.R.; Paraboni, I. 2024</t>
+          <t>Duran, M.S.; Pardo, T.A.S. 2024</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -6701,21 +6701,21 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Mental Health Prediction From Social Media Text Using Mixture Of Experts. Ieee Latin America Transactions, Vol. 21, N. 6, Pp.723-729</t>
+          <t>Prompt-based mental health screening from social media text. In the Proceedings of the XIII Brazilian Workshop on Social Network Analysis and Mining BraSNAM, pp. 186-192 July, 21-25.</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Santos, W.r.; Sungwon, Y.; Paraboni, I. (2023)</t>
+          <t>Santos, W.R.; Paraboni, I. 2024</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Revista Internacional</t>
+          <t>Conferência Nacional</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6730,12 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Setembrobr: A Social Media Corpus For Depression And Anxiety Disorder Prediction. Language Resources And Evaluation.https://doi.org/10.1007/s10579-022-09633-0</t>
+          <t>Mental Health Prediction From Social Media Text Using Mixture Of Experts. Ieee Latin America Transactions, Vol. 21, N. 6, Pp.723-729</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Santos, W.r.; Oliveira, R.l.; Paraboni, I. (2023)</t>
+          <t>Santos, W.r.; Sungwon, Y.; Paraboni, I. (2023)</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -6755,12 +6755,12 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Multimodal Intent Classification With Incomplete Modalities Using Heterogeneous Networks. Multimedia Systems (submitted).</t>
+          <t>Setembrobr: A Social Media Corpus For Depression And Anxiety Disorder Prediction. Language Resources And Evaluation.https://doi.org/10.1007/s10579-022-09633-0</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Gonzaga, V.m.; Murrugarra-llerena, N.; Marcacini, R.m.</t>
+          <t>Santos, W.r.; Oliveira, R.l.; Paraboni, I. (2023)</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -6780,17 +6780,17 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>O Corpus Dan Testocks: Uma Análise da Distribuição de Etiquetas Morfossintáticas de Acordo Com O Modelo Universal Dependencies. Revista da Abralin. (accepted)</t>
+          <t>Multimodal Intent Classification With Incomplete Modalities Using Heterogeneous Networks. Multimedia Systems (submitted).</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Di Felippo, A.; Roman, N.t.; Pardo, T.a.s.; Moura, L.p. (2023)</t>
+          <t>Gonzaga, V.m.; Murrugarra-llerena, N.; Marcacini, R.m.</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Revista Nacional</t>
+          <t>Revista Internacional</t>
         </is>
       </c>
     </row>
@@ -6805,12 +6805,12 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Falsos Diminutivos do Portuguˆes Brasileiro e Seu Reconhecimento Em Um Dicionário Computacional de Livre Acesso. Revista do Gelne. (accepted)</t>
+          <t>O Corpus Dan Testocks: Uma Análise da Distribuição de Etiquetas Morfossintáticas de Acordo Com O Modelo Universal Dependencies. Revista da Abralin. (accepted)</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Rodrigues, R.; Vale, O.a. (2023)</t>
+          <t>Di Felippo, A.; Roman, N.t.; Pardo, T.a.s.; Moura, L.p. (2023)</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Construções Comparativas Em Português e Sua Anotação Usando A Sintaxe de Dependências. Revista da Abralin. (accepted)</t>
+          <t>Falsos Diminutivos do Portuguˆes Brasileiro e Seu Reconhecimento Em Um Dicionário Computacional de Livre Acesso. Revista do Gelne. (accepted)</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Duran, M.s.; Lopes, L.; Nunes, M.g.v.; Pardo, T.a.s. (2023)</t>
+          <t>Rodrigues, R.; Vale, O.a. (2023)</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>The Amr-pt Corpus And The Semantic Annotation Of Challenging Sentences From Journalistic And Opinion Texts. Delta: Documentação e Estudos Em Linguística Teórica e Aplicada. (accepted)</t>
+          <t>Construções Comparativas Em Português e Sua Anotação Usando A Sintaxe de Dependências. Revista da Abralin. (accepted)</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Inácio, M.l.; Sobrevilla Cabezudo, M.a.; Ramisch, R.; Di Felippo, A.; Pardo, T.a.s. (2023)</t>
+          <t>Duran, M.s.; Lopes, L.; Nunes, M.g.v.; Pardo, T.a.s. (2023)</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -6880,17 +6880,17 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Asr Data Augmentation In Low-resource Settings Using Cross-lingual Multi-speaker Tts And Cross-lingual Voice Conversion. In The Proceedings Of Interspeech, Pp. 1244-1248.</t>
+          <t>The Amr-pt Corpus And The Semantic Annotation Of Challenging Sentences From Journalistic And Opinion Texts. Delta: Documentação e Estudos Em Linguística Teórica e Aplicada. (accepted)</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Casanova, E.; Shulby, C.; Korolev, A.; Candido Junior, A.; Soares, A.s.; Aluísio, S.; Ponti, M.a. (2023)</t>
+          <t>Inácio, M.l.; Sobrevilla Cabezudo, M.a.; Ramisch, R.; Di Felippo, A.; Pardo, T.a.s. (2023)</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Conferência Internacional</t>
+          <t>Revista Nacional</t>
         </is>
       </c>
     </row>
@@ -6905,17 +6905,17 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Sinalizadores Retórico-discursivos: Revisitando A Anotação Rst No Córpus Cstnews. In Anais da Viii Jornada de Descrição do Português (jdp). (accepted)</t>
+          <t>Asr Data Augmentation In Low-resource Settings Using Cross-lingual Multi-speaker Tts And Cross-lingual Voice Conversion. In The Proceedings Of Interspeech, Pp. 1244-1248.</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Rodrigues, R.; Souza, J.w.; Cardoso, P.c.f. (2023)</t>
+          <t>Casanova, E.; Shulby, C.; Korolev, A.; Candido Junior, A.; Soares, A.s.; Aluísio, S.; Ponti, M.a. (2023)</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Conferência Nacional</t>
+          <t>Conferência Internacional</t>
         </is>
       </c>
     </row>
@@ -6930,12 +6930,12 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Aposições Anafóricas e Catafóricas No Português e Sua Anotação No Esquema Universal Dependencies. In Anais da Viii Jornada de Descrição do Português (jdp). (accepted)</t>
+          <t>Sinalizadores Retórico-discursivos: Revisitando A Anotação Rst No Córpus Cstnews. In Anais da Viii Jornada de Descrição do Português (jdp). (accepted)</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Duran, M.s.; Nunes, M.g.v. (2023)</t>
+          <t>Rodrigues, R.; Souza, J.w.; Cardoso, P.c.f. (2023)</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Tipologia de Fenômenos Ortográficos e Lexicais Em Cgu: O Caso dos Tweets do Mercado Financeiro. In Anais da Viii Jornada de Descrição do Português (jdp). (accepted)</t>
+          <t>Aposições Anafóricas e Catafóricas No Português e Sua Anotação No Esquema Universal Dependencies. In Anais da Viii Jornada de Descrição do Português (jdp). (accepted)</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Scandarolli, C.l.; Di Felippo, A.; Roman, N.t.; Pardo, T.a.s. (2023)</t>
+          <t>Duran, M.s.; Nunes, M.g.v. (2023)</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Formal Features For A Syntactic-semantic Classification Of Predicative Adjectives In Brazilian Portuguese. In Anais da Viii Jornada de Descrição do Português (jdp). (accepted)</t>
+          <t>Tipologia de Fenômenos Ortográficos e Lexicais Em Cgu: O Caso dos Tweets do Mercado Financeiro. In Anais da Viii Jornada de Descrição do Português (jdp). (accepted)</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Martinez, R.m.s.m; Vale, O.a. (2023)</t>
+          <t>Scandarolli, C.l.; Di Felippo, A.; Roman, N.t.; Pardo, T.a.s. (2023)</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Indução Gramatical Para O Português: A Contribuição da Informação Mútua Para Descoberta de Relações de Dependência. In Anais da Viii Jornada de Descrição do Português (jdp). (accepted)</t>
+          <t>Formal Features For A Syntactic-semantic Classification Of Predicative Adjectives In Brazilian Portuguese. In Anais da Viii Jornada de Descrição do Português (jdp). (accepted)</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Silva, D.p.g.; Pardo, T.a.s. (2023)</t>
+          <t>Martinez, R.m.s.m; Vale, O.a. (2023)</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Lexical Noun Phrase Chunking With Universal Dependencies For Portuguese. In The Proceedings Of The 2nd Edition Of The Universal Dependencies Brazilian Festival (udfest-br). (accepted)</t>
+          <t>Indução Gramatical Para O Português: A Contribuição da Informação Mútua Para Descoberta de Relações de Dependência. In Anais da Viii Jornada de Descrição do Português (jdp). (accepted)</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Souza, A.; Ruiz, E.e.s. (2023)</t>
+          <t>Silva, D.p.g.; Pardo, T.a.s. (2023)</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -7055,12 +7055,12 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Um Estudo das Construções Dar + Para + V [infinitivo] Nas Universal Dependencies. In The Proceedings Of The 2nd Edition Of The Universal Dependencies Brazilian Festival (udfest-br). (accepted)</t>
+          <t>Lexical Noun Phrase Chunking With Universal Dependencies For Portuguese. In The Proceedings Of The 2nd Edition Of The Universal Dependencies Brazilian Festival (udfest-br). (accepted)</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Vale, O.a.; Couto, M.m.l. (2023)</t>
+          <t>Souza, A.; Ruiz, E.e.s. (2023)</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Em Direção `a Anotação Sintática – Ud de Tweets do Mercado Financeiro. In The Proceedings Of The 2nd Edition Of The Universal Dependencies Brazilian Festival (udfest-br). (accepted)</t>
+          <t>Um Estudo das Construções Dar + Para + V [infinitivo] Nas Universal Dependencies. In The Proceedings Of The 2nd Edition Of The Universal Dependencies Brazilian Festival (udfest-br). (accepted)</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Barbosa, B.k.s.; Di Felippo, A. (2023)</t>
+          <t>Vale, O.a.; Couto, M.m.l. (2023)</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Construções Sintáticas do Português Que Desafiam A Tarefa de Parsing: Uma Análise Qualitativa. In The Proceedings Of The 2nd Edition Of The Universal Dependencies Brazilian Festival (udfest-br). (aaccepted)</t>
+          <t>Em Direção `a Anotação Sintática – Ud de Tweets do Mercado Financeiro. In The Proceedings Of The 2nd Edition Of The Universal Dependencies Brazilian Festival (udfest-br). (accepted)</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Duran, M.s.; Nunes, M.g.v.; Pardo, T.a.s. (2023)</t>
+          <t>Barbosa, B.k.s.; Di Felippo, A. (2023)</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -7130,12 +7130,12 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Enhanced Dependencies Para O Português Brasileiro. In The Proceedings Of The 2nd Edition Of The Universal Dependencies Brazilian Festival (udfest-br). (accepted)</t>
+          <t>Construções Sintáticas do Português Que Desafiam A Tarefa de Parsing: Uma Análise Qualitativa. In The Proceedings Of The 2nd Edition Of The Universal Dependencies Brazilian Festival (udfest-br). (aaccepted)</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Pagano, A.s.; Duran, M.s.; Pardo, T.a.s. (2023)</t>
+          <t>Duran, M.s.; Nunes, M.g.v.; Pardo, T.a.s. (2023)</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Insights Into The Ud Tagset: Unveiling Its Intricacies. In The Proceedings Of The 2nd Edition Of The Universal Dependencies Brazilian Festival (udfest-br). (accepted)</t>
+          <t>Enhanced Dependencies Para O Português Brasileiro. In The Proceedings Of The 2nd Edition Of The Universal Dependencies Brazilian Festival (udfest-br). (accepted)</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Duran, M.s. (2023)</t>
+          <t>Pagano, A.s.; Duran, M.s.; Pardo, T.a.s. (2023)</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Verifica-ud: A Verifier For Universal Dependencies Annotation For Portuguese. In The Proceedings Of The 2nd Edition Of The Universal Dependencies Brazilian Festival (udfest-br). (accepted)</t>
+          <t>Insights Into The Ud Tagset: Unveiling Its Intricacies. In The Proceedings Of The 2nd Edition Of The Universal Dependencies Brazilian Festival (udfest-br). (accepted)</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Lopes, L.; Duran, M.s.; Pardo, T.a.s. (2023)</t>
+          <t>Duran, M.s. (2023)</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Etiquetagem Morfossintática Multigênero Para O Português do Brasil Segundo O Modelo ”universal Dependencies”. In The Proceedings Of The 15th Symposium In Information And Human Language Technology (stil). (accepted)</t>
+          <t>Verifica-ud: A Verifier For Universal Dependencies Annotation For Portuguese. In The Proceedings Of The 2nd Edition Of The Universal Dependencies Brazilian Festival (udfest-br). (accepted)</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Silva, E.h.; Pardo, T.a.s.; Roman, N.t. (2023)</t>
+          <t>Lopes, L.; Duran, M.s.; Pardo, T.a.s. (2023)</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>The Dawn Of The Porttinari Multigenre Treebank: Introducing Its Journalistic Portion. In The Proceedings Of The 14th Symposium In Information And Human Language Technology (stil). (accepted)</t>
+          <t>Etiquetagem Morfossintática Multigênero Para O Português do Brasil Segundo O Modelo ”universal Dependencies”. In The Proceedings Of The 15th Symposium In Information And Human Language Technology (stil). (accepted)</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Duran, M.s.; Lopes, L.; Nunes, M.g.v.; Pardo, T.a.s. (2023)</t>
+          <t>Silva, E.h.; Pardo, T.a.s.; Roman, N.t. (2023)</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -7255,12 +7255,12 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>A Sentiment Analysis Benchmark For Automated Machine Learning Applications And A Proof Of Concept In Hate Speech Detection. In The Proceedings Of The 15th Symposium In Information And Human Language Technology (stil). (accepted)</t>
+          <t>The Dawn Of The Porttinari Multigenre Treebank: Introducing Its Journalistic Portion. In The Proceedings Of The 14th Symposium In Information And Human Language Technology (stil). (accepted)</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Silva, M.c.r.; Oliveira, V.a.; Pardo, T.a.s. (2023)</t>
+          <t>Duran, M.s.; Lopes, L.; Nunes, M.g.v.; Pardo, T.a.s. (2023)</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -7280,12 +7280,12 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Disambiguation Of Universal Dependencies Part-of-speech Tags Of Closed Class Words In Portuguese. In The Proceedings Of The 12th Brazilian Conference On Intelligent Systems (bracis). (accepted)</t>
+          <t>A Sentiment Analysis Benchmark For Automated Machine Learning Applications And A Proof Of Concept In Hate Speech Detection. In The Proceedings Of The 15th Symposium In Information And Human Language Technology (stil). (accepted)</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Lopes, L.; Fernandes, R.h.l.; Duran, M.s.; Inácio, M.l.; Pardo, T.a.s. (2023)</t>
+          <t>Silva, M.c.r.; Oliveira, V.a.; Pardo, T.a.s. (2023)</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -7305,17 +7305,17 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Avaliação Qualitativa do Analisador Sintático Udpipe 2 Treinado Sobre O Córpus Jornalístico Porttinari Base. Relatório Técnico do Icmc 442. Instituto de Ciências Matemáticas e de Computação, Universidade de São Paulo. São Carlos-sp, Abril, 58p.</t>
+          <t>Disambiguation Of Universal Dependencies Part-of-speech Tags Of Closed Class Words In Portuguese. In The Proceedings Of The 12th Brazilian Conference On Intelligent Systems (bracis). (accepted)</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Duran, M.s.; Nunes, M.g.v.; Pardo, T.a.s. (2023)</t>
+          <t>Lopes, L.; Fernandes, R.h.l.; Duran, M.s.; Inácio, M.l.; Pardo, T.a.s. (2023)</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Outros (relatórios Técnicos, Capítulos de Livros Etc.)</t>
+          <t>Conferência Nacional</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Evaluating Openai’s Whisper Asr For Punctuation Prediction And Topic Modeling Of Life Histories Of The Museum Of The Person. Prosodic Interfaces, De Gruyter Eds., Miguel Oliveira Jr. Org. (submitted)</t>
+          <t>Avaliação Qualitativa do Analisador Sintático Udpipe 2 Treinado Sobre O Córpus Jornalístico Porttinari Base. Relatório Técnico do Icmc 442. Instituto de Ciências Matemáticas e de Computação, Universidade de São Paulo. São Carlos-sp, Abril, 58p.</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Gris, L.; Ricardo Marcondes Marcacini; Candido Junior, A.; Casanova, E.; Soares, A.; Aluísio, S.m.</t>
+          <t>Duran, M.s.; Nunes, M.g.v.; Pardo, T.a.s. (2023)</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -7355,12 +7355,12 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Recursos Para O Processamento de Fala. Processamento de Linguagem Natural: Conceitos, Técnicas e Aplicações Em Português, Brasileiras Em Pln Eds. (accepted)</t>
+          <t>Evaluating Openai’s Whisper Asr For Punctuation Prediction And Topic Modeling Of Life Histories Of The Museum Of The Person. Prosodic Interfaces, De Gruyter Eds., Miguel Oliveira Jr. Org. (submitted)</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Casanova, E.; Santos, V.g.; Svartman, F.r.f.; Leite, M.q.; Candido Junior, A.; Ricardo Marcondes Marcacini; Solange Rezende;; Alu´isio, S.m.</t>
+          <t>Gris, L.; Ricardo Marcondes Marcacini; Candido Junior, A.; Casanova, E.; Soares, A.; Aluísio, S.m.</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -7380,17 +7380,17 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>NILC-Metrix: assessing the complexity of written and spoken language in Brazilian Portuguese. Lang Resources and Evaluation 2023</t>
+          <t>Recursos Para O Processamento de Fala. Processamento de Linguagem Natural: Conceitos, Técnicas e Aplicações Em Português, Brasileiras Em Pln Eds. (accepted)</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Leal, S.E., Duran, M.S., Scarton, C.E., Aluisio, S.M.</t>
+          <t>Casanova, E.; Santos, V.g.; Svartman, F.r.f.; Leite, M.q.; Candido Junior, A.; Ricardo Marcondes Marcacini; Solange Rezende;; Alu´isio, S.m.</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Revista Internacional</t>
+          <t>Outros (relatórios Técnicos, Capítulos de Livros Etc.)</t>
         </is>
       </c>
     </row>
@@ -7405,17 +7405,17 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Falsos Diminutivos do Portugues Brasileiro e seu Reconhecimento em um Dicionario Computacional de Livre Acesso. Revista do GELNE, Vol. 25, N. 3.</t>
+          <t>NILC-Metrix: assessing the complexity of written and spoken language in Brazilian Portuguese. Lang Resources and Evaluation 2023</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Rodrigues, R.; Vale, O.A. 2023</t>
+          <t>Leal, S.E., Duran, M.S., Scarton, C.E., Aluisio, S.M.</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Revista Nacional</t>
+          <t>Revista Internacional</t>
         </is>
       </c>
     </row>
@@ -7430,12 +7430,12 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Ações para aquisição de conhecimento de matematica e de computação por alunos do ensino médio. Grad+: Revista de Graduação USP, Vol. 7, N. 1, pp. 75-88.</t>
+          <t>Falsos Diminutivos do Portugues Brasileiro e seu Reconhecimento em um Dicionario Computacional de Livre Acesso. Revista do GELNE, Vol. 25, N. 3.</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Cunha, F.D.; Souza, K.V.M.; Pardo, T.A.S. 2023</t>
+          <t>Rodrigues, R.; Vale, O.A. 2023</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -7455,17 +7455,17 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>On the Use of Aggregation Functions for Semi-Supervised Network Embedding. In: 2023 International Joint Conference on Neural Networks IJCNN IEEE, 2023. p. 1-8</t>
+          <t>Ações para aquisição de conhecimento de matematica e de computação por alunos do ensino médio. Grad+: Revista de Graduação USP, Vol. 7, N. 1, pp. 75-88.</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Moraes, Marcelo Isaias; Marcacini, Ricardo Marcondes.</t>
+          <t>Cunha, F.D.; Souza, K.V.M.; Pardo, T.A.S. 2023</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Conferência Internacional</t>
+          <t>Revista Nacional</t>
         </is>
       </c>
     </row>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>A Multilingual Dataset for Speech Synthesis in Low-Resource Languages. In: Text, Speech, and Dialogue TSD 2023, 2023, Plzen, Czechia. Text, Speech, and Dialogue. Cham: Springer ˇ Nature Switzerland, 2023. p. 188-199</t>
+          <t>On the Use of Aggregation Functions for Semi-Supervised Network Embedding. In: 2023 International Joint Conference on Neural Networks IJCNN IEEE, 2023. p. 1-8</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Frederico S. Oliveira, Edresson Casanova, Arnaldo Candido Junior, Anderson S. Soares and Arlindo R. Galvao Filho. CML-TTS:</t>
+          <t>Moraes, Marcelo Isaias; Marcacini, Ricardo Marcondes.</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Evaluation of Speech Representations for MOS Prediction. In: Text, Speech, and Dialogue TSD 2023, 2023, Plzen, Czechia. Text, Speech, and Dialogue. Cham: Springer Nature Switzerland, ˇ 2023. p. 270-282</t>
+          <t>A Multilingual Dataset for Speech Synthesis in Low-Resource Languages. In: Text, Speech, and Dialogue TSD 2023, 2023, Plzen, Czechia. Text, Speech, and Dialogue. Cham: Springer ˇ Nature Switzerland, 2023. p. 188-199</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>ASR data augmentation in low-resource settings using crosslingual multi-speaker TTS and cross-lingual voice conversion. Proc INTERSPEECH 2023, 1244-1248, doi: 10.21437 Interspeech.2023-496 44</t>
+          <t>Evaluation of Speech Representations for MOS Prediction. In: Text, Speech, and Dialogue TSD 2023, 2023, Plzen, Czechia. Text, Speech, and Dialogue. Cham: Springer Nature Switzerland, ˇ 2023. p. 270-282</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Casanova, E., Shulby, C., Korolev, A., Junior, A.C., Soares, A.d.S., Aluísio, S., Ponti, M.A. 2023</t>
+          <t>Frederico S. Oliveira, Edresson Casanova, Arnaldo Candido Junior, Anderson S. Soares and Arlindo R. Galvao Filho. CML-TTS:</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -7555,12 +7555,12 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>CORAA ASR: A large corpus of spontaneous and prepared speech manually validated for speech recognition in Brazilian Portuguese. Language Resources and Evaluation 57.3 2023: 1139-1171</t>
+          <t>ASR data augmentation in low-resource settings using crosslingual multi-speaker TTS and cross-lingual voice conversion. Proc INTERSPEECH 2023, 1244-1248, doi: 10.21437 Interspeech.2023-496 44</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Candido Junior, Arnaldo, et al.</t>
+          <t>Casanova, E., Shulby, C., Korolev, A., Junior, A.C., Soares, A.d.S., Aluísio, S., Ponti, M.A. 2023</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>A Sentiment Analysis Benchmark for Automated Machine Learning Applications. In the Proceedings of the IEEE 22nd International Conference on Machine Learning and Applications ICMLA, pp. 1487-1494. December, 15-17</t>
+          <t>CORAA ASR: A large corpus of spontaneous and prepared speech manually validated for speech recognition in Brazilian Portuguese. Language Resources and Evaluation 57.3 2023: 1139-1171</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Silva, M.C.R.; Oliveira, V.A.; Pardo, T.A.S. 2023</t>
+          <t>Candido Junior, Arnaldo, et al.</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>NoHateBrazil: A Brazilian Portuguese Text Offensiveness Analysis System. In the Proceedings of the 14th Conference on Recent Advances in Natural Language Processing RANLP, pp. 1180-1186. September, 4-6</t>
+          <t>A Sentiment Analysis Benchmark for Automated Machine Learning Applications. In the Proceedings of the IEEE 22nd International Conference on Machine Learning and Applications ICMLA, pp. 1487-1494. December, 15-17</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Vargas, F.; Carvalho, I.; Schmeisser-Nieto, W.S.; Benevenuto, F.; Pardo, T.A.S. 2023</t>
+          <t>Silva, M.C.R.; Oliveira, V.A.; Pardo, T.A.S. 2023</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Socially Responsible Hate Speech Detection: Can Classifiers Reflect Social Stereotypes? In the Proceedings of the 14th Conference on Recent Advances in Natural Language Processing RANLP, pp. 1187-1196. September, 4-6</t>
+          <t>NoHateBrazil: A Brazilian Portuguese Text Offensiveness Analysis System. In the Proceedings of the 14th Conference on Recent Advances in Natural Language Processing RANLP, pp. 1180-1186. September, 4-6</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Vargas, F.; Carvalho, I.; Hurriyeto ¨ glu, A.; Pardo, T.A.S.; Benevenuto, F. 2023 ˘</t>
+          <t>Vargas, F.; Carvalho, I.; Schmeisser-Nieto, W.S.; Benevenuto, F.; Pardo, T.A.S. 2023</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Predicting SentenceLevel Factuality of News and Bias of Media Outlets. In the Proceedings of the 14th Conference on Recent Advances in Natural Language Processing RANLP, pp. 1197-1206 September, 4-6. 46</t>
+          <t>Socially Responsible Hate Speech Detection: Can Classifiers Reflect Social Stereotypes? In the Proceedings of the 14th Conference on Recent Advances in Natural Language Processing RANLP, pp. 1187-1196. September, 4-6</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Vargas, F.; Jaidka, K.; Pardo, T.A.S.; Benevenuto, F. 2023</t>
+          <t>Vargas, F.; Carvalho, I.; Hurriyeto ¨ glu, A.; Pardo, T.A.S.; Benevenuto, F. 2023 ˘</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -7680,17 +7680,17 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Cluster Fusion Training: Exploring Cluster Analysis to Enhance Cross-Domain Sentiment Classification. In: Anais do XX Encontro Nacional de Inteligencia Artificial e Computacional ENIAC 2023 SBC, 2023. p. 330-344.</t>
+          <t>Predicting SentenceLevel Factuality of News and Bias of Media Outlets. In the Proceedings of the 14th Conference on Recent Advances in Natural Language Processing RANLP, pp. 1197-1206 September, 4-6. 46</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Tomita, Victor Akihito Kamada; DA SILVA, Angelo Cesar Mendes; Marcacini, Ricardo Marcondes.</t>
+          <t>Vargas, F.; Jaidka, K.; Pardo, T.A.S.; Benevenuto, F. 2023</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Conferência Nacional</t>
+          <t>Conferência Internacional</t>
         </is>
       </c>
     </row>
@@ -7705,12 +7705,12 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Disambiguation of Universal Dependencies Part-of-Speech Tags of Closed Class Words Systems BRACIS, pp. 241-255 September, 25-29.</t>
+          <t>Cluster Fusion Training: Exploring Cluster Analysis to Enhance Cross-Domain Sentiment Classification. In: Anais do XX Encontro Nacional de Inteligencia Artificial e Computacional ENIAC 2023 SBC, 2023. p. 330-344.</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Lopes, L.; Fernandes, P.; Duran, M.S.; Inacio, M.L.; Pardo, T.A.S. 2023</t>
+          <t>Tomita, Victor Akihito Kamada; DA SILVA, Angelo Cesar Mendes; Marcacini, Ricardo Marcondes.</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Sinalizadores retorico-discursivos: revisitando a anotação RST no c orpus CSTNews. In Anais da VIII Jornada de Descrição do Português JDP, pp. 249-257. September, 25-29</t>
+          <t>Disambiguation of Universal Dependencies Part-of-Speech Tags of Closed Class Words Systems BRACIS, pp. 241-255 September, 25-29.</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Rodrigues, R.; Souza, J.W.; Cardoso, P.C.F. 2023</t>
+          <t>Lopes, L.; Fernandes, P.; Duran, M.S.; Inacio, M.L.; Pardo, T.A.S. 2023</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Aposições anaf oricas e cataf oricas no portugues e sua anotação ao no esquema Universal Dependencies. In Anais da VIII. Jornada de Descrição do Português JDP, pp. 268-277. September, 25-29</t>
+          <t>Sinalizadores retorico-discursivos: revisitando a anotação RST no c orpus CSTNews. In Anais da VIII Jornada de Descrição do Português JDP, pp. 249-257. September, 25-29</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Duran, M.S.; Nunes, M.G.V. 2023</t>
+          <t>Rodrigues, R.; Souza, J.W.; Cardoso, P.C.F. 2023</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -7780,12 +7780,12 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Tipologia de fenomenos ortogr aficos e lexicais em CGU: o caso dos tweets do mercado financeiro. In Anais da VIII Jornada de Descrição do Português JDP, pp. 240-248 September, 25-29.</t>
+          <t>Aposições anaf oricas e cataf oricas no portugues e sua anotação ao no esquema Universal Dependencies. In Anais da VIII. Jornada de Descrição do Português JDP, pp. 268-277. September, 25-29</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Scandarolli, C.L.; Di Felippo, A.; Roman, N.T.; Pardo, T.A.S. 2023</t>
+          <t>Duran, M.S.; Nunes, M.G.V. 2023</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Formal features for a syntactic-semantic classification of predicative adjectives in Brazilian Portuguese. In Anais da VIII Jornada de Descrição do Português JDP, pp. 336-345. September, 25-29</t>
+          <t>Tipologia de fenomenos ortogr aficos e lexicais em CGU: o caso dos tweets do mercado financeiro. In Anais da VIII Jornada de Descrição do Português JDP, pp. 240-248 September, 25-29.</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Martinez, R.M.S.M; Vale, O.A. 2023</t>
+          <t>Scandarolli, C.L.; Di Felippo, A.; Roman, N.T.; Pardo, T.A.S. 2023</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Indução Gramatical para o Português: a Contribuição da Informação Mútua para Descoberta de Relações de Dependência.In Anais da VIII Jornada de Descrição do Português JDP, pp. 298-307 September, 25-29.</t>
+          <t>Formal features for a syntactic-semantic classification of predicative adjectives in Brazilian Portuguese. In Anais da VIII Jornada de Descrição do Português JDP, pp. 336-345. September, 25-29</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Silva, D.P.G.; Pardo, T.A.S. 2023</t>
+          <t>Martinez, R.M.S.M; Vale, O.A. 2023</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Lexical noun phrase chunking with Universal Dependencies for Portuguese. In the Proceedings of the 2nd Edition of the Universal Dependencies Brazilian Festival UDFest-BR, pp. 422-431 September, 25.</t>
+          <t>Indução Gramatical para o Português: a Contribuição da Informação Mútua para Descoberta de Relações de Dependência.In Anais da VIII Jornada de Descrição do Português JDP, pp. 298-307 September, 25-29.</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Souza, A.; Ruiz, E.E.S. 2023</t>
+          <t>Silva, D.P.G.; Pardo, T.A.S. 2023</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Um estudo das construções dar + para + V [infinitivo] nas Universal Dependencies. In the Proceedings of the 2nd Edition of the Universal Dependencies Brazilian Festival UDFest-BR, pp. 481-490 September, 25.</t>
+          <t>Lexical noun phrase chunking with Universal Dependencies for Portuguese. In the Proceedings of the 2nd Edition of the Universal Dependencies Brazilian Festival UDFest-BR, pp. 422-431 September, 25.</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Couto, M.M.L.; Vale, O.A. 2023</t>
+          <t>Souza, A.; Ruiz, E.E.S. 2023</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Em Direção a Anotação Sintática - UD de Tweets do Mercado Financeiro. In the Proceedings of the 2nd Edition of the Universal Dependencies Brazilian Festival UDFest-BR, pp. 499-508 September, 25.</t>
+          <t>Um estudo das construções dar + para + V [infinitivo] nas Universal Dependencies. In the Proceedings of the 2nd Edition of the Universal Dependencies Brazilian Festival UDFest-BR, pp. 481-490 September, 25.</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Barbosa, B.K.S.; Di Felippo, A. 2023</t>
+          <t>Couto, M.M.L.; Vale, O.A. 2023</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -7930,12 +7930,12 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Construções sint aticas do portugues que desafiam a tarefa de parsing: uma an alise qualitativa. In the ´. Proceedings of the 2nd Edition of the Universal Dependencies Brazilian Festival UDFest-BR, pp. 432-441 September, 25.</t>
+          <t>Em Direção a Anotação Sintática - UD de Tweets do Mercado Financeiro. In the Proceedings of the 2nd Edition of the Universal Dependencies Brazilian Festival UDFest-BR, pp. 499-508 September, 25.</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Duran, M.S.; Nunes, M.G.V.; Pardo, T.A.S. 2023</t>
+          <t>Barbosa, B.K.S.; Di Felippo, A. 2023</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Enhanced dependencies para o portugues brasileiro. In the Proceedings of the 2nd Edition of the Universal. Dependencies Brazilian Festival UDFest-BR, pp. 461-470 September, 25.</t>
+          <t>Construções sint aticas do portugues que desafiam a tarefa de parsing: uma an alise qualitativa. In the ´. Proceedings of the 2nd Edition of the Universal Dependencies Brazilian Festival UDFest-BR, pp. 432-441 September, 25.</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Pagano, A.S.; Duran, M.S.; Pardo, T.A.S. 2023</t>
+          <t>Duran, M.S.; Nunes, M.G.V.; Pardo, T.A.S. 2023</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -7980,12 +7980,12 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Insights into the UD Tagset: Unveiling its Intricacies. In the Proceedings of the 2nd Edition of the Universal Dependencies Brazilian Festival UDFest-BR, pp. 491-498 September, 25.</t>
+          <t>Enhanced dependencies para o portugues brasileiro. In the Proceedings of the 2nd Edition of the Universal. Dependencies Brazilian Festival UDFest-BR, pp. 461-470 September, 25.</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Duran, M.S. 2023</t>
+          <t>Pagano, A.S.; Duran, M.S.; Pardo, T.A.S. 2023</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Verifica-UD: a Verifier for Universal Dependencies Annotation for Portuguese. In the Proceedings of the 2nd Edition of the Universal Dependencies Brazilian Festival UDFest-BR, pp 451-460. September, 25.</t>
+          <t>Insights into the UD Tagset: Unveiling its Intricacies. In the Proceedings of the 2nd Edition of the Universal Dependencies Brazilian Festival UDFest-BR, pp. 491-498 September, 25.</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Lopes, L.; Duran, M.S.; Pardo, T.A.S. 2023</t>
+          <t>Duran, M.S. 2023</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Predição de transtorno depressivo em redes sociais: BERT supervisionado ou ChatGPT zero-shot? In the Proceedings of the 14th Symposium in Information and Human Language Technology STIL, pp. 11-21 September, 25-29.</t>
+          <t>Verifica-UD: a Verifier for Universal Dependencies Annotation for Portuguese. In the Proceedings of the 2nd Edition of the Universal Dependencies Brazilian Festival UDFest-BR, pp 451-460. September, 25.</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Santos, W.R.; Paraboni, I. 2023</t>
+          <t>Lopes, L.; Duran, M.S.; Pardo, T.A.S. 2023</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>A Deep Learning Approach for Stance Analysis of Covid-19 Vaccines Tweets by Brazilian Political Elites. In the Proceedings of the 14th Symposium in Information and Human Language Technology STIL, pp. 104-114 September, 25-29.</t>
+          <t>Predição de transtorno depressivo em redes sociais: BERT supervisionado ou ChatGPT zero-shot? In the Proceedings of the 14th Symposium in Information and Human Language Technology STIL, pp. 11-21 September, 25-29.</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Barberia, L.G.; Schmalz, P.H.S.; Roman, N.T. 2023 When Tweets Get Viral</t>
+          <t>Santos, W.R.; Paraboni, I. 2023</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Etiquetagem morfossintatica multigenero para o portugu es do Brasil segundo o modelo ”Universal Dependencies”. In the Proceedings of the 14th Symposium in Information and Human Language Technology STIL, pp. 63-73 September, 25-29.</t>
+          <t>A Deep Learning Approach for Stance Analysis of Covid-19 Vaccines Tweets by Brazilian Political Elites. In the Proceedings of the 14th Symposium in Information and Human Language Technology STIL, pp. 104-114 September, 25-29.</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Silva, E.H.; Pardo, T.A.S.; Roman, N.T. 2023</t>
+          <t>Barberia, L.G.; Schmalz, P.H.S.; Roman, N.T. 2023 When Tweets Get Viral</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>The Dawn of the Porttinari Multigenre Treebank: Introducing its Journalistic Portion. In the Proceedings of the 14th Symposium in Information and Human Language Technology STIL, pp. 115-124 September, 25-29.</t>
+          <t>Etiquetagem morfossintatica multigenero para o portugu es do Brasil segundo o modelo ”Universal Dependencies”. In the Proceedings of the 14th Symposium in Information and Human Language Technology STIL, pp. 63-73 September, 25-29.</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Duran, M.S.; Lopes, L.; Nunes, M.G.V.; Pardo, T.A.S. 2023</t>
+          <t>Silva, E.H.; Pardo, T.A.S.; Roman, N.T. 2023</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>A Sentiment Analysis Benchmark for Automated Machine Learning Applications and a Proof of Concept in. Hate Speech Detection. In the Proceedings of the 14th Symposium in Information and Human Language Technology STIL, pp. 199-206 September, 25-29.</t>
+          <t>The Dawn of the Porttinari Multigenre Treebank: Introducing its Journalistic Portion. In the Proceedings of the 14th Symposium in Information and Human Language Technology STIL, pp. 115-124 September, 25-29.</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Silva, M.C.R.; Oliveira, V.A.; Pardo, T.A.S. 2023</t>
+          <t>Duran, M.S.; Lopes, L.; Nunes, M.G.V.; Pardo, T.A.S. 2023</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>SteamBR: a dataset for game reviews and evaluation of a state-of-the-art method for helpfulness prediction. In the Proceedings of the XII Brazilian Workshop on Social Network Analysis and Mining BraSNAM, pp. 210-215 August, 6-11.</t>
+          <t>A Sentiment Analysis Benchmark for Automated Machine Learning Applications and a Proof of Concept in. Hate Speech Detection. In the Proceedings of the 14th Symposium in Information and Human Language Technology STIL, pp. 199-206 September, 25-29.</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Jorge, G.A.Z. and Pardo, T.A.S. 2023</t>
+          <t>Silva, M.C.R.; Oliveira, V.A.; Pardo, T.A.S. 2023</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -8180,17 +8180,17 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Evaluating OpenAI’s Whisper ASR for Punctuation Prediction and Topic Modeling of life histories of the Museum of the Person. Prosodic Interfaces, De Gruyter eds., Miguel Oliveira Jr org.</t>
+          <t>SteamBR: a dataset for game reviews and evaluation of a state-of-the-art method for helpfulness prediction. In the Proceedings of the XII Brazilian Workshop on Social Network Analysis and Mining BraSNAM, pp. 210-215 August, 6-11.</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Lucas Gris, Ricardo Marcondes Marcacini, Arnaldo Candido Junior, Edresson Casanova,Anderson Soares, Sandra Maria Aluísio.</t>
+          <t>Jorge, G.A.Z. and Pardo, T.A.S. 2023</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Outros (relatórios Técnicos, Capítulos de Livros Etc.)</t>
+          <t>Conferência Nacional</t>
         </is>
       </c>
     </row>
@@ -8201,21 +8201,21 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Portilexicon-ud: A Portuguese Lexical Resource According To Universal Dependencies Model. In The Proceedings Of The 13th Edition Of The Language Resources And Evaluation Conference (lrec’22), Pp. 6635-6643. June, 20-25. http://www.lrec-conf.org/proceedings/lrec2022/pdf/2022.lrec-1.715.pdf</t>
+          <t>Evaluating OpenAI’s Whisper ASR for Punctuation Prediction and Topic Modeling of life histories of the Museum of the Person. Prosodic Interfaces, De Gruyter eds., Miguel Oliveira Jr org.</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Lopes, L.; Duran, M.s.; Fernandes, P.h.l.; Pardo, T.a.s.</t>
+          <t>Lucas Gris, Ricardo Marcondes Marcacini, Arnaldo Candido Junior, Edresson Casanova,Anderson Soares, Sandra Maria Aluísio.</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Publicação</t>
+          <t>Outros (relatórios Técnicos, Capítulos de Livros Etc.)</t>
         </is>
       </c>
     </row>
@@ -8230,12 +8230,12 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Evaluating Methods For Extraction Of Aspect Terms In Opinion Texts In Portuguese - The Challenges Of Implicit Aspects. In The Proceedings Of The 13th Edition Of The Language Resources And Evaluation Conference (lrec’22), Pp. 3819-3828. June, 20-25. http://www.lrec-conf.org/proceedings/lrec2022/pdf/2022.lrec-1.407.pdf</t>
+          <t>Portilexicon-ud: A Portuguese Lexical Resource According To Universal Dependencies Model. In The Proceedings Of The 13th Edition Of The Language Resources And Evaluation Conference (lrec’22), Pp. 6635-6643. June, 20-25. http://www.lrec-conf.org/proceedings/lrec2022/pdf/2022.lrec-1.715.pdf</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Machado, M.t. And Pardo, T.a.s.</t>
+          <t>Lopes, L.; Duran, M.s.; Fernandes, P.h.l.; Pardo, T.a.s.</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -8255,17 +8255,17 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Casanova, Edresson, Arnaldo Candido Junior, Christopher Shulby, Frederico Santos de Oliveira, João Paulo Teixeira, Moacir Antonelli Ponti, And Sandra Aluísio. "tts-portuguese Corpus: A Corpus For Speech Synthesis In Brazilian Portuguese." Language Resources And Evaluation (lrec’22) (2022): 1-13.[3 Citação]</t>
+          <t>Evaluating Methods For Extraction Of Aspect Terms In Opinion Texts In Portuguese - The Challenges Of Implicit Aspects. In The Proceedings Of The 13th Edition Of The Language Resources And Evaluation Conference (lrec’22), Pp. 3819-3828. June, 20-25. http://www.lrec-conf.org/proceedings/lrec2022/pdf/2022.lrec-1.407.pdf</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Casanova, Edresson, Arnaldo Candido Junior, Christopher Shulby, Frederico Santos de Oliveira, João Paulo Teixeira, Moacir Antonelli Ponti, And Sandra Aluísio</t>
+          <t>Machado, M.t. And Pardo, T.a.s.</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Citação</t>
+          <t>Publicação</t>
         </is>
       </c>
     </row>
@@ -8280,17 +8280,17 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Proving Properties Of Binary Classification Neural Networks Via ?ukasiewicz Logic." Logic Journal Of The Igpl</t>
+          <t>Casanova, Edresson, Arnaldo Candido Junior, Christopher Shulby, Frederico Santos de Oliveira, João Paulo Teixeira, Moacir Antonelli Ponti, And Sandra Aluísio. "tts-portuguese Corpus: A Corpus For Speech Synthesis In Brazilian Portuguese." Language Resources And Evaluation (lrec’22) (2022): 1-13.[3 Citação]</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Preto, Sandro, And Marcelo Finger</t>
+          <t>Casanova, Edresson, Arnaldo Candido Junior, Christopher Shulby, Frederico Santos de Oliveira, João Paulo Teixeira, Moacir Antonelli Ponti, And Sandra Aluísio</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Publicação</t>
+          <t>Citação</t>
         </is>
       </c>
     </row>
@@ -8305,12 +8305,12 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Shallow Parsing Of Portuguese Texts Annotated Under Universal Dependencies." In Procedings Of The Universal Dependencies Brazilian Festival, Pp. 1-8.</t>
+          <t>Proving Properties Of Binary Classification Neural Networks Via ?ukasiewicz Logic." Logic Journal Of The Igpl</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Oliveira, Guilherme Martiniano, Paulo Berlanga Neto, And Evandro Eduardo Seron Ruiz</t>
+          <t>Preto, Sandro, And Marcelo Finger</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -8330,17 +8330,17 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>"pir\'a: A Bilingual Portuguese-english Dataset For Question-answering About The Ocean." Arxiv Preprint Arxiv:2202.02398 (2022).[5 Citação]</t>
+          <t>Shallow Parsing Of Portuguese Texts Annotated Under Universal Dependencies." In Procedings Of The Universal Dependencies Brazilian Festival, Pp. 1-8.</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Paschoal, André Fa, Paulo Pirozelli, Valdinei Freire, Karina V. Delgado, Sarajane M. Peres, Marcos M. José, Flávio Nakasato Et Al</t>
+          <t>Oliveira, Guilherme Martiniano, Paulo Berlanga Neto, And Evandro Eduardo Seron Ruiz</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Citação</t>
+          <t>Publicação</t>
         </is>
       </c>
     </row>
@@ -8355,17 +8355,17 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>"verbert: Automating Brazilian Case Law Document Multi-label Categorization Using Bert." Arxiv Preprint Arxiv:2203.06224</t>
+          <t>"pir\'a: A Bilingual Portuguese-english Dataset For Question-answering About The Ocean." Arxiv Preprint Arxiv:2202.02398 (2022).[5 Citação]</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Serras, Felipe R., And Marcelo Finger</t>
+          <t>Paschoal, André Fa, Paulo Pirozelli, Valdinei Freire, Karina V. Delgado, Sarajane M. Peres, Marcos M. José, Flávio Nakasato Et Al</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Publicação</t>
+          <t>Citação</t>
         </is>
       </c>
     </row>
@@ -8380,12 +8380,12 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>"pretrained Audio Neural Networks For Speech Emotion Recognition In Portuguese." (2022). In Proceedings Of The First Workshop On Automatic Speech Recognition For Spontaneous And Prepared Speech - Speech Emotion Recognition In Portuguese (ser 2022), Co-located With Propor 2022. March 21st</t>
+          <t>"verbert: Automating Brazilian Case Law Document Multi-label Categorization Using Bert." Arxiv Preprint Arxiv:2203.06224</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Gauy, Marcelo Matheus, And Marcelo Finger</t>
+          <t>Serras, Felipe R., And Marcelo Finger</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Transfer Learning And Data Augmentation Techniques Applied To Speech Emotion Recognition In Se&amp;r 2022". In The Proceedings Of The First Workshop On Automatic Speech Recognition For Spontaneous And Prepared Speech &amp; Speech Emotion Recognition In Portuguese, Co-located With Propor 2022. March 21st, 2022 (online). Vol. 1, Pp. 25-36, https://sites.google.com/view/ser2022/</t>
+          <t>"pretrained Audio Neural Networks For Speech Emotion Recognition In Portuguese." (2022). In Proceedings Of The First Workshop On Automatic Speech Recognition For Spontaneous And Prepared Speech - Speech Emotion Recognition In Portuguese (ser 2022), Co-located With Propor 2022. March 21st</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Alves, Caroline, Bruno Carlotto, Bruno Dias, Anátale Garcia, Bruno Gianesi, Renan Izaias, Maria Luiza Morais, Paula Oliveira, Vinícius G. Santos, Rafael Sicoli, Flaviane R. Fernandes Svartman, Sandra Aluísio &amp; Sidney Leal</t>
+          <t>Gauy, Marcelo Matheus, And Marcelo Finger</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -8430,12 +8430,12 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>"speech Emotion Recognition In Portuguese For Sofiafala: Ser Sofiafala". In The Proceedings Of The First Workshop On Automatic Speech Recognition For Spontaneous And Prepared Speech &amp; Speech Emotion Recognition In Portuguese, Co-located With Propor 2022. March 21st, 2022 (online). Vol. 1, Pp. 37-41, 2022 https://sites.google.com/view/ser2022/</t>
+          <t>Transfer Learning And Data Augmentation Techniques Applied To Speech Emotion Recognition In Se&amp;r 2022". In The Proceedings Of The First Workshop On Automatic Speech Recognition For Spontaneous And Prepared Speech &amp; Speech Emotion Recognition In Portuguese, Co-located With Propor 2022. March 21st, 2022 (online). Vol. 1, Pp. 25-36, https://sites.google.com/view/ser2022/</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Scaranti, Alexander, Douglas Silva, Fernando Meloni &amp; Alessandra Alaniz</t>
+          <t>Alves, Caroline, Bruno Carlotto, Bruno Dias, Anátale Garcia, Bruno Gianesi, Renan Izaias, Maria Luiza Morais, Paula Oliveira, Vinícius G. Santos, Rafael Sicoli, Flaviane R. Fernandes Svartman, Sandra Aluísio &amp; Sidney Leal</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Multimodal Representation Learning Over Heterogeneous Networks For Tag-based Music Retrieval." Expert Systems With Applications, P.117969. https://doi.org/10.1016/j.eswa.2022.117969</t>
+          <t>"speech Emotion Recognition In Portuguese For Sofiafala: Ser Sofiafala". In The Proceedings Of The First Workshop On Automatic Speech Recognition For Spontaneous And Prepared Speech &amp; Speech Emotion Recognition In Portuguese, Co-located With Propor 2022. March 21st, 2022 (online). Vol. 1, Pp. 37-41, 2022 https://sites.google.com/view/ser2022/</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>da Silva, A.c.m., Silva, D.f. And Marcacini, R.m., 2022</t>
+          <t>Scaranti, Alexander, Douglas Silva, Fernando Meloni &amp; Alessandra Alaniz</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -8480,17 +8480,17 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>"opinion Mining For App Reviews: An Analysis Of Textual Representation And Predictive Models." Automated Software Engineering, 29(1), Pp.1-30. [3 Citação] https://doi.org/10.1007/s10515-021-00301-1</t>
+          <t>Multimodal Representation Learning Over Heterogeneous Networks For Tag-based Music Retrieval." Expert Systems With Applications, P.117969. https://doi.org/10.1016/j.eswa.2022.117969</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Araujo, A.f., Gôlo, M.p. And Marcacini, R.m.,</t>
+          <t>da Silva, A.c.m., Silva, D.f. And Marcacini, R.m., 2022</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Citação</t>
+          <t>Publicação</t>
         </is>
       </c>
     </row>
@@ -8505,17 +8505,17 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>"temporal Dynamics Of Requirements Engineering From Mobile App Reviews." Peerj Computer Science, 8, P.e874. https://peerj.com/articles/cs-874/</t>
+          <t>"opinion Mining For App Reviews: An Analysis Of Textual Representation And Predictive Models." Automated Software Engineering, 29(1), Pp.1-30. [3 Citação] https://doi.org/10.1007/s10515-021-00301-1</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>de Lima, V.m.a., de Araújo, A.f. And Marcacini, R.m., 2022.</t>
+          <t>Araujo, A.f., Gôlo, M.p. And Marcacini, R.m.,</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Publicação</t>
+          <t>Citação</t>
         </is>
       </c>
     </row>
@@ -8530,12 +8530,12 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Análise Semântica Com Base Em Amr Para O Português. Linguamática, Vol. 14, N. 1, Pp. 33-48 https://linguamatica.com/index.php/linguamatica/article/view/358</t>
+          <t>"temporal Dynamics Of Requirements Engineering From Mobile App Reviews." Peerj Computer Science, 8, P.e874. https://peerj.com/articles/cs-874/</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Anchiêta, R.t. And Pardo, T.a.s.</t>
+          <t>de Lima, V.m.a., de Araújo, A.f. And Marcacini, R.m., 2022.</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Building Contrastive Summaries Of Subjective Text Via Opinion Ranking. Revista de Informática Teórica e Aplicada (rita), Vol. 29, N. 2, Pp. 11-34 https://seer.ufrgs.br/index.php/rita/article/view/118372</t>
+          <t>Análise Semântica Com Base Em Amr Para O Português. Linguamática, Vol. 14, N. 1, Pp. 33-48 https://linguamatica.com/index.php/linguamatica/article/view/358</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Silva, R.r. And Pardo, T.a.s.</t>
+          <t>Anchiêta, R.t. And Pardo, T.a.s.</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Building Contrastive Summaries Of Subjective Text Via Opinion Ranking. Revista de Informática Teórica e Aplicada (rita), Vol. 29, N. 2, Pp. 11-34 http://journal.sepln.org/sepln/ojs/ojs/index.php/pln/article/view/6408</t>
+          <t>Building Contrastive Summaries Of Subjective Text Via Opinion Ranking. Revista de Informática Teórica e Aplicada (rita), Vol. 29, N. 2, Pp. 11-34 https://seer.ufrgs.br/index.php/rita/article/view/118372</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Sobrevilla Cabezudo, M.a. And Pardo, T.a.s.</t>
+          <t>Silva, R.r. And Pardo, T.a.s.</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Evaluating Content Features And Classification Methods For Helpfulness Prediction Of Online Reviews: Establishing A Benchmark For Portuguese. In The Proceedings Of The 12th Workshop On Computational Approaches To Subjectivity, Sentiment &amp; Social Media Analysis (wassa), Pp. 204-213. May, 26 https://aclanthology.org/2022.wassa-1.19/</t>
+          <t>Building Contrastive Summaries Of Subjective Text Via Opinion Ranking. Revista de Informática Teórica e Aplicada (rita), Vol. 29, N. 2, Pp. 11-34 http://journal.sepln.org/sepln/ojs/ojs/index.php/pln/article/view/6408</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Sousa, R.f. And Pardo, T.a.s.</t>
+          <t>Sobrevilla Cabezudo, M.a. And Pardo, T.a.s.</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Shallow Parsing Of Portuguese Texts Annotated Under Universal Dependencies. In The Proceedings Of The Universal Dependencies Brazilian Festival (udfest-br), Pp. 1-8. March, 21. https://aclanthology.org/2022.udfestbr-1.4/</t>
+          <t>Evaluating Content Features And Classification Methods For Helpfulness Prediction Of Online Reviews: Establishing A Benchmark For Portuguese. In The Proceedings Of The 12th Workshop On Computational Approaches To Subjectivity, Sentiment &amp; Social Media Analysis (wassa), Pp. 204-213. May, 26 https://aclanthology.org/2022.wassa-1.19/</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Oliveira, G.m.; Berlanga Neto, P.; Ruiz, E.e.r.</t>
+          <t>Sousa, R.f. And Pardo, T.a.s.</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Que Simples Que Nada: A Anotação da Palavra Que Em Córpus de Ud. In The Proceedings Of The Universal Dependencies Brazilian Festival (udfest-br), Pp. 1-11. March, 21 https://aclanthology.org/2022.udfestbr-1.3/</t>
+          <t>Shallow Parsing Of Portuguese Texts Annotated Under Universal Dependencies. In The Proceedings Of The Universal Dependencies Brazilian Festival (udfest-br), Pp. 1-8. March, 21. https://aclanthology.org/2022.udfestbr-1.4/</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Duran, M.s.; Oliveira, H.; Scandarolli, C.</t>
+          <t>Oliveira, G.m.; Berlanga Neto, P.; Ruiz, E.e.r.</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Udconcord: A Concordancer For Universal Dependencies Treebanks. In The Proceedings Of The Universal Dependencies Brazilian Festival (udfest-br), Pp. 1-10. March, 21 https://aclanthology.org/2022.udfestbr-1.6/</t>
+          <t>Que Simples Que Nada: A Anotação da Palavra Que Em Córpus de Ud. In The Proceedings Of The Universal Dependencies Brazilian Festival (udfest-br), Pp. 1-11. March, 21 https://aclanthology.org/2022.udfestbr-1.3/</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Miranda, L.g.m. And Pardo, T.a.s.</t>
+          <t>Duran, M.s.; Oliveira, H.; Scandarolli, C.</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>An Improved And Extended Annotation Tool For Universal Dependencies-based Treebank Construction. In The Proceedings Of The Propor Demonstrations Workshop, Pp. 1-3. March, 21-23 https://drive.google.com/file/d/1gz9k3- Su72zxx6v2a0ltruthvatpumux/view</t>
+          <t>Udconcord: A Concordancer For Universal Dependencies Treebanks. In The Proceedings Of The Universal Dependencies Brazilian Festival (udfest-br), Pp. 1-10. March, 21 https://aclanthology.org/2022.udfestbr-1.6/</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Abstract Meaning Representation Parsing For The Brazilian Portuguese Language. In The Proceedings Of The International Conference On Computational Processing Of Portuguese (propor) (lnai 13208), Pp. 429-434. March, 21-23 https://link.springer.com/chapter/10.1007/978-3-030-98305-5_41</t>
+          <t>An Improved And Extended Annotation Tool For Universal Dependencies-based Treebank Construction. In The Proceedings Of The Propor Demonstrations Workshop, Pp. 1-3. March, 21-23 https://drive.google.com/file/d/1gz9k3- Su72zxx6v2a0ltruthvatpumux/view</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Anchiêta, R.t. And Pardo, T.a.s.</t>
+          <t>Miranda, L.g.m. And Pardo, T.a.s.</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -8755,17 +8755,17 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Implicit Opinion Aspect Clues In Portuguese Texts: Analysis And Categorization. In The Proceedings Of The International Conference On Computational Processing Of Portuguese (propor) (lnai 13208), Pp. 68-78. March, 21-23..[1 Citation] https://link.springer.com/chapter/10.1007/978-3-030-98305-5_7</t>
+          <t>Abstract Meaning Representation Parsing For The Brazilian Portuguese Language. In The Proceedings Of The International Conference On Computational Processing Of Portuguese (propor) (lnai 13208), Pp. 429-434. March, 21-23 https://link.springer.com/chapter/10.1007/978-3-030-98305-5_41</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Machado, M.t.; Pardo, T.a.s.; Ruiz, E.e.s.; Di Felippo, A.; Vargas, F.</t>
+          <t>Anchiêta, R.t. And Pardo, T.a.s.</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Citação</t>
+          <t>Publicação</t>
         </is>
       </c>
     </row>
@@ -8780,17 +8780,17 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Coraa Asr: A Large Corpus Of Spontaneous And Prepared Speech Manually Validated For Speech Recognition In Brazilian Portuguese. Lang Resources &amp; Evaluation. https://doi.org/10.1007/s10579-022-09621-4</t>
+          <t>Implicit Opinion Aspect Clues In Portuguese Texts: Analysis And Categorization. In The Proceedings Of The International Conference On Computational Processing Of Portuguese (propor) (lnai 13208), Pp. 68-78. March, 21-23..[1 Citation] https://link.springer.com/chapter/10.1007/978-3-030-98305-5_7</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Candido Junior, A.; Casanova, E.; Soares, A. Et Al. (2022)</t>
+          <t>Machado, M.t.; Pardo, T.a.s.; Ruiz, E.e.s.; Di Felippo, A.; Vargas, F.</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Revista Internacional</t>
+          <t>Citação</t>
         </is>
       </c>
     </row>
@@ -8805,17 +8805,17 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Manual de Anotação Como Recurso de Processamento de Linguagem Natural: O Modelo Universal Dependencies Em Língua Portuguesa. Domínios de Linguagem, Vol. 16, N. 4, Pp. 1608-1643.</t>
+          <t>Coraa Asr: A Large Corpus Of Spontaneous And Prepared Speech Manually Validated For Speech Recognition In Brazilian Portuguese. Lang Resources &amp; Evaluation. https://doi.org/10.1007/s10579-022-09621-4</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Duran, M.s.; Nunes, M.g.v.; Lopes, L.; Pardo, T.a.s. (2022)</t>
+          <t>Candido Junior, A.; Casanova, E.; Soares, A. Et Al. (2022)</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Revista Nacional</t>
+          <t>Revista Internacional</t>
         </is>
       </c>
     </row>
@@ -8830,12 +8830,12 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Bases Lexicais Verbais do Português Brasileiro. Domínios de Linguagem, Vol. 16, N. 4, Pp. 1489-1516.</t>
+          <t>Manual de Anotação Como Recurso de Processamento de Linguagem Natural: O Modelo Universal Dependencies Em Língua Portuguesa. Domínios de Linguagem, Vol. 16, N. 4, Pp. 1608-1643.</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Rodrigues, R.; Lemos-couto, M.; Coelho, F.l.; Miranda Jr., I.s.; Vale, O. (2022)</t>
+          <t>Duran, M.s.; Nunes, M.g.v.; Lopes, L.; Pardo, T.a.s. (2022)</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -8855,17 +8855,17 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Heterogeneous Graph Neural Network For Music Emotion Recognition. In The Proceedings Of The 23rd International Society For Music Information Retrieval Conference (ismir).</t>
+          <t>Bases Lexicais Verbais do Português Brasileiro. Domínios de Linguagem, Vol. 16, N. 4, Pp. 1489-1516.</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Mendes da Silva, A.c.; Silva, D.f.; Marcacini, R.m. (2022)</t>
+          <t>Rodrigues, R.; Lemos-couto, M.; Coelho, F.l.; Miranda Jr., I.s.; Vale, O. (2022)</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Conferência Internacional</t>
+          <t>Revista Nacional</t>
         </is>
       </c>
     </row>
@@ -8880,12 +8880,12 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Transfer Learning With Joint Fine-tuning For Ultimodal Sentiment Analysis. In The Proceedings Of The Latinx Workshop At The Thirty-ninth International Conference On Machine Learning (latinx @icml 2022).</t>
+          <t>Heterogeneous Graph Neural Network For Music Emotion Recognition. In The Proceedings Of The 23rd International Society For Music Information Retrieval Conference (ismir).</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Toledo, G.l.; Marcacini, R.m. (2022)</t>
+          <t>Mendes da Silva, A.c.; Silva, D.f.; Marcacini, R.m. (2022)</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Sentence Similarity Recognition In Portuguese From Multiple Embedding Models. In The Proceedings Of The 21st Ieee International Conference On Machine Learning And Applications (icmla), Pp. 154-159.</t>
+          <t>Transfer Learning With Joint Fine-tuning For Ultimodal Sentiment Analysis. In The Proceedings Of The Latinx Workshop At The Thirty-ninth International Conference On Machine Learning (latinx @icml 2022).</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Rodrigues A.c.; Marcacini R.m. (2022)</t>
+          <t>Toledo, G.l.; Marcacini, R.m. (2022)</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Exploring A Pos-based Two Stage Approach For Improving Low-resource Amr-to-text Generation. In The Proceedings Of The 2nd Workshop On Natural Language Generation, Evaluation, And Metrics (gem), Pp. 531-538.</t>
+          <t>Sentence Similarity Recognition In Portuguese From Multiple Embedding Models. In The Proceedings Of The 21st Ieee International Conference On Machine Learning And Applications (icmla), Pp. 154-159.</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Sobrevilla Cabezudo, M.a.; Pardo, T.a.s. (2022)</t>
+          <t>Rodrigues A.c.; Marcacini R.m. (2022)</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Nilc At Absapt 2022: Aspect Extraction For Portuguese. In The Proceedings Of The Iberlef Shared Task On Aspect-based Sentiment Analysis In Portuguese (absapt), Pp. 1-10.</t>
+          <t>Exploring A Pos-based Two Stage Approach For Improving Low-resource Amr-to-text Generation. In The Proceedings Of The 2nd Workshop On Natural Language Generation, Evaluation, And Metrics (gem), Pp. 531-538.</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Machado, M.t.; Pardo, T.a.s. (2022)</t>
+          <t>Sobrevilla Cabezudo, M.a.; Pardo, T.a.s. (2022)</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -8980,12 +8980,12 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Coraa Nurc-sp Minimal Corpus: A Manually Annotated Corpus Of Brazilian Portuguese Spontaneous Speech. In The Proceedings Of Iberspeech, Pp. 161-165.</t>
+          <t>Nilc At Absapt 2022: Aspect Extraction For Portuguese. In The Proceedings Of The Iberlef Shared Task On Aspect-based Sentiment Analysis In Portuguese (absapt), Pp. 1-10.</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Santos, V.g.; Alves, C.a.; Carlotto, B.b.; Papa Dias, B.a.; Stefanel Gris, L.r.; Lima Izaias, R.d.; Azevedo de Morais, M.l.; Marin de Oliveira, P.; Sicoli, R.; Svartman, F.r.f.; Leite, M.q.; Alu´isio, S.m. (2022)</t>
+          <t>Machado, M.t.; Pardo, T.a.s. (2022)</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Bringing Nurc/sp To Digital Life: The Role Of Open-source Automatic Speech Recognition Models. In The Proceedings Of The Xix Encontro Nacional de Inteligência Artificial (eniac), Pp. 330-341.</t>
+          <t>Coraa Nurc-sp Minimal Corpus: A Manually Annotated Corpus Of Brazilian Portuguese Spontaneous Speech. In The Proceedings Of Iberspeech, Pp. 161-165.</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Gris, L.r.s.; Candido Junior, A.; Santos, V.g.; Dias, B.a.p.; Leite, M.q.; Svartman, F.r.f.; Aluisio, S.m. (2022)</t>
+          <t>Santos, V.g.; Alves, C.a.; Carlotto, B.b.; Papa Dias, B.a.; Stefanel Gris, L.r.; Lima Izaias, R.d.; Azevedo de Morais, M.l.; Marin de Oliveira, P.; Sicoli, R.; Svartman, F.r.f.; Leite, M.q.; Alu´isio, S.m. (2022)</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -9030,17 +9030,17 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Video Summarization Using Text Subjectivity Classification. In Proceedings Of The Brazilian Symposium On Multimedia And The Web, Pp. 133-141.</t>
+          <t>Bringing Nurc/sp To Digital Life: The Role Of Open-source Automatic Speech Recognition Models. In The Proceedings Of The Xix Encontro Nacional de Inteligência Artificial (eniac), Pp. 330-341.</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Moraes, L.; Ricardo Marcondes Marcacini; Goularte, R. (2022)</t>
+          <t>Gris, L.r.s.; Candido Junior, A.; Santos, V.g.; Dias, B.a.p.; Leite, M.q.; Svartman, F.r.f.; Aluisio, S.m. (2022)</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Conferência Nacional</t>
+          <t>Conferência Internacional</t>
         </is>
       </c>
     </row>
@@ -9055,12 +9055,12 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Investigating Lexical Np-chunking With Universal Dependencies For Portuguese. In The Proceedings Of The 19th National Meeting On Artificial And Computational Intelligence (eniac), Pp. 342-351. November, 28 To December, 01.</t>
+          <t>Video Summarization Using Text Subjectivity Classification. In Proceedings Of The Brazilian Symposium On Multimedia And The Web, Pp. 133-141.</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Souza, A. And Ruiz, E. (2022)</t>
+          <t>Moraes, L.; Ricardo Marcondes Marcacini; Goularte, R. (2022)</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>How Aspects Of Similar Datasets Can Impact Distributional Models. In The Proceedings Of The 19th National Meeting On Artificial And Computational Intelligence (eniac), Pp. 579-590. November, 28 To December, 01.</t>
+          <t>Investigating Lexical Np-chunking With Universal Dependencies For Portuguese. In The Proceedings Of The 19th National Meeting On Artificial And Computational Intelligence (eniac), Pp. 342-351. November, 28 To December, 01.</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Gomes, I.a. And Roman, N. (2022)</t>
+          <t>Souza, A. And Ruiz, E. (2022)</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Generalizing Over Data Sets: A Preliminary Study With Bert For Natural Language Inference. In The Proceedings Of The 19th National Meeting On Artificial And Computational Intelligence (eniac), Pp. 602-611. November, 28 To December, 01.</t>
+          <t>How Aspects Of Similar Datasets Can Impact Distributional Models. In The Proceedings Of The 19th National Meeting On Artificial And Computational Intelligence (eniac), Pp. 579-590. November, 28 To December, 01.</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Nanclarez, R.; Roman, N.; Silva, F. (2022)</t>
+          <t>Gomes, I.a. And Roman, N. (2022)</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -9130,17 +9130,17 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Manual de Anotação de Relações de Dependência – Versão Revisada e Estendida: Orientações Para Anotação de Relações de Dependência Sintática Em Língua Portuguesa, Seguindo As Diretrizes da Abordagem Universal Dependencies (ud). Relatório Técnico do Icmc 440. Instituto de Ciências Matemáticas e de Computação, Universidade de São Paulo. São Carlos-sp, Outubro, 166p.</t>
+          <t>Generalizing Over Data Sets: A Preliminary Study With Bert For Natural Language Inference. In The Proceedings Of The 19th National Meeting On Artificial And Computational Intelligence (eniac), Pp. 602-611. November, 28 To December, 01.</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Duran, M.s. (2022)</t>
+          <t>Nanclarez, R.; Roman, N.; Silva, F. (2022)</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Outros (relatórios Técnicos, Capítulos de Livros Etc.)</t>
+          <t>Conferência Nacional</t>
         </is>
       </c>
     </row>
@@ -9151,21 +9151,21 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Efficient Representation Of Piecewise Linear Functions Into ?ukasiewicz Logic Modulo Satisfiability." Mathematical Structures In Computer Science (2022): 1-26.[1 Citation]</t>
+          <t>Manual de Anotação de Relações de Dependência – Versão Revisada e Estendida: Orientações Para Anotação de Relações de Dependência Sintática Em Língua Portuguesa, Seguindo As Diretrizes da Abordagem Universal Dependencies (ud). Relatório Técnico do Icmc 440. Instituto de Ciências Matemáticas e de Computação, Universidade de São Paulo. São Carlos-sp, Outubro, 166p.</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Preto, Sandro, And Marcelo Finger</t>
+          <t>Duran, M.s. (2022)</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Citação</t>
+          <t>Outros (relatórios Técnicos, Capítulos de Livros Etc.)</t>
         </is>
       </c>
     </row>
@@ -9180,17 +9180,17 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Descrição Preliminar do Corpus Dantestocks: Diretrizes de Segmentação Para Anotação Segundo Universal Dependencies." In Anais do Xiii Simpósio Brasileiro de Tecnologia da Informação e da Linguagem Humana, Pp. 335-343. Sbc, 2021.</t>
+          <t>Efficient Representation Of Piecewise Linear Functions Into ?ukasiewicz Logic Modulo Satisfiability." Mathematical Structures In Computer Science (2022): 1-26.[1 Citation]</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Di Felippo, Ariani, Caroline Postali, Gabriel Ceregatto, Laura S. Gazana, Emanuel H. da Silva, Norton T. Roman, And Thiago As Pardo</t>
+          <t>Preto, Sandro, And Marcelo Finger</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Publicação</t>
+          <t>Citação</t>
         </is>
       </c>
     </row>
@@ -9205,17 +9205,17 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Universal Dependencies-based Pos Tagging Refinement Through Linguistic Resources." In Brazilian Conference On Intelligent Systems, Pp. 601-615. Springer, Cham, 2021.[2 Citação]</t>
+          <t>Descrição Preliminar do Corpus Dantestocks: Diretrizes de Segmentação Para Anotação Segundo Universal Dependencies." In Anais do Xiii Simpósio Brasileiro de Tecnologia da Informação e da Linguagem Humana, Pp. 335-343. Sbc, 2021.</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Lopes, Lucelene, Magali S. Duran, And Thiago As Pardo</t>
+          <t>Di Felippo, Ariani, Caroline Postali, Gabriel Ceregatto, Laura S. Gazana, Emanuel H. da Silva, Norton T. Roman, And Thiago As Pardo</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Citação</t>
+          <t>Publicação</t>
         </is>
       </c>
     </row>
@@ -9230,17 +9230,17 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Inteligência Artificial e Os Rumos do Processamento do Português Brasileiro." Estudos Avançados 35 (2021): 51-72.</t>
+          <t>Universal Dependencies-based Pos Tagging Refinement Through Linguistic Resources." In Brazilian Conference On Intelligent Systems, Pp. 601-615. Springer, Cham, 2021.[2 Citação]</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Finger, Marcelo</t>
+          <t>Lopes, Lucelene, Magali S. Duran, And Thiago As Pardo</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Publicação</t>
+          <t>Citação</t>
         </is>
       </c>
     </row>
@@ -9255,17 +9255,17 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Monte-serrat, Dionéia Motta, Mateus Tarcinalli Machado, And Evandro Eduardo Seron Ruiz. "a Machine Learning Approach To Literary Genre Classification On Portuguese Texts: Circumventing Nlp’s Standard Varieties." In Anais do Xiii Simpósio Brasileiro de Tecnologia da Informação e da Linguagem Humana, Pp. 255-264. Sbc, 2021.[1 Citation]</t>
+          <t>Inteligência Artificial e Os Rumos do Processamento do Português Brasileiro." Estudos Avançados 35 (2021): 51-72.</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Monte-serrat, Dionéia Motta, Mateus Tarcinalli Machado, And Evandro Eduardo Seron Ruiz</t>
+          <t>Finger, Marcelo</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Citação</t>
+          <t>Publicação</t>
         </is>
       </c>
     </row>
@@ -9280,17 +9280,17 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>"coraa: A Large Corpus Of Spontaneous And Prepared Speech Manually Validated For Speech Recognition In Brazilian Portuguese." Arxiv Preprint Arxiv:2110.15731</t>
+          <t>Monte-serrat, Dionéia Motta, Mateus Tarcinalli Machado, And Evandro Eduardo Seron Ruiz. "a Machine Learning Approach To Literary Genre Classification On Portuguese Texts: Circumventing Nlp’s Standard Varieties." In Anais do Xiii Simpósio Brasileiro de Tecnologia da Informação e da Linguagem Humana, Pp. 255-264. Sbc, 2021.[1 Citation]</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Junior, Arnaldo Candido, Edresson Casanova, Anderson Soares, Frederico Santos de Oliveira, Lucas Oliveira, Ricardo Corso Fernandes Junior, Daniel Peixoto Pinto da Silva Et Al</t>
+          <t>Monte-serrat, Dionéia Motta, Mateus Tarcinalli Machado, And Evandro Eduardo Seron Ruiz</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Publicação</t>
+          <t>Citação</t>
         </is>
       </c>
     </row>
@@ -9305,12 +9305,12 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>"multimodal Intent Classification With Incomplete Modalities Using Text Embedding Propagation." In Proceedings Of The Brazilian Symposium On Multimedia And The Web (pp. 217-220) https://dl.acm.org/doi/10.1145/3470482.3479636</t>
+          <t>"coraa: A Large Corpus Of Spontaneous And Prepared Speech Manually Validated For Speech Recognition In Brazilian Portuguese." Arxiv Preprint Arxiv:2110.15731</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Gonzaga, V.m., Murrugarra-llerena, N. And Marcacini, R., 2021, November</t>
+          <t>Junior, Arnaldo Candido, Edresson Casanova, Anderson Soares, Frederico Santos de Oliveira, Lucas Oliveira, Ricardo Corso Fernandes Junior, Daniel Peixoto Pinto da Silva Et Al</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>"hierarchical Cluster Labeling Of Software Requirements Using Contextual Word Embeddings." In Brazilian Symposium On Software Engineering (pp. 297-302). https://dl.acm.org/doi/10.1145/3474624.3477067</t>
+          <t>"multimodal Intent Classification With Incomplete Modalities Using Text Embedding Propagation." In Proceedings Of The Brazilian Symposium On Multimedia And The Web (pp. 217-220) https://dl.acm.org/doi/10.1145/3470482.3479636</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Araujo, A. And Marcacini, R., 2021, September</t>
+          <t>Gonzaga, V.m., Murrugarra-llerena, N. And Marcacini, R., 2021, November</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -9355,12 +9355,12 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Instance Selection For Music Genre Classification Using Heterogeneous Networks." In Anais do Xviii Simpósio Brasileiro de Computação Musical (pp. 8-16). Sbc. https://sol.sbc.org.br/index.php/sbcm/article/view/19419</t>
+          <t>"hierarchical Cluster Labeling Of Software Requirements Using Contextual Word Embeddings." In Brazilian Symposium On Software Engineering (pp. 297-302). https://dl.acm.org/doi/10.1145/3474624.3477067</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>da Silva, A.c.m., do Carmo, P.r.v., Marcacini, R.m. And Silva, D.f., 2021,</t>
+          <t>Araujo, A. And Marcacini, R., 2021, September</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -9380,12 +9380,12 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>A Heterogeneous Network-based Positive And Unlabeled Learning Approach To Detect Fake News." In The Brazilian Conference On Intelligent Systems (pp. 3-18). Springer, Cham. https://sol.sbc.org.br/index.php/bracis/article/view/19054</t>
+          <t>Instance Selection For Music Genre Classification Using Heterogeneous Networks." In Anais do Xviii Simpósio Brasileiro de Computação Musical (pp. 8-16). Sbc. https://sol.sbc.org.br/index.php/sbcm/article/view/19419</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Souza, M.c.d., Nogueira, B.m., Rossi, R.g., Marcacini, R.m. And Solange Rezende;, 2021, November.</t>
+          <t>da Silva, A.c.m., do Carmo, P.r.v., Marcacini, R.m. And Silva, D.f., 2021,</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>On Auxiliary Verb In Universal Dependencies: Untangling The Issue And Proposing A Systematized Annotation Strategy. In The Proceedings Of The Sixth International Conference On Dependency Linguistics (depling), Pp. 10-21. March, 22-23, https://aclanthology.org/2021.depling-1.2/</t>
+          <t>A Heterogeneous Network-based Positive And Unlabeled Learning Approach To Detect Fake News." In The Brazilian Conference On Intelligent Systems (pp. 3-18). Springer, Cham. https://sol.sbc.org.br/index.php/bracis/article/view/19054</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Duran, M.s.; Rassi, A.p.; Pagano, A.s.; Pardo, T.a.s.</t>
+          <t>Souza, M.c.d., Nogueira, B.m., Rossi, R.g., Marcacini, R.m. And Solange Rezende;, 2021, November.</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -9430,17 +9430,17 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>The Challenges Of Modeling And Predicting Online Review Helpfulness. In The Proceedings Of The 18th National Meeting On Artificial And Computational Intelligence (eniac), Pp. 727-738. November, 29 To December, 3.[4 Citação] https://sol.sbc.org.br/index.php/eniac/article/view/18298/18132</t>
+          <t>On Auxiliary Verb In Universal Dependencies: Untangling The Issue And Proposing A Systematized Annotation Strategy. In The Proceedings Of The Sixth International Conference On Dependency Linguistics (depling), Pp. 10-21. March, 22-23, https://aclanthology.org/2021.depling-1.2/</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Sousa, R.f. And Pardo, T.a.s</t>
+          <t>Duran, M.s.; Rassi, A.p.; Pagano, A.s.; Pardo, T.a.s.</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Citação</t>
+          <t>Publicação</t>
         </is>
       </c>
     </row>
@@ -9455,17 +9455,17 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Universal Dependencies For Tweets In Brazilian Portuguese: Tokenization And Part Of Speech Tagging. In The Proceedings Of The 18th National Meeting On Artificial And Computational Intelligence (eniac), Pp. 434-445. November, 29 To December, https://sol.sbc.org.br/index.php/eniac/article/view/18273/18107</t>
+          <t>The Challenges Of Modeling And Predicting Online Review Helpfulness. In The Proceedings Of The 18th National Meeting On Artificial And Computational Intelligence (eniac), Pp. 727-738. November, 29 To December, 3.[4 Citação] https://sol.sbc.org.br/index.php/eniac/article/view/18298/18132</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Silva, E.h.; Pardo, T.a.s.; Roman, N.t.; Di Felippo, A.</t>
+          <t>Sousa, R.f. And Pardo, T.a.s</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Publicação</t>
+          <t>Citação</t>
         </is>
       </c>
     </row>
@@ -9480,12 +9480,12 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Descrição de Numerais Segundo Modelo Universal Dependencies e Sua Anotação No Português. In The Proceedings Of The Vii Workshop On Portuguese Description (jdp), Pp. 344-352. December, 1 https://sol.sbc.org.br/index.php/stil/article/view/17814/17648</t>
+          <t>Universal Dependencies For Tweets In Brazilian Portuguese: Tokenization And Part Of Speech Tagging. In The Proceedings Of The 18th National Meeting On Artificial And Computational Intelligence (eniac), Pp. 434-445. November, 29 To December, https://sol.sbc.org.br/index.php/eniac/article/view/18273/18107</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Duran, M.s.; Lopes, L.; Pardo, T.a.s</t>
+          <t>Silva, E.h.; Pardo, T.a.s.; Roman, N.t.; Di Felippo, A.</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>A Propósito do Verbo Falar No Português Brasileiro: Uma Análise Em Corpus e Em Bases de Dados Verbais. In The Proceedings Of The Vii Workshop On Portuguese Description (jdp), Pp. 315-324. December https://sol.sbc.org.br/index.php/stil/article/view/17811/17645</t>
+          <t>Descrição de Numerais Segundo Modelo Universal Dependencies e Sua Anotação No Português. In The Proceedings Of The Vii Workshop On Portuguese Description (jdp), Pp. 344-352. December, 1 https://sol.sbc.org.br/index.php/stil/article/view/17814/17648</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Miranda Junior, I.s.; Couto, M.m.l.; Coelho, F.l.; Rodrigues, R.; Vale, O.</t>
+          <t>Duran, M.s.; Lopes, L.; Pardo, T.a.s</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -9530,12 +9530,12 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Complexidade Textual Em Notícias Satíricas: Uma Análise Para O Português do Brasil. In The Proceedings Of The Vii Workshop On Portuguese Description (jdp), Pp. 409-415. December, 1 https://sol.sbc.org.br/index.php/stil/article/view/17821/17655</t>
+          <t>A Propósito do Verbo Falar No Português Brasileiro: Uma Análise Em Corpus e Em Bases de Dados Verbais. In The Proceedings Of The Vii Workshop On Portuguese Description (jdp), Pp. 315-324. December https://sol.sbc.org.br/index.php/stil/article/view/17811/17645</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Wick-pedro, G. And Santos, R.l.s.</t>
+          <t>Miranda Junior, I.s.; Couto, M.m.l.; Coelho, F.l.; Rodrigues, R.; Vale, O.</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Avaliação de Parsers Na Detecção de Relações Essenciais do Modelo Universal Dependencies Para O Português. In The Proceedings Of The Vii Student Workshop On Information And Human Language Technology (tilic), Pp. 442-446. November, 30 https://sol.sbc.org.br/index.php/stil/article/view/17826/17660</t>
+          <t>Complexidade Textual Em Notícias Satíricas: Uma Análise Para O Português do Brasil. In The Proceedings Of The Vii Workshop On Portuguese Description (jdp), Pp. 409-415. December, 1 https://sol.sbc.org.br/index.php/stil/article/view/17821/17655</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Belisário, L.b. And Pardo, T.a.s.</t>
+          <t>Wick-pedro, G. And Santos, R.l.s.</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Learning Rules For Automatic Identification Of Implicit Aspects In Portuguese. In The Proceedings Of The Xiv Symposium In Information And Human Language (stil), Pp. 82-91. November, 29 To December, 3. https://sol.sbc.org.br/index.php/stil/article/view/17787/17621</t>
+          <t>Avaliação de Parsers Na Detecção de Relações Essenciais do Modelo Universal Dependencies Para O Português. In The Proceedings Of The Vii Student Workshop On Information And Human Language Technology (tilic), Pp. 442-446. November, 30 https://sol.sbc.org.br/index.php/stil/article/view/17826/17660</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Machado, M.t.; Pardo, T.a.s.; Di Felippo, A.; Ruiz, E.e.s.</t>
+          <t>Belisário, L.b. And Pardo, T.a.s.</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Citação</t>
+          <t>Publicação</t>
         </is>
       </c>
     </row>
@@ -9605,17 +9605,17 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Structural Characterization And Graph-based Detection Of Fake News In Portuguese. In The Proceedings Of The Xiv Symposium In Information And Human Language (stil), Pp. 199-208. November, 29 To December, https://sol.sbc.org.br/index.php/stil/article/view/17799/17633</t>
+          <t>Learning Rules For Automatic Identification Of Implicit Aspects In Portuguese. In The Proceedings Of The Xiv Symposium In Information And Human Language (stil), Pp. 82-91. November, 29 To December, 3. https://sol.sbc.org.br/index.php/stil/article/view/17787/17621</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Santos, R.l.s. And Pardo, T.a.s.</t>
+          <t>Machado, M.t.; Pardo, T.a.s.; Di Felippo, A.; Ruiz, E.e.s.</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Publicação</t>
+          <t>Citação</t>
         </is>
       </c>
     </row>
@@ -9630,17 +9630,17 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>A Large Multi-genre Treebank For Brazilian Portuguese. In The Proceedings Of The Xiv Symposium In Information And Human Language (stil), Pp. 1-10. November, 29 To December, 3. [5 Citação] https://sol.sbc.org.br/index.php/stil/article/view/17778/17612</t>
+          <t>Structural Characterization And Graph-based Detection Of Fake News In Portuguese. In The Proceedings Of The Xiv Symposium In Information And Human Language (stil), Pp. 199-208. November, 29 To December, https://sol.sbc.org.br/index.php/stil/article/view/17799/17633</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Pardo, T.a.s.; Duran, M.s.; Lopes, L.; Di Felippo, A.; Roman, N.t.; Nunes, M.g.v. (2021). Porttinari</t>
+          <t>Santos, R.l.s. And Pardo, T.a.s.</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Citação</t>
+          <t>Publicação</t>
         </is>
       </c>
     </row>
@@ -9655,17 +9655,17 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Semantic-based Opinion Summarization. In The Proceedings Of Recent Advances In Natural Language Processing (ranlp), Pp. 624-633. September, 1-3. https://aclanthology.org/2021.ranlp-1.70//</t>
+          <t>A Large Multi-genre Treebank For Brazilian Portuguese. In The Proceedings Of The Xiv Symposium In Information And Human Language (stil), Pp. 1-10. November, 29 To December, 3. [5 Citação] https://sol.sbc.org.br/index.php/stil/article/view/17778/17612</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Inácio, M.l. And Pardo, T.a.s.</t>
+          <t>Pardo, T.a.s.; Duran, M.s.; Lopes, L.; Di Felippo, A.; Roman, N.t.; Nunes, M.g.v. (2021). Porttinari</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Publicação</t>
+          <t>Citação</t>
         </is>
       </c>
     </row>
@@ -9676,21 +9676,21 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Semantically Inspired Amr Alignment For The Portuguese Language. In The Proceedings Of The Conference On Empirical Methods In Natural Language Processing (emnlp’20), Pp. 1595-1600. November, 16-20. https://aclanthology.org/2020.emnlp-main.123.pdf</t>
+          <t>Semantic-based Opinion Summarization. In The Proceedings Of Recent Advances In Natural Language Processing (ranlp), Pp. 624-633. September, 1-3. https://aclanthology.org/2021.ranlp-1.70//</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Anchiêta, R.t. And Pardo, T.a.s</t>
+          <t>Inácio, M.l. And Pardo, T.a.s.</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Citação</t>
+          <t>Publicação</t>
         </is>
       </c>
     </row>
@@ -9705,12 +9705,12 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Pretrained Sequence-to- Sequence Models On Rdf-to-text Generation. In The Proceedings Of The 3rd International Workshop On Natural Language Generation From The Semantic Web (webnlg+), Pp. 131-136. December, 18. [3 Citação] https://webnlg-challenge.loria.fr/files/2020.webnlg-papers.14.pdf</t>
+          <t>Semantically Inspired Amr Alignment For The Portuguese Language. In The Proceedings Of The Conference On Empirical Methods In Natural Language Processing (emnlp’20), Pp. 1595-1600. November, 16-20. https://aclanthology.org/2020.emnlp-main.123.pdf</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Sobrevilla Cabezon, M.a. And Pardo, T.a.s.</t>
+          <t>Anchiêta, R.t. And Pardo, T.a.s</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -9730,37 +9730,37 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Nilc At Sr’20: Exploring Pre-trained Models In Surface Realisation. In The Proceedings Of The Third Workshop On Multilingual Surface Realisation (msr), Pp. 50-56. December https://aclanthology.org/2020.msr-1.6.pdf</t>
+          <t>Pretrained Sequence-to- Sequence Models On Rdf-to-text Generation. In The Proceedings Of The 3rd International Workshop On Natural Language Generation From The Semantic Web (webnlg+), Pp. 131-136. December, 18. [3 Citação] https://webnlg-challenge.loria.fr/files/2020.webnlg-papers.14.pdf</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Sobrevilla Cabezudo, M.a. And Pardo, T.a.s.</t>
+          <t>Sobrevilla Cabezon, M.a. And Pardo, T.a.s.</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Publicação</t>
+          <t>Citação</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>OceanML</t>
+          <t>NLP2</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Pinning synchronization of multiple fractional-order fuzzy complex-valued delayed spatiotemporal neural networks,” Chaos Solitons &amp; Fractals, vol. 182, p. 114801, 2024.</t>
+          <t>Nilc At Sr’20: Exploring Pre-trained Models In Surface Realisation. In The Proceedings Of The Third Workshop On Multilingual Surface Realisation (msr), Pp. 50-56. December https://aclanthology.org/2020.msr-1.6.pdf</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>K. Wu, M. Tang, Z. Liu, H. Ren, and L. Zhao,</t>
+          <t>Sobrevilla Cabezudo, M.a. And Pardo, T.a.s.</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Clustered and deep echo state networks for signal noise reduction, Machine Learning, vol. 111, pp. 2885-2904, 2022.</t>
+          <t>Pinning synchronization of multiple fractional-order fuzzy complex-valued delayed spatiotemporal neural networks,” Chaos Solitons &amp; Fractals, vol. 182, p. 114801, 2024.</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>L. de Oliveira Junior, F. Stelzer, and L. Zhao,</t>
+          <t>K. Wu, M. Tang, Z. Liu, H. Ren, and L. Zhao,</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>A Physics-Informed Neural Operator for the Simulation of Surface Waves, Journal of Offshore Mechanics and Arctic Engineering, vol. 146, no. 061201, Feb. 2024, doi: 10.1115/1.4064676.</t>
+          <t>Clustered and deep echo state networks for signal noise reduction, Machine Learning, vol. 111, pp. 2885-2904, 2022.</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>M. S. Mathias et al.,</t>
+          <t>L. de Oliveira Junior, F. Stelzer, and L. Zhao,</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Modelling graph neural network by aggregating the activation maps of self-organizing map, in 2024 International Joint Conference on Neural Networks IJCNN, 2024, vol. 1, pp. 1-8.</t>
+          <t>A Physics-Informed Neural Operator for the Simulation of Surface Waves, Journal of Offshore Mechanics and Arctic Engineering, vol. 146, no. 061201, Feb. 2024, doi: 10.1115/1.4064676.</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>L. V. C. Martins, D. Ji, and L. Zhao,</t>
+          <t>M. S. Mathias et al.,</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -9855,17 +9855,17 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>A Neural Operator for the Estimation of Wave Heights from Wind Data In: 43rd International Conference on Ocean, Offshore &amp; Arctic Engineering.</t>
+          <t>Modelling graph neural network by aggregating the activation maps of self-organizing map, in 2024 International Joint Conference on Neural Networks IJCNN, 2024, vol. 1, pp. 1-8.</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>M. S. Mathias et al.,</t>
+          <t>L. V. C. Martins, D. Ji, and L. Zhao,</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Artigo Acadêmico Completo Publicado (revista)</t>
+          <t>Publicação</t>
         </is>
       </c>
     </row>
@@ -9880,12 +9880,12 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Early Detection of Extreme Storm Tide Events Using Multimodal Data Processing, Proceedings of the AAAI Conference on Artificial Intelligence, vol. 38, no. 20, Art. no. 20, Mar. 2024, doi: 10.1609/aaai.v38i20.30194.</t>
+          <t>A Neural Operator for the Estimation of Wave Heights from Wind Data In: 43rd International Conference on Ocean, Offshore &amp; Arctic Engineering.</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>M. Barros et al.,</t>
+          <t>M. S. Mathias et al.,</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -9926,21 +9926,21 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>TransGNN: A transductive graph neural network with graph dynamic embedding, in 2023 International Joint Conference on Neural Networks IJCNN, 2023, vol. 1, pp. 1-8.</t>
+          <t>Early Detection of Extreme Storm Tide Events Using Multimodal Data Processing, Proceedings of the AAAI Conference on Artificial Intelligence, vol. 38, no. 20, Art. no. 20, Mar. 2024, doi: 10.1609/aaai.v38i20.30194.</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>L. Anghinoni, Y. Zhu, D. Ji, and L. Zhao,</t>
+          <t>M. Barros et al.,</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Publicação</t>
+          <t>Artigo Acadêmico Completo Publicado (revista)</t>
         </is>
       </c>
     </row>
@@ -9955,17 +9955,17 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Early Detection of Extreme Storm Tide Events Using Multimodal Data Processing, Proceedings of the 2024 Brazilian Conference on Intelligent Systems.</t>
+          <t>TransGNN: A transductive graph neural network with graph dynamic embedding, in 2023 International Joint Conference on Neural Networks IJCNN, 2023, vol. 1, pp. 1-8.</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>M. Barros et al.,</t>
+          <t>L. Anghinoni, Y. Zhu, D. Ji, and L. Zhao,</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Artigo Acadêmico Completo Publicado (revista)</t>
+          <t>Publicação</t>
         </is>
       </c>
     </row>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Embracing Data Irregularities in Multivariate Time Series with Recurrent and Graph Neural Networks, Proceedings of the 2023 Brazilian Conference on Intelligent Systems. This paper received the BRACIS 2023 BEST PAPER AWARD.</t>
+          <t>Early Detection of Extreme Storm Tide Events Using Multimodal Data Processing, Proceedings of the 2024 Brazilian Conference on Intelligent Systems.</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -10005,12 +10005,12 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>A Physics-Informed Neural Operator for the Simulation of Surface Waves, in Proc. 42nd Int. Conf. Ocean, Offshore &amp; Arctic Eng., 2023.</t>
+          <t>Embracing Data Irregularities in Multivariate Time Series with Recurrent and Graph Neural Networks, Proceedings of the 2023 Brazilian Conference on Intelligent Systems. This paper received the BRACIS 2023 BEST PAPER AWARD.</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>M. S. Mathias, C. F. D. Netto, F. M. Moreno, J. F. Coelho, L. P. Freitas, M. R. Barros, P. C. Mello, M. Dottori, A. H. Reali Costa, A. C. Nogueira Junior, E. S. Gomi, F. G. Cozman, and E. A. Tannuri,</t>
+          <t>M. Barros et al.,</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Echo State Networks for Surface Current Forecasting in a Port Access Channel, in Proc. 42nd Int. Conf. Ocean, Offshore &amp; Arctic Eng., 2023.</t>
+          <t>A Physics-Informed Neural Operator for the Simulation of Surface Waves, in Proc. 42nd Int. Conf. Ocean, Offshore &amp; Arctic Eng., 2023.</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>F. M. Moreno, M. R. Barros, C. F. D. Netto, J. F. Coelho, L. P. Freitas, M. S. Mathias, M. Dottori, A. H. Reali Costa, E. S. Gomi, F. G. Cozman, and E. A. Tannuri,</t>
+          <t>M. S. Mathias, C. F. D. Netto, F. M. Moreno, J. F. Coelho, L. P. Freitas, M. R. Barros, P. C. Mello, M. Dottori, A. H. Reali Costa, A. C. Nogueira Junior, E. S. Gomi, F. G. Cozman, and E. A. Tannuri,</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Modeling Oceanic Variables With Graph-Guided Networks for Irregularly Sampled Multivariate Time Series, in Proc. 42nd Int. Conf. Ocean, Offshore &amp; Arctic Eng., 2023.</t>
+          <t>Echo State Networks for Surface Current Forecasting in a Port Access Channel, in Proc. 42nd Int. Conf. Ocean, Offshore &amp; Arctic Eng., 2023.</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>J. F. Coelho, M. R. Barros, C. F. D. Netto, F. M. Moreno, L. P. Freitas, M. S. Mathias, F. G. Cozman, M. Dottori, E. S. Gomi, E. A. Tannuri, and A. H. Reali Costa,</t>
+          <t>F. M. Moreno, M. R. Barros, C. F. D. Netto, J. F. Coelho, L. P. Freitas, M. S. Mathias, M. Dottori, A. H. Reali Costa, E. S. Gomi, F. G. Cozman, and E. A. Tannuri,</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -10072,25 +10072,25 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>PROINDL</t>
+          <t>OceanML</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Disappearing Without a Trace: Coverage, Community, Quality, and Temporal Dynamics of Wikipedia Articles on Endangered Brazilian Indigenous Languages. Proc. of ICWSM 24. May 2024.</t>
+          <t>Modeling Oceanic Variables With Graph-Guided Networks for Irregularly Sampled Multivariate Time Series, in Proc. 42nd Int. Conf. Ocean, Offshore &amp; Arctic Eng., 2023.</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Marisa Vasconcelos, Priscilla Mizukani, Claudio Pinhanez.</t>
+          <t>J. F. Coelho, M. R. Barros, C. F. D. Netto, F. M. Moreno, L. P. Freitas, M. S. Mathias, F. G. Cozman, M. Dottori, E. S. Gomi, E. A. Tannuri, and A. H. Reali Costa,</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Artigo Completo</t>
+          <t>Artigo Acadêmico Completo Publicado (revista)</t>
         </is>
       </c>
     </row>
@@ -10105,12 +10105,12 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Quantifying the Ethical Dilemma of Using Culturally Toxic Training Data in AI Tools for Indigenous Languages. Proc. of the SIGUL workshop of LREC-COLING 24. May 2024.</t>
+          <t>Disappearing Without a Trace: Coverage, Community, Quality, and Temporal Dynamics of Wikipedia Articles on Endangered Brazilian Indigenous Languages. Proc. of ICWSM 24. May 2024.</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>P. Domingues, C. Pinhanez, P. Cavalin, J. Nogima.</t>
+          <t>Marisa Vasconcelos, Priscilla Mizukani, Claudio Pinhanez.</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Fixing Rogue Memorization in Many-to-One Multilingual Translators of Extremely-Low-Resource Languages by Rephrasing Training Samples. NAACL 24 Companion June 2024.</t>
+          <t>Quantifying the Ethical Dilemma of Using Culturally Toxic Training Data in AI Tools for Indigenous Languages. Proc. of the SIGUL workshop of LREC-COLING 24. May 2024.</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>P. Cavalin, P. Domingues, C. Pinhanez, J. Nogima.</t>
+          <t>P. Domingues, C. Pinhanez, P. Cavalin, J. Nogima.</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -10155,12 +10155,12 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Portal NURC-SP: Design, Development, and Speech Processing Corpora Resources to Support the Public Dissemination of Portuguese Spoken Language. In: 16th International Conference on Computational Processing of Portuguese PROPOR 2024, 2024, Santiago de Compostela. Proceedings of the 16th Internation</t>
+          <t>Fixing Rogue Memorization in Many-to-One Multilingual Translators of Extremely-Low-Resource Languages by Rephrasing Training Samples. NAACL 24 Companion June 2024.</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>RODRIGUES, A. C. ; MACEDO, A. A. ; CANDIDO JUNIOR, A. ; SVARTMAN, F. R. F. ; CRAVEIRO, G. M. ; LEITE, M. Q. ; ALU´ISIO, S. M. ; SANTOS, V. G. ; GARCIA, V. M. .</t>
+          <t>P. Cavalin, P. Domingues, C. Pinhanez, J. Nogima.</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -10180,17 +10180,17 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Human Evaluation of the Usefulness of FineTuned English Translators for the Guarani Mbya and Nheengatu Indigenous Languages. Proc. of the ILLC workshop of Propor 24. March 2024.</t>
+          <t>Portal NURC-SP: Design, Development, and Speech Processing Corpora Resources to Support the Public Dissemination of Portuguese Spoken Language. In: 16th International Conference on Computational Processing of Portuguese PROPOR 2024, 2024, Santiago de Compostela. Proceedings of the 16th Internation</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>P. Cavalin, C. Pinhanez, J. Nogima.</t>
+          <t>RODRIGUES, A. C. ; MACEDO, A. A. ; CANDIDO JUNIOR, A. ; SVARTMAN, F. R. F. ; CRAVEIRO, G. M. ; LEITE, M. Q. ; ALU´ISIO, S. M. ; SANTOS, V. G. ; GARCIA, V. M. .</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Artigo Curto</t>
+          <t>Artigo Completo</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Human Evaluation of the Usefulness of FineTuned English Translators for the Guarani Mbya and Nheengatu Indigenous Languages. Proc. of the AmericasNLP workshop of NAACL 24. June 2024.</t>
+          <t>Human Evaluation of the Usefulness of FineTuned English Translators for the Guarani Mbya and Nheengatu Indigenous Languages. Proc. of the ILLC workshop of Propor 24. March 2024.</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -10230,17 +10230,17 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Harnessing the Power of Artificial Intelligence to Vitalize Endangered Indigenous Languages: Technologies and Experiences. Arxiv: 2407.12620. 2024.</t>
+          <t>Human Evaluation of the Usefulness of FineTuned English Translators for the Guarani Mbya and Nheengatu Indigenous Languages. Proc. of the AmericasNLP workshop of NAACL 24. June 2024.</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>C. Pinhanez, P. Cavalin, L. Storto, T. Finbow and A. Cobbinah and J. Nogima and M. Vasconcelos and P. Domingues and P. Mizukami and N. Grell and M. Gongora and I. Gonçalves. H</t>
+          <t>P. Cavalin, C. Pinhanez, J. Nogima.</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Outros (relatórios Técnicos, Capítulos de Livros Etc.)</t>
+          <t>Artigo Curto</t>
         </is>
       </c>
     </row>
@@ -10255,12 +10255,12 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Sentence-level Aggregation of Lexical Metrics Correlate Stronger with Human Judgements than Corpus-level Aggregation. Arxiv: 2407.12832. 2024.</t>
+          <t>Harnessing the Power of Artificial Intelligence to Vitalize Endangered Indigenous Languages: Technologies and Experiences. Arxiv: 2407.12620. 2024.</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>P. Cavalin, P. Domingues, C. Pinhanez</t>
+          <t>C. Pinhanez, P. Cavalin, L. Storto, T. Finbow and A. Cobbinah and J. Nogima and M. Vasconcelos and P. Domingues and P. Mizukami and N. Grell and M. Gongora and I. Gonçalves. H</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -10276,21 +10276,21 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Balancing Social Impact, Opportunities, And Ethical Constraints Of Using Ai In The Documentation And Vitalization Of Indigenous Languages. In Proc. Of The Ijcai 2023 Special Track On Ai For Good. 2023.</t>
+          <t>Sentence-level Aggregation of Lexical Metrics Correlate Stronger with Human Judgements than Corpus-level Aggregation. Arxiv: 2407.12832. 2024.</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>C. Pinhanez, P. Cavalin, M. Vasconcelos, J. Nogima.</t>
+          <t>P. Cavalin, P. Domingues, C. Pinhanez</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Artigo Completo</t>
+          <t>Outros (relatórios Técnicos, Capítulos de Livros Etc.)</t>
         </is>
       </c>
     </row>
@@ -10305,17 +10305,17 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>How To Structure The Design Workshop Of A Conversational Language Aid For/with An Indigenous Community? Cui@chi’23 Workshop. 2023.</t>
+          <t>Balancing Social Impact, Opportunities, And Ethical Constraints Of Using Ai In The Documentation And Vitalization Of Indigenous Languages. In Proc. Of The Ijcai 2023 Special Track On Ai For Good. 2023.</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>C. Pinhanez.</t>
+          <t>C. Pinhanez, P. Cavalin, M. Vasconcelos, J. Nogima.</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Artigo Curto</t>
+          <t>Artigo Completo</t>
         </is>
       </c>
     </row>
@@ -10330,12 +10330,12 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Understanding Native Language Identification For Brazilian Indigenous Languages, Americasnlp@acl Work Shop, 2023.</t>
+          <t>How To Structure The Design Workshop Of A Conversational Language Aid For/with An Indigenous Community? Cui@chi’23 Workshop. 2023.</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>P. Cavalin, P.h. Domingues, J. Nogima, C. Pinhanez,</t>
+          <t>C. Pinhanez.</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -10355,17 +10355,17 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Disappearing Without A Trace: Coverage, Community, Quality, And Temporal Dynamics Of Wikipedia Articles On Endangered Brazilian Indigenous Languages. Submitted To Icwsm 23.</t>
+          <t>Understanding Native Language Identification For Brazilian Indigenous Languages, Americasnlp@acl Work Shop, 2023.</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Marisa Vasconcelos, Priscilla Mizukani, Claudio Pinhanez.</t>
+          <t>P. Cavalin, P.h. Domingues, J. Nogima, C. Pinhanez,</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Em Preparação, Em Revisão Ou Aceito Para Publicação</t>
+          <t>Artigo Curto</t>
         </is>
       </c>
     </row>
@@ -10380,12 +10380,12 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>A Trade-off Study On The Ethical Dilemma Of Using Culturally Toxic Training Data In Ai Tools For Indigenous Languages. Submitted To Aaai 24.</t>
+          <t>Disappearing Without A Trace: Coverage, Community, Quality, And Temporal Dynamics Of Wikipedia Articles On Endangered Brazilian Indigenous Languages. Submitted To Icwsm 23.</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>P. Domingues, C. Pinhanez, P. Cavalin, J. Nogima.</t>
+          <t>Marisa Vasconcelos, Priscilla Mizukani, Claudio Pinhanez.</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Report On Wikipedia Articles On Endangered Indigenous Languages In Brazil. To Be Published In 2023.</t>
+          <t>A Trade-off Study On The Ethical Dilemma Of Using Culturally Toxic Training Data In Ai Tools For Indigenous Languages. Submitted To Aaai 24.</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>M. Vasconcelos, P. Mizukani, C. Pinhanez.</t>
+          <t>P. Domingues, C. Pinhanez, P. Cavalin, J. Nogima.</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Report On The Existence Of Content In Brazilian Indigenous Languages In Selected Social Media Outlets And Survey Of Online Practices Of Indigenous Communities In Brazil. To Be Published In 2023.</t>
+          <t>Report On Wikipedia Articles On Endangered Indigenous Languages In Brazil. To Be Published In 2023.</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -10455,17 +10455,17 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Balancing Social Impact, Opportunities, and Ethical Constraints of Using AI in the Documentation and Vitalization of Indigenous Languages. In Proc. of the IJCAI 2023 special track on AI for Good. August 2023.</t>
+          <t>Report On The Existence Of Content In Brazilian Indigenous Languages In Selected Social Media Outlets And Survey Of Online Practices Of Indigenous Communities In Brazil. To Be Published In 2023.</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>C. Pinhanez, P. Cavalin, M. Vasconcelos, J. Nogima.</t>
+          <t>M. Vasconcelos, P. Mizukani, C. Pinhanez.</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Artigo Completo</t>
+          <t>Em Preparação, Em Revisão Ou Aceito Para Publicação</t>
         </is>
       </c>
     </row>
@@ -10480,12 +10480,12 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Determination of Harmonic Parameters in Pathological Voices-Efficient Algorithm. Applied Sciences-Basel, v. 13, p. 2333, 2023.</t>
+          <t>Balancing Social Impact, Opportunities, and Ethical Constraints of Using AI in the Documentation and Vitalization of Indigenous Languages. In Proc. of the IJCAI 2023 special track on AI for Good. August 2023.</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>FERNANDES, JOANA FILIPA TEIXEIRA ; FREITAS, DIAMANTINO ; JUNIOR, ARNALDO CANDIDO ; TEIXEIRA, JOAO PAULO .</t>
+          <t>C. Pinhanez, P. Cavalin, M. Vasconcelos, J. Nogima.</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -10505,12 +10505,12 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Recursos para o processamento de Fala. In: Caseli, H.M.; Nunes, M.G.V.. Org. Processamento de Linguagem Natural: Conceitos, Tecnicas e Aplicações em Portugués. 1ed.S ao Carlos: BPLN, 2023, v. , p. 61-82.</t>
+          <t>Determination of Harmonic Parameters in Pathological Voices-Efficient Algorithm. Applied Sciences-Basel, v. 13, p. 2333, 2023.</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>CASANOVA, E. ; SANTOS, V. G. ; SVARTMAN, F. R. F. ; LEITE, M. Q. ; CANDIDO JUNIOR, A. ; MARCACINI, R. M. ; Solange Rezende; O. ; ALUÍSIO, S. M. .</t>
+          <t>FERNANDES, JOANA FILIPA TEIXEIRA ; FREITAS, DIAMANTINO ; JUNIOR, ARNALDO CANDIDO ; TEIXEIRA, JOAO PAULO .</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Por uma abordagem perspectivista e ”ecologica” do contato lingu ´ıstico entre portugues e nheengatu. Revista Dialogos Revdia, v. 11, p. 1-29, 2023.</t>
+          <t>Recursos para o processamento de Fala. In: Caseli, H.M.; Nunes, M.G.V.. Org. Processamento de Linguagem Natural: Conceitos, Tecnicas e Aplicações em Portugués. 1ed.S ao Carlos: BPLN, 2023, v. , p. 61-82.</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>GOMES, Mariana Payno ; FINBOW, Thomas Daniel.</t>
+          <t>CASANOVA, E. ; SANTOS, V. G. ; SVARTMAN, F. R. F. ; LEITE, M. Q. ; CANDIDO JUNIOR, A. ; MARCACINI, R. M. ; Solange Rezende; O. ; ALUÍSIO, S. M. .</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -10555,17 +10555,17 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Understanding Native Language Identification for Brazilian Indigenous Languages, Proc. of the AmericasNLP workshop of ACL 23. 2023.</t>
+          <t>Por uma abordagem perspectivista e ”ecologica” do contato lingu ´ıstico entre portugues e nheengatu. Revista Dialogos Revdia, v. 11, p. 1-29, 2023.</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>P. Cavalin, P.H. Domingues, J. Nogima, C. Pinhanez,</t>
+          <t>GOMES, Mariana Payno ; FINBOW, Thomas Daniel.</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Artigo Curto</t>
+          <t>Artigo Completo</t>
         </is>
       </c>
     </row>
@@ -10580,15 +10580,40 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
+          <t>Understanding Native Language Identification for Brazilian Indigenous Languages, Proc. of the AmericasNLP workshop of ACL 23. 2023.</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>P. Cavalin, P.H. Domingues, J. Nogima, C. Pinhanez,</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Artigo Curto</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>PROINDL</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
           <t>Discriminant Audio Properties in Deep Learning Based Respiratory Insufficiency Detection in Brazilian Portuguese. In: 21st International Conference of Artificial Intelligence in Medicine AIME 2O23, 2023, Portoroz, Slovenia. Artificial Intelligence in Medicine. Cham: Springer Nature Switzerland, 20</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr">
+      <c r="D408" t="inlineStr">
         <is>
           <t>GAUY, M. M. ; BERTI, L. C. ; CANDIDO JUNIOR, A. ; CAMARGO NETO, A. C. ; GOLDMAN, A. ; LEVIN, A. S. S. ; MARTINS, M. ; MEDEIROS, B. R. ; QUEIROZ, M. ; SABINO, E. C. ; SVARTMAN, F. R. F. ; FINGER, M. .</t>
         </is>
       </c>
-      <c r="E407" t="inlineStr">
+      <c r="E408" t="inlineStr">
         <is>
           <t>Artigo Curto</t>
         </is>
